--- a/data/source/ontologies_source.xlsx
+++ b/data/source/ontologies_source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fbosche\Documents\GitHub\BE-OLS\data\source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007FE4DB-E1C1-4490-84D3-B9C2A7BC64AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E6E8BD-D2A1-4833-BF86-BE9CFE30934C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1380" yWindow="2655" windowWidth="21600" windowHeight="12360" xr2:uid="{C460B36E-D875-4E13-ACEB-9CF2004FB6B5}"/>
   </bookViews>
@@ -283,7 +283,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E108" authorId="10" shapeId="0" xr:uid="{FF38AB15-F518-4A75-8FD0-5D30FB36F963}">
+    <comment ref="E109" authorId="10" shapeId="0" xr:uid="{FF38AB15-F518-4A75-8FD0-5D30FB36F963}">
       <text>
         <r>
           <rPr>
@@ -300,7 +300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E109" authorId="11" shapeId="0" xr:uid="{C1789974-873D-4FE1-B73F-043CBD4ED103}">
+    <comment ref="E110" authorId="11" shapeId="0" xr:uid="{C1789974-873D-4FE1-B73F-043CBD4ED103}">
       <text>
         <r>
           <rPr>
@@ -317,7 +317,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M116" authorId="12" shapeId="0" xr:uid="{9B4FF538-E0FF-4ED4-A111-F93178D73F43}">
+    <comment ref="M117" authorId="12" shapeId="0" xr:uid="{9B4FF538-E0FF-4ED4-A111-F93178D73F43}">
       <text>
         <r>
           <rPr>
@@ -334,7 +334,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E138" authorId="13" shapeId="0" xr:uid="{BAF4458C-FE0F-4442-9348-DACD7E1A9B32}">
+    <comment ref="E139" authorId="13" shapeId="0" xr:uid="{BAF4458C-FE0F-4442-9348-DACD7E1A9B32}">
       <text>
         <r>
           <rPr>
@@ -351,7 +351,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E149" authorId="14" shapeId="0" xr:uid="{CAD6BC40-6B67-4E9E-AB3E-DA05BF8F7896}">
+    <comment ref="E150" authorId="14" shapeId="0" xr:uid="{CAD6BC40-6B67-4E9E-AB3E-DA05BF8F7896}">
       <text>
         <r>
           <rPr>
@@ -368,7 +368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E152" authorId="15" shapeId="0" xr:uid="{3EE948F8-4E0F-4FD4-8BC9-EA54C6408FF1}">
+    <comment ref="E153" authorId="15" shapeId="0" xr:uid="{3EE948F8-4E0F-4FD4-8BC9-EA54C6408FF1}">
       <text>
         <r>
           <rPr>
@@ -390,7 +390,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2920" uniqueCount="1172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2933" uniqueCount="1179">
   <si>
     <t>BE Product (Building)</t>
   </si>
@@ -1392,9 +1392,6 @@
   </si>
   <si>
     <t>obpa</t>
-  </si>
-  <si>
-    <t>https://sebseis.github.io/OBPA/</t>
   </si>
   <si>
     <t>https://www.sciencedirect.com/science/article/pii/S1474034623003440</t>
@@ -2692,9 +2689,6 @@
   </si>
   <si>
     <t>https://w3id.org/unocs#</t>
-  </si>
-  <si>
-    <t>https://w3.org/2003/01/geo/wgs84_pos#</t>
   </si>
   <si>
     <t>https://w3id.org/sbeo#</t>
@@ -3926,6 +3920,33 @@
   </si>
   <si>
     <t>https://saref.etsi.org/saref4bldg/</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/2003/01/geo/wgs84_pos#</t>
+  </si>
+  <si>
+    <t>OntoBPR: An ontological workflow for building permit review</t>
+  </si>
+  <si>
+    <t>ontobpr</t>
+  </si>
+  <si>
+    <t>https://w3id.org/ontobpr#</t>
+  </si>
+  <si>
+    <t>https://github.com/RUB-Informatik-im-Bauwesen/ontobpr; https://doi.org/10.1016/j.aei.2025.103369</t>
+  </si>
+  <si>
+    <t>CC BY SA 4.0</t>
+  </si>
+  <si>
+    <t>Building permitting is essential for ensuring the safety, sustainability, and societal alignment of construction projects. Despite interest from both practitioners and researchers, the process remains largely manual and fragmented. Ontologies offer a promising solution by managing complexity and enabling automation through semantic information, though current ontologies in the building permit domain are limited to specific aspects like building code checking. On the process level, the OntoBPR framework integrates multiple domain-specific ontologies for a seamless digital permitting process and provides a workflow to automate the lifecycle of the permit review. Therefore, it suggests integrating the submitted building application using standardized information containers. The paper explores how digital applications can be submitted, reviewed, verified for completeness, and forwarded to authorities, and how permit review results can be gathered to support decision-making and automate notification issuance, and it provides a demonstration in a case study. In conclusion, OntoBPR formalizes a multi-layered ontology that advances and aligns the partitioned building permit process and provides an adaptable framework to harmonize diverse legal, informatics, and procedural aspects.</t>
+  </si>
+  <si>
+    <t>obpa, isoprops</t>
+  </si>
+  <si>
+    <t>https://w3id.org/obpa#</t>
   </si>
 </sst>
 </file>
@@ -4214,10 +4235,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}" name="Table2" displayName="Table2" ref="A1:V159" totalsRowShown="0" headerRowDxfId="14">
-  <autoFilter ref="A1:V159" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V159">
-    <sortCondition ref="B1:B159"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}" name="Table2" displayName="Table2" ref="A1:V160" totalsRowShown="0" headerRowDxfId="14">
+  <autoFilter ref="A1:V160" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V160">
+    <sortCondition ref="B1:B160"/>
   </sortState>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{9A74C9B8-D669-464E-AF30-98194DC54E48}" name="title"/>
@@ -4632,7 +4653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6484B993-682B-477D-B31E-A58D58B7BF22}">
-  <dimension ref="A1:Z159"/>
+  <dimension ref="A1:Z160"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.5703125" customWidth="1"/>
@@ -4659,87 +4680,87 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>630</v>
+      </c>
+      <c r="C1" s="20" t="s">
         <v>632</v>
       </c>
-      <c r="B1" s="20" t="s">
-        <v>631</v>
-      </c>
-      <c r="C1" s="20" t="s">
+      <c r="D1" s="21" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1" s="20" t="s">
         <v>633</v>
       </c>
-      <c r="D1" s="21" t="s">
-        <v>646</v>
-      </c>
-      <c r="E1" s="20" t="s">
+      <c r="F1" s="20" t="s">
+        <v>790</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>708</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>707</v>
+      </c>
+      <c r="I1" s="22" t="s">
         <v>634</v>
       </c>
-      <c r="F1" s="20" t="s">
-        <v>792</v>
-      </c>
-      <c r="G1" s="20" t="s">
+      <c r="J1" s="22" t="s">
+        <v>635</v>
+      </c>
+      <c r="K1" s="22" t="s">
+        <v>636</v>
+      </c>
+      <c r="L1" s="23" t="s">
+        <v>637</v>
+      </c>
+      <c r="M1" s="23" t="s">
+        <v>711</v>
+      </c>
+      <c r="N1" s="23" t="s">
+        <v>710</v>
+      </c>
+      <c r="O1" s="24" t="s">
         <v>709</v>
       </c>
-      <c r="H1" s="20" t="s">
-        <v>708</v>
-      </c>
-      <c r="I1" s="22" t="s">
-        <v>635</v>
-      </c>
-      <c r="J1" s="22" t="s">
-        <v>636</v>
-      </c>
-      <c r="K1" s="22" t="s">
-        <v>637</v>
-      </c>
-      <c r="L1" s="23" t="s">
-        <v>638</v>
-      </c>
-      <c r="M1" s="23" t="s">
-        <v>712</v>
-      </c>
-      <c r="N1" s="23" t="s">
-        <v>711</v>
-      </c>
-      <c r="O1" s="24" t="s">
-        <v>710</v>
-      </c>
       <c r="P1" s="24" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q1" s="24" t="s">
+        <v>706</v>
+      </c>
+      <c r="R1" s="24" t="s">
         <v>705</v>
       </c>
-      <c r="Q1" s="24" t="s">
-        <v>707</v>
-      </c>
-      <c r="R1" s="24" t="s">
-        <v>706</v>
-      </c>
       <c r="S1" s="24" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="T1" s="22" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="U1" s="20" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="V1" s="29" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="165" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B2" t="s">
         <v>500</v>
       </c>
-      <c r="B2" t="s">
-        <v>501</v>
-      </c>
       <c r="C2" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="D2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>503</v>
-      </c>
-      <c r="D2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>504</v>
       </c>
       <c r="F2" t="s">
         <v>38</v>
@@ -4757,13 +4778,13 @@
         <v>38</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="O2" s="30" t="s">
         <v>29</v>
@@ -4781,27 +4802,27 @@
         <v>30</v>
       </c>
       <c r="U2" s="28" t="s">
+        <v>861</v>
+      </c>
+      <c r="V2" s="3" t="s">
         <v>863</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="270" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>712</v>
+      </c>
+      <c r="B3" t="s">
         <v>713</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>715</v>
-      </c>
-      <c r="D3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>716</v>
       </c>
       <c r="F3" t="s">
         <v>38</v>
@@ -4810,7 +4831,7 @@
         <v>14</v>
       </c>
       <c r="I3" s="26" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="J3">
         <v>2026</v>
@@ -4819,13 +4840,13 @@
         <v>128</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="O3" s="30" t="s">
         <v>29</v>
@@ -4843,10 +4864,10 @@
         <v>30</v>
       </c>
       <c r="U3" s="30" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="V3" s="32" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="165" x14ac:dyDescent="0.25">
@@ -4908,10 +4929,10 @@
         <v>15</v>
       </c>
       <c r="U4" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="195" x14ac:dyDescent="0.25">
@@ -4922,13 +4943,13 @@
         <v>34</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D5" t="s">
         <v>38</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F5" t="s">
         <v>38</v>
@@ -4946,13 +4967,13 @@
         <v>35</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>36</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="O5" s="30" t="s">
         <v>29</v>
@@ -4970,10 +4991,10 @@
         <v>29</v>
       </c>
       <c r="U5" s="28" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="150" x14ac:dyDescent="0.25">
@@ -4981,10 +5002,10 @@
         <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D6" t="s">
         <v>38</v>
@@ -5011,13 +5032,13 @@
         <v>23</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="O6" s="30" t="s">
         <v>29</v>
@@ -5038,10 +5059,10 @@
         <v>15</v>
       </c>
       <c r="U6" s="28" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="225" x14ac:dyDescent="0.25">
@@ -5082,7 +5103,7 @@
         <v>38</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="O7" s="30" t="s">
         <v>29</v>
@@ -5100,10 +5121,10 @@
         <v>30</v>
       </c>
       <c r="U7" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="75" x14ac:dyDescent="0.25">
@@ -5114,7 +5135,7 @@
         <v>46</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D8" t="s">
         <v>38</v>
@@ -5138,7 +5159,7 @@
         <v>38</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>38</v>
@@ -5162,10 +5183,10 @@
         <v>30</v>
       </c>
       <c r="U8" s="28" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -5200,13 +5221,13 @@
         <v>23</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="O9" s="30" t="s">
         <v>29</v>
@@ -5227,27 +5248,27 @@
         <v>22</v>
       </c>
       <c r="U9" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="210" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>1070</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1084</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>1071</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>1069</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>1072</v>
       </c>
       <c r="F10" s="27" t="s">
         <v>38</v>
@@ -5256,7 +5277,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="J10">
         <v>2025</v>
@@ -5265,13 +5286,13 @@
         <v>128</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="O10" s="30" t="s">
         <v>30</v>
@@ -5283,19 +5304,19 @@
     </row>
     <row r="11" spans="1:22" ht="135" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B11" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="F11" s="27" t="s">
         <v>38</v>
@@ -5307,7 +5328,7 @@
         <v>5</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="J11">
         <v>2025</v>
@@ -5316,13 +5337,13 @@
         <v>128</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="O11" s="30" t="s">
         <v>30</v>
@@ -5334,19 +5355,19 @@
     </row>
     <row r="12" spans="1:22" ht="210" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="B12" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="F12" s="27" t="s">
         <v>38</v>
@@ -5355,7 +5376,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="J12">
         <v>2025</v>
@@ -5364,13 +5385,13 @@
         <v>128</v>
       </c>
       <c r="L12" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>1082</v>
+      </c>
+      <c r="N12" s="13" t="s">
         <v>1083</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>1084</v>
-      </c>
-      <c r="N12" s="13" t="s">
-        <v>1085</v>
       </c>
       <c r="O12" s="30" t="s">
         <v>30</v>
@@ -5382,19 +5403,19 @@
     </row>
     <row r="13" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="B13" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="F13" s="27" t="s">
         <v>38</v>
@@ -5406,7 +5427,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="J13">
         <v>2025</v>
@@ -5415,13 +5436,13 @@
         <v>128</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="O13" s="30" t="s">
         <v>30</v>
@@ -5433,25 +5454,25 @@
     </row>
     <row r="14" spans="1:22" ht="255" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B14" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="F14" s="27" t="s">
         <v>38</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="J14">
         <v>2025</v>
@@ -5460,13 +5481,13 @@
         <v>128</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="O14" s="30" t="s">
         <v>30</v>
@@ -5478,19 +5499,19 @@
     </row>
     <row r="15" spans="1:22" ht="225" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="B15" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>38</v>
@@ -5502,7 +5523,7 @@
         <v>8</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="J15">
         <v>2025</v>
@@ -5511,13 +5532,13 @@
         <v>128</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>80</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="O15" s="30" t="s">
         <v>30</v>
@@ -5529,13 +5550,13 @@
     </row>
     <row r="16" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C16" s="25" t="s">
         <v>1101</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>1103</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="1"/>
@@ -5556,13 +5577,13 @@
         <v>128</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="O16" s="30" t="s">
         <v>30</v>
@@ -5574,13 +5595,13 @@
     </row>
     <row r="17" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>1095</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>1097</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>38</v>
@@ -5596,7 +5617,7 @@
         <v>11</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="J17">
         <v>2025</v>
@@ -5605,13 +5626,13 @@
         <v>128</v>
       </c>
       <c r="L17" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="M17" s="3" t="s">
         <v>1098</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>1100</v>
-      </c>
       <c r="N17" s="13" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="O17" s="30" t="s">
         <v>30</v>
@@ -5653,13 +5674,13 @@
         <v>57</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="O18" s="30" t="s">
         <v>29</v>
@@ -5680,30 +5701,30 @@
         <v>15</v>
       </c>
       <c r="U18" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="B19" t="s">
         <v>59</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F19" t="s">
         <v>1162</v>
-      </c>
-      <c r="D19" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>1163</v>
-      </c>
-      <c r="F19" t="s">
-        <v>1164</v>
       </c>
       <c r="G19" t="s">
         <v>0</v>
@@ -5712,10 +5733,10 @@
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="O19" s="30" t="s">
         <v>30</v>
@@ -5733,19 +5754,19 @@
         <v>29</v>
       </c>
       <c r="U19" s="28" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V19" s="3" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>505</v>
+      </c>
+      <c r="B20" t="s">
         <v>506</v>
       </c>
-      <c r="B20" t="s">
-        <v>507</v>
-      </c>
       <c r="C20" t="s">
         <v>38</v>
       </c>
@@ -5753,7 +5774,7 @@
         <v>38</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F20" t="s">
         <v>38</v>
@@ -5768,14 +5789,14 @@
         <v>38</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="M20" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="N20" s="10" t="s">
         <v>510</v>
       </c>
-      <c r="N20" s="10" t="s">
-        <v>511</v>
-      </c>
       <c r="O20" s="30" t="s">
         <v>29</v>
       </c>
@@ -5792,10 +5813,10 @@
         <v>30</v>
       </c>
       <c r="U20" s="28" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="V20" s="3" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="60" x14ac:dyDescent="0.25">
@@ -5854,10 +5875,10 @@
         <v>15</v>
       </c>
       <c r="U21" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -5889,7 +5910,7 @@
         <v>38</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>69</v>
@@ -5916,27 +5937,27 @@
         <v>15</v>
       </c>
       <c r="U22" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V22" s="3" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="240" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B23" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>38</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>38</v>
@@ -5948,7 +5969,7 @@
         <v>4</v>
       </c>
       <c r="I23" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="J23">
         <v>2026</v>
@@ -5957,13 +5978,13 @@
         <v>128</v>
       </c>
       <c r="L23" s="3" t="s">
+        <v>1064</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>1065</v>
+      </c>
+      <c r="N23" s="13" t="s">
         <v>1066</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>1067</v>
-      </c>
-      <c r="N23" s="13" t="s">
-        <v>1068</v>
       </c>
       <c r="O23" s="30" t="s">
         <v>29</v>
@@ -6005,13 +6026,13 @@
         <v>23</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="O24" s="30" t="s">
         <v>29</v>
@@ -6032,27 +6053,27 @@
         <v>15</v>
       </c>
       <c r="U24" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V24" s="3" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B25" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>38</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="F25" s="27" t="s">
         <v>38</v>
@@ -6064,13 +6085,13 @@
         <v>0.2</v>
       </c>
       <c r="L25" s="3" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>1125</v>
+      </c>
+      <c r="N25" s="13" t="s">
         <v>1126</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>1127</v>
-      </c>
-      <c r="N25" s="13" t="s">
-        <v>1128</v>
       </c>
       <c r="O25" s="30" t="s">
         <v>30</v>
@@ -6121,7 +6142,7 @@
         <v>38</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="O26" s="30" t="s">
         <v>29</v>
@@ -6139,10 +6160,10 @@
         <v>30</v>
       </c>
       <c r="U26" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V26" s="3" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -6177,13 +6198,13 @@
         <v>82</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="O27" s="30" t="s">
         <v>29</v>
@@ -6201,10 +6222,10 @@
         <v>29</v>
       </c>
       <c r="U27" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -6215,7 +6236,7 @@
         <v>87</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D28" t="s">
         <v>38</v>
@@ -6263,27 +6284,27 @@
         <v>29</v>
       </c>
       <c r="U28" s="28" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V28" s="3" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="270" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B29" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>38</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="F29" s="27" t="s">
         <v>38</v>
@@ -6296,13 +6317,13 @@
         <v>0.1</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>100</v>
       </c>
       <c r="N29" s="13" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="O29" s="30" t="s">
         <v>30</v>
@@ -6347,7 +6368,7 @@
         <v>95</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="M30" s="10" t="s">
         <v>97</v>
@@ -6374,10 +6395,10 @@
         <v>78</v>
       </c>
       <c r="U30" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V30" s="3" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="75" x14ac:dyDescent="0.25">
@@ -6418,7 +6439,7 @@
         <v>38</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="O31" s="30" t="s">
         <v>31</v>
@@ -6436,10 +6457,10 @@
         <v>29</v>
       </c>
       <c r="U31" s="28" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="V31" s="3" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="300" x14ac:dyDescent="0.25">
@@ -6477,7 +6498,7 @@
         <v>107</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>28</v>
@@ -6501,10 +6522,10 @@
         <v>15</v>
       </c>
       <c r="U32" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V32" s="3" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -6566,21 +6587,21 @@
         <v>30</v>
       </c>
       <c r="U33" s="28" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V33" s="3" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B34" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D34" t="s">
         <v>38</v>
@@ -6601,13 +6622,13 @@
         <v>128</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="O34" s="30" t="s">
         <v>29</v>
@@ -6625,10 +6646,10 @@
         <v>29</v>
       </c>
       <c r="U34" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V34" s="3" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
     </row>
     <row r="35" spans="1:22" ht="180" x14ac:dyDescent="0.25">
@@ -6666,7 +6687,7 @@
         <v>38</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>117</v>
@@ -6690,10 +6711,10 @@
         <v>30</v>
       </c>
       <c r="U35" s="28" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V35" s="3" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="36" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -6731,7 +6752,7 @@
         <v>38</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="M36" s="3" t="s">
         <v>38</v>
@@ -6755,33 +6776,33 @@
         <v>30</v>
       </c>
       <c r="U36" s="28" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V36" s="3" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="37" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B37" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D37" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F37" t="s">
         <v>38</v>
       </c>
       <c r="G37" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I37" s="9">
         <v>0.2</v>
@@ -6793,13 +6814,13 @@
         <v>23</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="O37" s="33" t="s">
         <v>29</v>
@@ -6817,18 +6838,18 @@
         <v>29</v>
       </c>
       <c r="U37" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V37" s="3" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="255" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B38" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C38" t="s">
         <v>38</v>
@@ -6837,7 +6858,7 @@
         <v>38</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F38" t="s">
         <v>38</v>
@@ -6855,14 +6876,14 @@
         <v>38</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M38" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="N38" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="N38" s="3" t="s">
-        <v>552</v>
-      </c>
       <c r="O38" s="30" t="s">
         <v>29</v>
       </c>
@@ -6879,10 +6900,10 @@
         <v>29</v>
       </c>
       <c r="U38" s="28" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
     <row r="39" spans="1:22" ht="285" x14ac:dyDescent="0.25">
@@ -6923,7 +6944,7 @@
         <v>125</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="O39" s="30" t="s">
         <v>30</v>
@@ -6941,27 +6962,27 @@
         <v>29</v>
       </c>
       <c r="U39" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="40" spans="1:22" ht="165" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>571</v>
+      </c>
+      <c r="B40" t="s">
         <v>572</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>574</v>
-      </c>
       <c r="D40" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F40" t="s">
         <v>38</v>
@@ -6979,13 +7000,13 @@
         <v>23</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="O40" s="33" t="s">
         <v>29</v>
@@ -7003,27 +7024,27 @@
         <v>29</v>
       </c>
       <c r="U40" s="28" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="41" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" ht="285" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>566</v>
+      </c>
+      <c r="B41" t="s">
         <v>567</v>
       </c>
-      <c r="B41" t="s">
-        <v>568</v>
-      </c>
       <c r="C41" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="D41" t="s">
+        <v>578</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>570</v>
-      </c>
-      <c r="D41" t="s">
-        <v>579</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>571</v>
       </c>
       <c r="F41" t="s">
         <v>38</v>
@@ -7041,13 +7062,13 @@
         <v>23</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="O41" s="33" t="s">
         <v>29</v>
@@ -7065,10 +7086,10 @@
         <v>30</v>
       </c>
       <c r="U41" s="28" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="42" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -7079,7 +7100,7 @@
         <v>127</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="D42" t="s">
         <v>118</v>
@@ -7100,7 +7121,7 @@
         <v>128</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>130</v>
@@ -7124,27 +7145,27 @@
         <v>30</v>
       </c>
       <c r="U42" s="28" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="V42" s="3" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="43" spans="1:22" ht="135" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>559</v>
+      </c>
+      <c r="B43" t="s">
         <v>560</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="D43" t="s">
+        <v>38</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="D43" t="s">
-        <v>38</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>562</v>
       </c>
       <c r="F43" t="s">
         <v>38</v>
@@ -7162,13 +7183,13 @@
         <v>128</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="O43" s="30" t="s">
         <v>29</v>
@@ -7186,10 +7207,10 @@
         <v>30</v>
       </c>
       <c r="U43" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V43" s="3" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
     <row r="44" spans="1:22" ht="180" x14ac:dyDescent="0.25">
@@ -7197,7 +7218,7 @@
         <v>132</v>
       </c>
       <c r="B44" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C44" t="s">
         <v>38</v>
@@ -7227,13 +7248,13 @@
         <v>133</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="O44" s="30" t="s">
         <v>29</v>
@@ -7251,10 +7272,10 @@
         <v>29</v>
       </c>
       <c r="U44" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V44" s="3" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="45" spans="1:22" ht="135" x14ac:dyDescent="0.25">
@@ -7265,7 +7286,7 @@
         <v>138</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="D45" t="s">
         <v>142</v>
@@ -7289,7 +7310,7 @@
         <v>23</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>140</v>
@@ -7313,10 +7334,10 @@
         <v>29</v>
       </c>
       <c r="U45" s="28" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="46" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -7327,7 +7348,7 @@
         <v>144</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="D46" t="s">
         <v>142</v>
@@ -7351,7 +7372,7 @@
         <v>128</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>146</v>
@@ -7372,10 +7393,10 @@
         <v>29</v>
       </c>
       <c r="U46" s="28" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="47" spans="1:22" ht="180" x14ac:dyDescent="0.25">
@@ -7386,7 +7407,7 @@
         <v>148</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="D47" t="s">
         <v>142</v>
@@ -7434,10 +7455,10 @@
         <v>29</v>
       </c>
       <c r="U47" s="28" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="V47" s="3" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="48" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -7448,7 +7469,7 @@
         <v>154</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D48" t="s">
         <v>142</v>
@@ -7478,7 +7499,7 @@
         <v>157</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="O48" s="30" t="s">
         <v>29</v>
@@ -7496,10 +7517,10 @@
         <v>30</v>
       </c>
       <c r="U48" s="28" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="49" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -7510,7 +7531,7 @@
         <v>159</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D49" t="s">
         <v>142</v>
@@ -7540,7 +7561,7 @@
         <v>162</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="O49" s="30" t="s">
         <v>29</v>
@@ -7558,10 +7579,10 @@
         <v>29</v>
       </c>
       <c r="U49" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V49" s="3" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="50" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -7572,7 +7593,7 @@
         <v>164</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="D50" t="s">
         <v>142</v>
@@ -7596,13 +7617,13 @@
         <v>128</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="M50" s="3" t="s">
         <v>162</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="O50" s="30" t="s">
         <v>29</v>
@@ -7620,10 +7641,10 @@
         <v>30</v>
       </c>
       <c r="U50" s="28" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="51" spans="1:22" ht="180" x14ac:dyDescent="0.25">
@@ -7631,7 +7652,7 @@
         <v>135</v>
       </c>
       <c r="B51" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>136</v>
@@ -7653,13 +7674,13 @@
         <v>38</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="M51" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="O51" s="30" t="s">
         <v>29</v>
@@ -7677,13 +7698,13 @@
         <v>30</v>
       </c>
       <c r="U51" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="52" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>167</v>
       </c>
@@ -7691,7 +7712,7 @@
         <v>168</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="D52" t="s">
         <v>142</v>
@@ -7721,7 +7742,7 @@
         <v>171</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="O52" s="30" t="s">
         <v>29</v>
@@ -7739,13 +7760,13 @@
         <v>29</v>
       </c>
       <c r="U52" s="28" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="53" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" ht="180" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>172</v>
       </c>
@@ -7753,7 +7774,7 @@
         <v>173</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D53" t="s">
         <v>142</v>
@@ -7786,7 +7807,7 @@
         <v>176</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="O53" s="30" t="s">
         <v>29</v>
@@ -7804,10 +7825,10 @@
         <v>30</v>
       </c>
       <c r="U53" s="28" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="54" spans="1:22" ht="210" x14ac:dyDescent="0.25">
@@ -7818,7 +7839,7 @@
         <v>178</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D54" t="s">
         <v>142</v>
@@ -7866,10 +7887,10 @@
         <v>29</v>
       </c>
       <c r="U54" s="28" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="V54" s="3" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="55" spans="1:22" ht="180" x14ac:dyDescent="0.25">
@@ -7880,7 +7901,7 @@
         <v>183</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="D55" t="s">
         <v>142</v>
@@ -7893,13 +7914,13 @@
         <v>14</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="M55" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="O55" s="30" t="s">
         <v>29</v>
@@ -7917,10 +7938,10 @@
         <v>30</v>
       </c>
       <c r="U55" s="28" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="V55" s="3" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="56" spans="1:22" ht="60" x14ac:dyDescent="0.25">
@@ -7931,7 +7952,7 @@
         <v>185</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="D56" t="s">
         <v>142</v>
@@ -7944,7 +7965,7 @@
         <v>4</v>
       </c>
       <c r="H56" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="J56">
         <v>2019</v>
@@ -7953,13 +7974,13 @@
         <v>128</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="M56" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="O56" s="30" t="s">
         <v>29</v>
@@ -7977,10 +7998,10 @@
         <v>29</v>
       </c>
       <c r="U56" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V56" s="3" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="57" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -7991,7 +8012,7 @@
         <v>187</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D57" t="s">
         <v>142</v>
@@ -8039,10 +8060,10 @@
         <v>29</v>
       </c>
       <c r="U57" s="28" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="V57" s="3" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="58" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -8080,7 +8101,7 @@
         <v>38</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>38</v>
@@ -8104,19 +8125,19 @@
         <v>30</v>
       </c>
       <c r="U58" s="28" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V58" s="3" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="360" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>602</v>
+      </c>
+      <c r="B59" t="s">
         <v>603</v>
       </c>
-      <c r="B59" t="s">
-        <v>604</v>
-      </c>
       <c r="C59" t="s">
         <v>38</v>
       </c>
@@ -8124,7 +8145,7 @@
         <v>38</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F59" t="s">
         <v>38</v>
@@ -8145,7 +8166,7 @@
         <v>38</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>38</v>
@@ -8169,13 +8190,13 @@
         <v>30</v>
       </c>
       <c r="U59" s="28" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V59" s="3" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="60" spans="1:22" ht="75" x14ac:dyDescent="0.25">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>193</v>
       </c>
@@ -8183,7 +8204,7 @@
         <v>194</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="D60" t="s">
         <v>38</v>
@@ -8210,7 +8231,7 @@
         <v>196</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="O60" s="30" t="s">
         <v>29</v>
@@ -8228,10 +8249,10 @@
         <v>30</v>
       </c>
       <c r="U60" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V60" s="3" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="61" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -8269,13 +8290,13 @@
         <v>23</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="M61" s="3" t="s">
         <v>203</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="O61" s="30" t="s">
         <v>29</v>
@@ -8293,10 +8314,10 @@
         <v>30</v>
       </c>
       <c r="U61" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V61" s="3" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="62" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
@@ -8340,7 +8361,7 @@
         <v>208</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="O62" s="30" t="s">
         <v>29</v>
@@ -8358,13 +8379,13 @@
         <v>30</v>
       </c>
       <c r="U62" s="28" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V62" s="3" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="63" spans="1:22" ht="165" x14ac:dyDescent="0.25">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>209</v>
       </c>
@@ -8399,13 +8420,13 @@
         <v>38</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="M63" s="3" t="s">
         <v>213</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="O63" s="30" t="s">
         <v>29</v>
@@ -8423,10 +8444,10 @@
         <v>30</v>
       </c>
       <c r="U63" s="28" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V63" s="3" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="64" spans="1:22" ht="120" x14ac:dyDescent="0.25">
@@ -8464,10 +8485,10 @@
         <v>221</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="O64" s="30" t="s">
         <v>29</v>
@@ -8485,30 +8506,30 @@
         <v>30</v>
       </c>
       <c r="U64" s="28" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="V64" s="3" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
     </row>
     <row r="65" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>718</v>
+      </c>
+      <c r="B65" t="s">
         <v>719</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="D65" t="s">
+        <v>38</v>
+      </c>
+      <c r="E65" t="s">
         <v>721</v>
       </c>
-      <c r="D65" t="s">
-        <v>38</v>
-      </c>
-      <c r="E65" t="s">
-        <v>722</v>
-      </c>
       <c r="G65" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="I65" s="9" t="s">
         <v>230</v>
@@ -8520,14 +8541,14 @@
         <v>242</v>
       </c>
       <c r="L65" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="M65" s="3" t="s">
         <v>723</v>
       </c>
-      <c r="M65" s="3" t="s">
+      <c r="N65" s="3" t="s">
         <v>724</v>
       </c>
-      <c r="N65" s="3" t="s">
-        <v>725</v>
-      </c>
       <c r="O65" s="30" t="s">
         <v>29</v>
       </c>
@@ -8544,10 +8565,10 @@
         <v>30</v>
       </c>
       <c r="U65" s="30" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V65" s="32" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="66" spans="1:22" ht="60" x14ac:dyDescent="0.25">
@@ -8558,7 +8579,7 @@
         <v>224</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D66" t="s">
         <v>38</v>
@@ -8582,7 +8603,7 @@
         <v>225</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="M66" s="3" t="s">
         <v>38</v>
@@ -8606,10 +8627,10 @@
         <v>30</v>
       </c>
       <c r="U66" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V66" s="3" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="67" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -8620,7 +8641,7 @@
         <v>229</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D67" t="s">
         <v>38</v>
@@ -8644,13 +8665,13 @@
         <v>231</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="M67" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="O67" s="30" t="s">
         <v>29</v>
@@ -8668,10 +8689,10 @@
         <v>30</v>
       </c>
       <c r="U67" s="28" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V67" s="3" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
     </row>
     <row r="68" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -8715,7 +8736,7 @@
         <v>239</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="O68" s="30" t="s">
         <v>29</v>
@@ -8733,10 +8754,10 @@
         <v>30</v>
       </c>
       <c r="U68" s="28" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="V68" s="3" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="69" spans="1:22" ht="135" x14ac:dyDescent="0.25">
@@ -8771,13 +8792,13 @@
         <v>242</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="M69" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="O69" s="30" t="s">
         <v>29</v>
@@ -8795,13 +8816,13 @@
         <v>30</v>
       </c>
       <c r="U69" s="28" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V69" s="3" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="70" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>245</v>
       </c>
@@ -8833,13 +8854,13 @@
         <v>23</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="N70" s="3" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="O70" s="30" t="s">
         <v>29</v>
@@ -8857,10 +8878,10 @@
         <v>29</v>
       </c>
       <c r="U70" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V70" s="3" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="71" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -8871,7 +8892,7 @@
         <v>251</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D71" t="s">
         <v>38</v>
@@ -8895,13 +8916,13 @@
         <v>253</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="M71" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N71" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="O71" s="30" t="s">
         <v>29</v>
@@ -8919,25 +8940,25 @@
         <v>30</v>
       </c>
       <c r="U71" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V71" s="3" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="72" spans="1:22" ht="255" x14ac:dyDescent="0.25">
       <c r="A72" s="15" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C72" s="15" t="s">
         <v>38</v>
       </c>
       <c r="D72" s="18"/>
       <c r="E72" s="17" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F72" t="s">
         <v>38</v>
@@ -8949,22 +8970,22 @@
         <v>10</v>
       </c>
       <c r="I72" s="16" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J72" s="15">
         <v>2010</v>
       </c>
       <c r="K72" s="15" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="M72" s="13" t="s">
         <v>38</v>
       </c>
       <c r="N72" s="13" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="O72" s="36" t="s">
         <v>29</v>
@@ -8982,10 +9003,10 @@
         <v>30</v>
       </c>
       <c r="U72" s="28" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="V72" s="3" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="73" spans="1:22" ht="255" x14ac:dyDescent="0.25">
@@ -9026,7 +9047,7 @@
         <v>80</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="O73" s="30" t="s">
         <v>29</v>
@@ -9044,19 +9065,19 @@
         <v>30</v>
       </c>
       <c r="U73" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V73" s="3" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="74" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>484</v>
+      </c>
+      <c r="B74" s="15" t="s">
         <v>485</v>
       </c>
-      <c r="B74" s="15" t="s">
-        <v>486</v>
-      </c>
       <c r="C74" t="s">
         <v>38</v>
       </c>
@@ -9064,7 +9085,7 @@
         <v>38</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F74" t="s">
         <v>38</v>
@@ -9085,13 +9106,13 @@
         <v>23</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O74" s="30" t="s">
         <v>30</v>
@@ -9109,33 +9130,33 @@
         <v>30</v>
       </c>
       <c r="U74" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V74" s="3" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="75" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>725</v>
+      </c>
+      <c r="B75" t="s">
         <v>726</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="D75" t="s">
+        <v>38</v>
+      </c>
+      <c r="E75" s="1" t="s">
         <v>728</v>
-      </c>
-      <c r="D75" t="s">
-        <v>38</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>729</v>
       </c>
       <c r="G75" t="s">
         <v>15</v>
       </c>
       <c r="H75" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="I75" s="26" t="s">
         <v>72</v>
@@ -9147,13 +9168,13 @@
         <v>35</v>
       </c>
       <c r="L75" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="M75" s="3" t="s">
         <v>730</v>
       </c>
-      <c r="M75" s="3" t="s">
-        <v>731</v>
-      </c>
       <c r="N75" s="3" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="O75" s="30" t="s">
         <v>29</v>
@@ -9171,10 +9192,10 @@
         <v>30</v>
       </c>
       <c r="U75" s="30" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V75" s="32" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="76" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -9215,7 +9236,7 @@
         <v>265</v>
       </c>
       <c r="N76" s="3" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="O76" s="30" t="s">
         <v>29</v>
@@ -9233,27 +9254,27 @@
         <v>29</v>
       </c>
       <c r="U76" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V76" s="3" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="77" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="B77" t="s">
+        <v>640</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B77" t="s">
-        <v>641</v>
-      </c>
-      <c r="C77" s="1" t="s">
+      <c r="D77" t="s">
+        <v>38</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>513</v>
-      </c>
-      <c r="D77" t="s">
-        <v>38</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>514</v>
       </c>
       <c r="F77" t="s">
         <v>38</v>
@@ -9274,13 +9295,13 @@
         <v>23</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="M77" s="3" t="s">
         <v>80</v>
       </c>
       <c r="N77" s="3" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="O77" s="30" t="s">
         <v>29</v>
@@ -9298,19 +9319,19 @@
         <v>29</v>
       </c>
       <c r="U77" s="28" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="V77" s="3" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
     </row>
     <row r="78" spans="1:22" ht="165" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>597</v>
+      </c>
+      <c r="B78" t="s">
         <v>598</v>
       </c>
-      <c r="B78" t="s">
-        <v>599</v>
-      </c>
       <c r="C78" t="s">
         <v>38</v>
       </c>
@@ -9318,7 +9339,7 @@
         <v>38</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F78" t="s">
         <v>38</v>
@@ -9339,7 +9360,7 @@
         <v>38</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="M78" s="3" t="s">
         <v>38</v>
@@ -9363,27 +9384,27 @@
         <v>30</v>
       </c>
       <c r="U78" s="28" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V78" s="3" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="79" spans="1:22" ht="225" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>599</v>
+      </c>
+      <c r="B79" t="s">
+        <v>596</v>
+      </c>
+      <c r="C79" t="s">
+        <v>38</v>
+      </c>
+      <c r="D79" t="s">
+        <v>38</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="B79" t="s">
-        <v>597</v>
-      </c>
-      <c r="C79" t="s">
-        <v>38</v>
-      </c>
-      <c r="D79" t="s">
-        <v>38</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>601</v>
       </c>
       <c r="F79" t="s">
         <v>38</v>
@@ -9404,7 +9425,7 @@
         <v>38</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="M79" s="3" t="s">
         <v>38</v>
@@ -9428,30 +9449,30 @@
         <v>30</v>
       </c>
       <c r="U79" s="28" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V79" s="3" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="80" spans="1:22" ht="165" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>563</v>
+      </c>
+      <c r="B80" t="s">
+        <v>639</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>772</v>
+      </c>
+      <c r="D80" t="s">
+        <v>38</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="F80" t="s">
         <v>564</v>
-      </c>
-      <c r="B80" t="s">
-        <v>640</v>
-      </c>
-      <c r="C80" s="11" t="s">
-        <v>774</v>
-      </c>
-      <c r="D80" t="s">
-        <v>38</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="F80" t="s">
-        <v>565</v>
       </c>
       <c r="G80" t="s">
         <v>7</v>
@@ -9463,10 +9484,10 @@
         <v>2023</v>
       </c>
       <c r="K80" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="N80" s="10"/>
       <c r="O80" s="30" t="s">
@@ -9485,18 +9506,18 @@
         <v>29</v>
       </c>
       <c r="U80" s="28" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="V80" s="3" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="81" spans="1:22" ht="255" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C81" s="15" t="s">
         <v>38</v>
@@ -9505,7 +9526,7 @@
         <v>38</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F81" t="s">
         <v>38</v>
@@ -9520,10 +9541,10 @@
         <v>2020</v>
       </c>
       <c r="K81" t="s">
+        <v>490</v>
+      </c>
+      <c r="L81" s="3" t="s">
         <v>491</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>492</v>
       </c>
       <c r="M81" s="3" t="s">
         <v>38</v>
@@ -9548,18 +9569,18 @@
       </c>
       <c r="T81" s="30"/>
       <c r="U81" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V81" s="3" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="82" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B82" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>38</v>
@@ -9568,7 +9589,7 @@
         <v>38</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F82" t="s">
         <v>38</v>
@@ -9586,13 +9607,13 @@
         <v>38</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="O82" s="30" t="s">
         <v>29</v>
@@ -9610,27 +9631,27 @@
         <v>30</v>
       </c>
       <c r="U82" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V82" s="3" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="83" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>732</v>
+      </c>
+      <c r="B83" t="s">
         <v>733</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="D83" t="s">
+        <v>38</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>735</v>
-      </c>
-      <c r="D83" t="s">
-        <v>38</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>736</v>
       </c>
       <c r="G83" t="s">
         <v>0</v>
@@ -9648,14 +9669,14 @@
         <v>35</v>
       </c>
       <c r="L83" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="M83" s="3" t="s">
         <v>737</v>
       </c>
-      <c r="M83" s="3" t="s">
+      <c r="N83" s="3" t="s">
         <v>738</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>739</v>
-      </c>
       <c r="O83" s="30" t="s">
         <v>29</v>
       </c>
@@ -9672,10 +9693,10 @@
         <v>29</v>
       </c>
       <c r="U83" s="30" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V83" s="32" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="84" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -9713,13 +9734,13 @@
         <v>23</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="M84" s="3" t="s">
         <v>271</v>
       </c>
       <c r="N84" s="3" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="O84" s="30" t="s">
         <v>30</v>
@@ -9740,10 +9761,10 @@
         <v>0</v>
       </c>
       <c r="U84" s="28" t="s">
+        <v>866</v>
+      </c>
+      <c r="V84" s="3" t="s">
         <v>868</v>
-      </c>
-      <c r="V84" s="3" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="85" spans="1:22" ht="150" x14ac:dyDescent="0.25">
@@ -9778,13 +9799,13 @@
         <v>23</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="O85" s="30" t="s">
         <v>29</v>
@@ -9802,10 +9823,10 @@
         <v>30</v>
       </c>
       <c r="U85" s="28" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="V85" s="3" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="86" spans="1:22" s="15" customFormat="1" ht="105" x14ac:dyDescent="0.25">
@@ -9813,10 +9834,10 @@
         <v>277</v>
       </c>
       <c r="B86" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D86" t="s">
         <v>38</v>
@@ -9843,7 +9864,7 @@
         <v>242</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="M86" s="3" t="s">
         <v>38</v>
@@ -9868,27 +9889,27 @@
       </c>
       <c r="T86" s="37"/>
       <c r="U86" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V86" s="3" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="87" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C87" s="25" t="s">
         <v>1107</v>
       </c>
-      <c r="B87" t="s">
+      <c r="D87" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>1108</v>
-      </c>
-      <c r="C87" s="25" t="s">
-        <v>1109</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>1110</v>
       </c>
       <c r="F87" s="27" t="s">
         <v>38</v>
@@ -9909,7 +9930,7 @@
         <v>128</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="N87" s="13"/>
       <c r="S87" s="31"/>
@@ -9925,7 +9946,7 @@
         <v>281</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="D88" t="s">
         <v>38</v>
@@ -9949,13 +9970,13 @@
         <v>35</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="M88" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N88" s="3" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="O88" s="30" t="s">
         <v>29</v>
@@ -9973,10 +9994,10 @@
         <v>30</v>
       </c>
       <c r="U88" s="28" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="V88" s="3" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="89" spans="1:22" ht="75" x14ac:dyDescent="0.25">
@@ -10011,13 +10032,13 @@
         <v>23</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N89" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="O89" s="30" t="s">
         <v>29</v>
@@ -10038,10 +10059,10 @@
         <v>15</v>
       </c>
       <c r="U89" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V89" s="3" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="90" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -10052,7 +10073,7 @@
         <v>213</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D90" t="s">
         <v>38</v>
@@ -10076,13 +10097,13 @@
         <v>225</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="M90" s="3" t="s">
         <v>289</v>
       </c>
       <c r="N90" s="3" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O90" s="30" t="s">
         <v>29</v>
@@ -10100,10 +10121,10 @@
         <v>30</v>
       </c>
       <c r="U90" s="28" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="V90" s="3" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="91" spans="1:22" ht="165" x14ac:dyDescent="0.25">
@@ -10144,7 +10165,7 @@
         <v>295</v>
       </c>
       <c r="N91" s="3" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="O91" s="30" t="s">
         <v>29</v>
@@ -10162,10 +10183,10 @@
         <v>29</v>
       </c>
       <c r="U91" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V91" s="3" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
     </row>
     <row r="92" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -10176,7 +10197,7 @@
         <v>297</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="D92" t="s">
         <v>38</v>
@@ -10194,13 +10215,13 @@
         <v>38</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="M92" s="3" t="s">
         <v>299</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="O92" s="30" t="s">
         <v>29</v>
@@ -10218,27 +10239,27 @@
         <v>29</v>
       </c>
       <c r="U92" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V92" s="3" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="93" spans="1:22" ht="75" x14ac:dyDescent="0.25">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" ht="165" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>497</v>
+      </c>
+      <c r="B93" t="s">
         <v>498</v>
       </c>
-      <c r="B93" t="s">
-        <v>499</v>
-      </c>
       <c r="C93" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D93" t="s">
         <v>38</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F93" t="s">
         <v>38</v>
@@ -10253,18 +10274,18 @@
         <v>2016</v>
       </c>
       <c r="K93" t="s">
+        <v>556</v>
+      </c>
+      <c r="L93" s="3" t="s">
         <v>557</v>
-      </c>
-      <c r="L93" s="3" t="s">
-        <v>558</v>
       </c>
       <c r="N93" s="10"/>
       <c r="S93" s="31"/>
       <c r="U93" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V93" s="3" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
     </row>
     <row r="94" spans="1:22" ht="135" x14ac:dyDescent="0.25">
@@ -10305,7 +10326,7 @@
         <v>304</v>
       </c>
       <c r="N94" s="3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="O94" s="30" t="s">
         <v>29</v>
@@ -10323,10 +10344,10 @@
         <v>29</v>
       </c>
       <c r="U94" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V94" s="3" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="95" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -10364,13 +10385,13 @@
         <v>57</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="M95" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N95" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="O95" s="30" t="s">
         <v>30</v>
@@ -10388,10 +10409,10 @@
         <v>30</v>
       </c>
       <c r="U95" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V95" s="3" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
     </row>
     <row r="96" spans="1:22" ht="75" x14ac:dyDescent="0.25">
@@ -10426,13 +10447,13 @@
         <v>23</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="M96" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N96" s="3" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="O96" s="30" t="s">
         <v>29</v>
@@ -10450,10 +10471,10 @@
         <v>29</v>
       </c>
       <c r="U96" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V96" s="3" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="97" spans="1:26" ht="90" x14ac:dyDescent="0.25">
@@ -10512,10 +10533,10 @@
         <v>30</v>
       </c>
       <c r="U97" s="28" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V97" s="3" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="98" spans="1:26" ht="105" x14ac:dyDescent="0.25">
@@ -10556,7 +10577,7 @@
         <v>38</v>
       </c>
       <c r="N98" s="3" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="O98" s="30" t="s">
         <v>29</v>
@@ -10574,10 +10595,10 @@
         <v>30</v>
       </c>
       <c r="U98" s="28" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V98" s="3" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="99" spans="1:26" ht="105" x14ac:dyDescent="0.25">
@@ -10588,7 +10609,7 @@
         <v>324</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="D99" t="s">
         <v>38</v>
@@ -10615,10 +10636,10 @@
         <v>325</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N99" s="3" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="O99" s="30" t="s">
         <v>29</v>
@@ -10636,27 +10657,27 @@
         <v>30</v>
       </c>
       <c r="U99" s="28" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="V99" s="3" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="100" spans="1:26" ht="105" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>1047</v>
       </c>
-      <c r="B100" t="s">
+      <c r="D100" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>1048</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>1050</v>
       </c>
       <c r="F100" t="s">
         <v>38</v>
@@ -10669,13 +10690,13 @@
         <v>2025</v>
       </c>
       <c r="K100" t="s">
+        <v>1049</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="M100" t="s">
         <v>1051</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>1052</v>
-      </c>
-      <c r="M100" t="s">
-        <v>1053</v>
       </c>
       <c r="N100" s="13" t="s">
         <v>38</v>
@@ -10753,30 +10774,30 @@
         <v>30</v>
       </c>
       <c r="U101" s="28" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V101" s="3" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="102" spans="1:26" ht="90" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>535</v>
+      </c>
+      <c r="B102" t="s">
         <v>536</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="D102" t="s">
+        <v>542</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D102" t="s">
-        <v>543</v>
-      </c>
-      <c r="E102" s="1" t="s">
+      <c r="F102" t="s">
         <v>539</v>
-      </c>
-      <c r="F102" t="s">
-        <v>540</v>
       </c>
       <c r="G102" t="s">
         <v>19</v>
@@ -10794,13 +10815,13 @@
         <v>38</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N102" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="O102" s="30" t="s">
         <v>29</v>
@@ -10818,13 +10839,13 @@
         <v>29</v>
       </c>
       <c r="U102" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V102" s="3" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="103" spans="1:26" ht="90" x14ac:dyDescent="0.25">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="103" spans="1:26" ht="105" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>332</v>
       </c>
@@ -10832,13 +10853,13 @@
         <v>333</v>
       </c>
       <c r="C103" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D103" t="s">
+        <v>38</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="D103" t="s">
-        <v>38</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>335</v>
       </c>
       <c r="F103" t="s">
         <v>38</v>
@@ -10856,13 +10877,13 @@
         <v>38</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="M103" s="3" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="N103" s="3" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="O103" s="30" t="s">
         <v>29</v>
@@ -10880,27 +10901,27 @@
         <v>30</v>
       </c>
       <c r="U103" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V103" s="3" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="104" spans="1:26" ht="120" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="B104" t="s">
         <v>521</v>
       </c>
-      <c r="B104" t="s">
-        <v>522</v>
-      </c>
       <c r="C104" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="D104" t="s">
+        <v>38</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>524</v>
-      </c>
-      <c r="D104" t="s">
-        <v>38</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>525</v>
       </c>
       <c r="F104" t="s">
         <v>38</v>
@@ -10918,13 +10939,13 @@
         <v>35</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="M104" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="N104" s="3" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="O104" s="30" t="s">
         <v>29</v>
@@ -10942,27 +10963,27 @@
         <v>29</v>
       </c>
       <c r="U104" s="28" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="V104" s="3" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="105" spans="1:26" ht="165" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>335</v>
+      </c>
+      <c r="B105" t="s">
         <v>336</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C105" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="D105" t="s">
+        <v>38</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="D105" t="s">
-        <v>38</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>339</v>
       </c>
       <c r="F105" t="s">
         <v>38</v>
@@ -10980,13 +11001,13 @@
         <v>23</v>
       </c>
       <c r="L105" s="3" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="M105" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N105" s="3" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="O105" s="30" t="s">
         <v>29</v>
@@ -11004,27 +11025,27 @@
         <v>29</v>
       </c>
       <c r="U105" s="28" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="V105" s="3" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="106" spans="1:26" ht="75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B106" t="s">
         <v>265</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="D106" t="s">
         <v>38</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F106" t="s">
         <v>38</v>
@@ -11042,13 +11063,13 @@
         <v>23</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="M106" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N106" s="3" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="O106" s="30" t="s">
         <v>29</v>
@@ -11066,19 +11087,19 @@
         <v>29</v>
       </c>
       <c r="U106" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V106" s="3" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="107" spans="1:26" ht="105" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>343</v>
+      </c>
+      <c r="B107" t="s">
         <v>344</v>
       </c>
-      <c r="B107" t="s">
-        <v>345</v>
-      </c>
       <c r="C107" t="s">
         <v>38</v>
       </c>
@@ -11086,16 +11107,16 @@
         <v>38</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F107" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G107" t="s">
         <v>10</v>
       </c>
       <c r="I107" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J107">
         <v>2019</v>
@@ -11104,7 +11125,7 @@
         <v>38</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="M107" s="3" t="s">
         <v>38</v>
@@ -11128,180 +11149,167 @@
         <v>30</v>
       </c>
       <c r="U107" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V107" s="3" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
     </row>
     <row r="108" spans="1:26" ht="90" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>349</v>
+        <v>1171</v>
       </c>
       <c r="B108" t="s">
-        <v>350</v>
-      </c>
-      <c r="C108" t="s">
-        <v>38</v>
-      </c>
-      <c r="D108" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C108" s="25" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D108" s="6" t="s">
         <v>38</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F108" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F108" s="27" t="s">
         <v>38</v>
       </c>
       <c r="G108" t="s">
-        <v>7</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H108" s="1"/>
       <c r="I108" s="9" t="s">
-        <v>351</v>
+        <v>38</v>
       </c>
       <c r="J108">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="K108" t="s">
-        <v>38</v>
+        <v>1175</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>1022</v>
+        <v>1176</v>
       </c>
       <c r="M108" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N108" s="3" t="s">
+        <v>1177</v>
+      </c>
+      <c r="N108" s="13" t="s">
         <v>38</v>
       </c>
       <c r="O108" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="P108" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q108" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R108" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="S108" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="U108" s="28" t="s">
-        <v>885</v>
-      </c>
-      <c r="V108" s="3" t="s">
-        <v>901</v>
-      </c>
+      <c r="S108" s="31"/>
+      <c r="T108" s="30"/>
+      <c r="U108" s="30"/>
+      <c r="V108" s="32"/>
     </row>
     <row r="109" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>348</v>
+      </c>
+      <c r="B109" t="s">
+        <v>349</v>
+      </c>
+      <c r="C109" t="s">
+        <v>38</v>
+      </c>
+      <c r="D109" t="s">
+        <v>38</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="F109" t="s">
+        <v>38</v>
+      </c>
+      <c r="G109" t="s">
+        <v>7</v>
+      </c>
+      <c r="I109" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="J109">
+        <v>2020</v>
+      </c>
+      <c r="K109" t="s">
+        <v>38</v>
+      </c>
+      <c r="L109" s="3" t="s">
+        <v>1020</v>
+      </c>
+      <c r="M109" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N109" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O109" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="P109" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q109" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="R109" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="S109" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="U109" s="28" t="s">
+        <v>883</v>
+      </c>
+      <c r="V109" s="3" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="110" spans="1:26" ht="90" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>352</v>
+      </c>
+      <c r="B110" t="s">
         <v>353</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C110" t="s">
+        <v>38</v>
+      </c>
+      <c r="D110" t="s">
+        <v>38</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C109" t="s">
-        <v>38</v>
-      </c>
-      <c r="D109" t="s">
-        <v>38</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="F109" t="s">
-        <v>38</v>
-      </c>
-      <c r="G109" t="s">
+      <c r="F110" t="s">
+        <v>38</v>
+      </c>
+      <c r="G110" t="s">
         <v>12</v>
       </c>
-      <c r="I109" s="9">
+      <c r="I110" s="9">
         <v>5</v>
       </c>
-      <c r="J109">
+      <c r="J110">
         <v>2005</v>
       </c>
-      <c r="K109" t="s">
-        <v>38</v>
-      </c>
-      <c r="L109" s="3" t="s">
-        <v>826</v>
-      </c>
-      <c r="M109" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N109" s="3" t="s">
+      <c r="K110" t="s">
+        <v>38</v>
+      </c>
+      <c r="L110" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="M110" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N110" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="O109" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P109" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q109" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R109" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="S109" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="U109" s="28" t="s">
-        <v>881</v>
-      </c>
-      <c r="V109" s="3" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="110" spans="1:26" ht="135" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>356</v>
-      </c>
-      <c r="B110" t="s">
-        <v>357</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D110" t="s">
-        <v>32</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F110" t="s">
-        <v>38</v>
-      </c>
-      <c r="G110" t="s">
-        <v>3</v>
-      </c>
-      <c r="I110" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="J110">
-        <v>2020</v>
-      </c>
-      <c r="K110" t="s">
-        <v>23</v>
-      </c>
-      <c r="L110" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="M110" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="N110" s="3" t="s">
-        <v>690</v>
-      </c>
       <c r="O110" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="P110" s="30" t="s">
+      <c r="P110" s="35" t="s">
         <v>29</v>
       </c>
       <c r="Q110" s="30" t="s">
@@ -11314,51 +11322,51 @@
         <v>30</v>
       </c>
       <c r="U110" s="28" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="V110" s="3" t="s">
-        <v>882</v>
+        <v>954</v>
       </c>
     </row>
     <row r="111" spans="1:26" ht="90" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B111" t="s">
-        <v>299</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>363</v>
+        <v>356</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="D111" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>363</v>
+        <v>26</v>
       </c>
       <c r="F111" t="s">
         <v>38</v>
       </c>
       <c r="G111" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I111" s="9" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="J111">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="K111" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="M111" s="3" t="s">
-        <v>90</v>
+        <v>359</v>
       </c>
       <c r="N111" s="3" t="s">
-        <v>364</v>
+        <v>689</v>
       </c>
       <c r="O111" s="30" t="s">
         <v>29</v>
@@ -11373,56 +11381,55 @@
         <v>29</v>
       </c>
       <c r="S111" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U111" s="28" t="s">
-        <v>863</v>
+        <v>879</v>
       </c>
       <c r="V111" s="3" t="s">
-        <v>971</v>
+        <v>880</v>
       </c>
       <c r="Z111" s="3"/>
     </row>
     <row r="112" spans="1:26" ht="90" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>794</v>
+        <v>360</v>
       </c>
       <c r="B112" t="s">
-        <v>795</v>
-      </c>
-      <c r="C112" s="25" t="s">
-        <v>796</v>
-      </c>
-      <c r="D112" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D112" t="s">
         <v>38</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>797</v>
+        <v>362</v>
       </c>
       <c r="F112" t="s">
         <v>38</v>
       </c>
-      <c r="G112" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="H112" s="1"/>
+      <c r="G112" t="s">
+        <v>5</v>
+      </c>
       <c r="I112" s="9" t="s">
-        <v>798</v>
+        <v>38</v>
       </c>
       <c r="J112">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="K112" t="s">
-        <v>799</v>
+        <v>82</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>800</v>
+        <v>361</v>
       </c>
       <c r="M112" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N112" s="13" t="s">
-        <v>38</v>
+        <v>90</v>
+      </c>
+      <c r="N112" s="3" t="s">
+        <v>363</v>
       </c>
       <c r="O112" s="30" t="s">
         <v>29</v>
@@ -11439,53 +11446,53 @@
       <c r="S112" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="T112" s="30"/>
-      <c r="U112" s="30" t="s">
-        <v>892</v>
-      </c>
-      <c r="V112" s="32" t="s">
-        <v>862</v>
+      <c r="U112" s="28" t="s">
+        <v>861</v>
+      </c>
+      <c r="V112" s="3" t="s">
+        <v>969</v>
       </c>
     </row>
     <row r="113" spans="1:22" ht="150" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>365</v>
+        <v>792</v>
       </c>
       <c r="B113" t="s">
-        <v>366</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="D113" t="s">
-        <v>118</v>
+        <v>793</v>
+      </c>
+      <c r="C113" s="25" t="s">
+        <v>794</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>38</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>368</v>
+        <v>795</v>
       </c>
       <c r="F113" t="s">
         <v>38</v>
       </c>
-      <c r="G113" t="s">
-        <v>14</v>
-      </c>
+      <c r="G113" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H113" s="1"/>
       <c r="I113" s="9" t="s">
-        <v>367</v>
+        <v>796</v>
       </c>
       <c r="J113">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="K113" t="s">
-        <v>23</v>
+        <v>797</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>1024</v>
+        <v>798</v>
       </c>
       <c r="M113" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="N113" s="3" t="s">
-        <v>691</v>
+        <v>38</v>
+      </c>
+      <c r="N113" s="13" t="s">
+        <v>38</v>
       </c>
       <c r="O113" s="30" t="s">
         <v>29</v>
@@ -11502,37 +11509,38 @@
       <c r="S113" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="U113" s="28" t="s">
-        <v>861</v>
-      </c>
-      <c r="V113" s="3" t="s">
-        <v>904</v>
+      <c r="T113" s="30"/>
+      <c r="U113" s="30" t="s">
+        <v>890</v>
+      </c>
+      <c r="V113" s="32" t="s">
+        <v>860</v>
       </c>
     </row>
     <row r="114" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="B114" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="D114" t="s">
         <v>118</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="F114" t="s">
         <v>38</v>
       </c>
       <c r="G114" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I114" s="9" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="J114">
         <v>2022</v>
@@ -11541,13 +11549,13 @@
         <v>23</v>
       </c>
       <c r="L114" s="3" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="M114" s="3" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="N114" s="3" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="O114" s="30" t="s">
         <v>29</v>
@@ -11562,156 +11570,159 @@
         <v>29</v>
       </c>
       <c r="S114" s="31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U114" s="28" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="V114" s="3" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="115" spans="1:22" ht="285" x14ac:dyDescent="0.25">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="115" spans="1:22" ht="150" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1042</v>
+        <v>369</v>
       </c>
       <c r="B115" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C115" s="39" t="s">
-        <v>1044</v>
-      </c>
-      <c r="D115" s="6" t="s">
-        <v>38</v>
+        <v>370</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D115" t="s">
+        <v>118</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>1044</v>
-      </c>
-      <c r="F115" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="G115" s="27" t="s">
+        <v>372</v>
+      </c>
+      <c r="F115" t="s">
+        <v>38</v>
+      </c>
+      <c r="G115" t="s">
         <v>15</v>
       </c>
-      <c r="H115" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="I115" s="9">
-        <v>0.5</v>
+      <c r="I115" s="9" t="s">
+        <v>371</v>
       </c>
       <c r="J115">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="K115" t="s">
-        <v>128</v>
+        <v>23</v>
       </c>
       <c r="L115" s="3" t="s">
-        <v>1045</v>
-      </c>
-      <c r="N115" s="10"/>
-      <c r="S115" s="31"/>
-      <c r="T115" s="30"/>
-      <c r="U115" s="30"/>
-      <c r="V115" s="32"/>
+        <v>1023</v>
+      </c>
+      <c r="M115" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="N115" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="O115" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="P115" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q115" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R115" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S115" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="U115" s="28" t="s">
+        <v>859</v>
+      </c>
+      <c r="V115" s="3" t="s">
+        <v>903</v>
+      </c>
     </row>
     <row r="116" spans="1:22" ht="195" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>375</v>
+        <v>1040</v>
       </c>
       <c r="B116" t="s">
-        <v>376</v>
-      </c>
-      <c r="C116" t="s">
-        <v>38</v>
-      </c>
-      <c r="D116" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C116" s="39" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D116" s="6" t="s">
         <v>38</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="F116" t="s">
-        <v>38</v>
-      </c>
-      <c r="G116" t="s">
-        <v>594</v>
+        <v>1042</v>
+      </c>
+      <c r="F116" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="G116" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H116" s="27" t="s">
+        <v>17</v>
       </c>
       <c r="I116" s="9">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J116">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="K116" t="s">
-        <v>377</v>
+        <v>128</v>
       </c>
       <c r="L116" s="3" t="s">
-        <v>837</v>
-      </c>
-      <c r="M116" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="N116" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="O116" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P116" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q116" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R116" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="S116" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="U116" s="28" t="s">
-        <v>863</v>
-      </c>
-      <c r="V116" s="3" t="s">
-        <v>975</v>
-      </c>
+        <v>1043</v>
+      </c>
+      <c r="N116" s="10"/>
+      <c r="S116" s="31"/>
+      <c r="T116" s="30"/>
+      <c r="U116" s="30"/>
+      <c r="V116" s="32"/>
     </row>
     <row r="117" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>583</v>
+        <v>374</v>
       </c>
       <c r="B117" t="s">
-        <v>584</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>586</v>
+        <v>375</v>
+      </c>
+      <c r="C117" t="s">
+        <v>38</v>
+      </c>
+      <c r="D117" t="s">
+        <v>38</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>587</v>
+        <v>377</v>
       </c>
       <c r="F117" t="s">
         <v>38</v>
       </c>
       <c r="G117" t="s">
-        <v>8</v>
-      </c>
-      <c r="I117" s="9" t="s">
-        <v>230</v>
+        <v>593</v>
+      </c>
+      <c r="I117" s="9">
+        <v>4</v>
       </c>
       <c r="J117">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="K117" t="s">
-        <v>128</v>
+        <v>376</v>
       </c>
       <c r="L117" s="3" t="s">
-        <v>585</v>
+        <v>835</v>
       </c>
       <c r="M117" s="3" t="s">
-        <v>38</v>
+        <v>378</v>
       </c>
       <c r="N117" s="3" t="s">
-        <v>693</v>
+        <v>379</v>
       </c>
       <c r="O117" s="30" t="s">
         <v>29</v>
@@ -11723,57 +11734,54 @@
         <v>29</v>
       </c>
       <c r="R117" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S117" s="31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U117" s="28" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="V117" s="3" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
     </row>
     <row r="118" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>381</v>
-      </c>
-      <c r="B118" s="15" t="s">
-        <v>382</v>
-      </c>
-      <c r="C118" t="s">
-        <v>38</v>
-      </c>
-      <c r="D118" t="s">
-        <v>38</v>
+        <v>582</v>
+      </c>
+      <c r="B118" t="s">
+        <v>583</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>585</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>58</v>
+        <v>586</v>
       </c>
       <c r="F118" t="s">
         <v>38</v>
       </c>
       <c r="G118" t="s">
-        <v>4</v>
-      </c>
-      <c r="I118" s="9">
-        <v>1.1000000000000001</v>
+        <v>8</v>
+      </c>
+      <c r="I118" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="J118">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="K118" t="s">
-        <v>57</v>
+        <v>128</v>
       </c>
       <c r="L118" s="3" t="s">
-        <v>838</v>
+        <v>584</v>
       </c>
       <c r="M118" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="N118" s="13" t="s">
-        <v>38</v>
+      <c r="N118" s="3" t="s">
+        <v>692</v>
       </c>
       <c r="O118" s="30" t="s">
         <v>29</v>
@@ -11782,60 +11790,60 @@
         <v>29</v>
       </c>
       <c r="Q118" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R118" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S118" s="31" t="s">
         <v>30</v>
       </c>
       <c r="U118" s="28" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="V118" s="3" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
     </row>
     <row r="119" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>383</v>
-      </c>
-      <c r="B119" t="s">
-        <v>384</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>386</v>
+        <v>380</v>
+      </c>
+      <c r="B119" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="C119" t="s">
+        <v>38</v>
       </c>
       <c r="D119" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="F119" t="s">
         <v>38</v>
       </c>
       <c r="G119" t="s">
-        <v>14</v>
-      </c>
-      <c r="I119" s="9" t="s">
-        <v>385</v>
+        <v>4</v>
+      </c>
+      <c r="I119" s="9">
+        <v>1.1000000000000001</v>
       </c>
       <c r="J119">
         <v>2020</v>
       </c>
       <c r="K119" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="L119" s="3" t="s">
-        <v>1015</v>
+        <v>836</v>
       </c>
       <c r="M119" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="N119" s="3" t="s">
-        <v>388</v>
+        <v>38</v>
+      </c>
+      <c r="N119" s="13" t="s">
+        <v>38</v>
       </c>
       <c r="O119" s="30" t="s">
         <v>29</v>
@@ -11844,10 +11852,10 @@
         <v>29</v>
       </c>
       <c r="Q119" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R119" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S119" s="31" t="s">
         <v>30</v>
@@ -11856,48 +11864,48 @@
         <v>861</v>
       </c>
       <c r="V119" s="3" t="s">
-        <v>883</v>
+        <v>975</v>
       </c>
     </row>
     <row r="120" spans="1:22" ht="165" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="B120" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="D120" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>392</v>
+        <v>26</v>
       </c>
       <c r="F120" t="s">
         <v>38</v>
       </c>
       <c r="G120" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I120" s="9" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="J120">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="K120" t="s">
         <v>23</v>
       </c>
       <c r="L120" s="3" t="s">
-        <v>1026</v>
+        <v>1013</v>
       </c>
       <c r="M120" s="3" t="s">
-        <v>1138</v>
+        <v>386</v>
       </c>
       <c r="N120" s="3" t="s">
-        <v>691</v>
+        <v>387</v>
       </c>
       <c r="O120" s="30" t="s">
         <v>29</v>
@@ -11912,39 +11920,39 @@
         <v>29</v>
       </c>
       <c r="S120" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U120" s="28" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="V120" s="3" t="s">
-        <v>906</v>
+        <v>881</v>
       </c>
     </row>
     <row r="121" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>409</v>
+        <v>388</v>
       </c>
       <c r="B121" t="s">
-        <v>410</v>
+        <v>389</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
       <c r="D121" t="s">
         <v>118</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
       <c r="F121" t="s">
         <v>38</v>
       </c>
       <c r="G121" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I121" s="9" t="s">
-        <v>411</v>
+        <v>390</v>
       </c>
       <c r="J121">
         <v>2022</v>
@@ -11953,13 +11961,13 @@
         <v>23</v>
       </c>
       <c r="L121" s="3" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="M121" s="3" t="s">
-        <v>413</v>
+        <v>1136</v>
       </c>
       <c r="N121" s="3" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="O121" s="30" t="s">
         <v>29</v>
@@ -11974,55 +11982,55 @@
         <v>29</v>
       </c>
       <c r="S121" s="31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U121" s="28" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="V121" s="3" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
     </row>
     <row r="122" spans="1:22" s="15" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="B122" t="s">
-        <v>415</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>769</v>
+        <v>409</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>411</v>
       </c>
       <c r="D122" t="s">
-        <v>38</v>
+        <v>118</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="F122" t="s">
         <v>38</v>
       </c>
       <c r="G122" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H122"/>
       <c r="I122" s="9" t="s">
-        <v>38</v>
+        <v>410</v>
       </c>
       <c r="J122">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="K122" t="s">
-        <v>242</v>
+        <v>23</v>
       </c>
       <c r="L122" s="3" t="s">
-        <v>416</v>
+        <v>1025</v>
       </c>
       <c r="M122" s="3" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="N122" s="3" t="s">
-        <v>419</v>
+        <v>696</v>
       </c>
       <c r="O122" s="30" t="s">
         <v>29</v>
@@ -12034,34 +12042,34 @@
         <v>29</v>
       </c>
       <c r="R122" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S122" s="31" t="s">
         <v>30</v>
       </c>
       <c r="T122" s="28"/>
       <c r="U122" s="28" t="s">
-        <v>885</v>
+        <v>859</v>
       </c>
       <c r="V122" s="3" t="s">
-        <v>998</v>
+        <v>905</v>
       </c>
     </row>
     <row r="123" spans="1:22" ht="150" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="B123" t="s">
-        <v>395</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>422</v>
+        <v>414</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>767</v>
       </c>
       <c r="D123" t="s">
-        <v>396</v>
+        <v>38</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="F123" t="s">
         <v>38</v>
@@ -12070,123 +12078,122 @@
         <v>10</v>
       </c>
       <c r="I123" s="9" t="s">
-        <v>613</v>
+        <v>38</v>
       </c>
       <c r="J123">
+        <v>2016</v>
+      </c>
+      <c r="K123" t="s">
+        <v>242</v>
+      </c>
+      <c r="L123" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="M123" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="N123" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="O123" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="P123" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q123" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R123" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="S123" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="U123" s="28" t="s">
+        <v>883</v>
+      </c>
+      <c r="V123" s="3" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="124" spans="1:22" ht="285" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>419</v>
+      </c>
+      <c r="B124" t="s">
+        <v>394</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D124" t="s">
+        <v>395</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="F124" t="s">
+        <v>38</v>
+      </c>
+      <c r="G124" t="s">
+        <v>10</v>
+      </c>
+      <c r="I124" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="J124">
         <v>2024</v>
       </c>
-      <c r="K123" t="s">
+      <c r="K124" t="s">
         <v>95</v>
       </c>
-      <c r="L123" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="M123" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="N123" s="3" t="s">
-        <v>698</v>
-      </c>
-      <c r="O123" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P123" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q123" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R123" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="S123" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="U123" s="28" t="s">
-        <v>863</v>
-      </c>
-      <c r="V123" s="3" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="124" spans="1:22" ht="285" x14ac:dyDescent="0.25">
-      <c r="A124" s="15" t="s">
-        <v>615</v>
-      </c>
-      <c r="B124" s="15" t="s">
-        <v>741</v>
-      </c>
-      <c r="C124" s="17" t="s">
-        <v>616</v>
-      </c>
-      <c r="D124" s="18" t="s">
-        <v>396</v>
-      </c>
-      <c r="E124" s="17" t="s">
-        <v>616</v>
-      </c>
-      <c r="F124" t="s">
-        <v>38</v>
-      </c>
-      <c r="G124" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H124" s="15"/>
-      <c r="I124" s="19" t="s">
-        <v>605</v>
-      </c>
-      <c r="J124" s="15">
-        <v>2025</v>
-      </c>
-      <c r="K124" s="15" t="s">
-        <v>95</v>
-      </c>
       <c r="L124" s="3" t="s">
-        <v>847</v>
-      </c>
-      <c r="M124" s="13" t="s">
-        <v>1140</v>
-      </c>
-      <c r="N124" s="13" t="s">
-        <v>1139</v>
-      </c>
-      <c r="O124" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="P124" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q124" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="R124" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="S124" s="36" t="s">
-        <v>30</v>
+        <v>420</v>
+      </c>
+      <c r="M124" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="N124" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="O124" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="P124" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q124" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R124" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S124" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="U124" s="28" t="s">
         <v>861</v>
       </c>
       <c r="V124" s="3" t="s">
-        <v>988</v>
+        <v>981</v>
       </c>
     </row>
     <row r="125" spans="1:22" s="15" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A125" s="15" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C125" s="17" t="s">
-        <v>754</v>
+        <v>615</v>
       </c>
       <c r="D125" s="18" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E125" s="17" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="F125" t="s">
         <v>38</v>
@@ -12194,11 +12201,8 @@
       <c r="G125" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H125" s="15" t="s">
-        <v>591</v>
-      </c>
       <c r="I125" s="19" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="J125" s="15">
         <v>2025</v>
@@ -12207,13 +12211,13 @@
         <v>95</v>
       </c>
       <c r="L125" s="3" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="M125" s="13" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="N125" s="13" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="O125" s="36" t="s">
         <v>29</v>
@@ -12232,104 +12236,104 @@
       </c>
       <c r="T125" s="28"/>
       <c r="U125" s="28" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="V125" s="3" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
     </row>
     <row r="126" spans="1:22" ht="285" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>606</v>
-      </c>
-      <c r="B126" t="s">
-        <v>743</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>1171</v>
-      </c>
-      <c r="D126" t="s">
-        <v>396</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>394</v>
+      <c r="A126" s="15" t="s">
+        <v>616</v>
+      </c>
+      <c r="B126" s="15" t="s">
+        <v>741</v>
+      </c>
+      <c r="C126" s="17" t="s">
+        <v>753</v>
+      </c>
+      <c r="D126" s="18" t="s">
+        <v>395</v>
+      </c>
+      <c r="E126" s="17" t="s">
+        <v>617</v>
       </c>
       <c r="F126" t="s">
+        <v>38</v>
+      </c>
+      <c r="G126" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H126" s="15" t="s">
+        <v>590</v>
+      </c>
+      <c r="I126" s="19" t="s">
+        <v>604</v>
+      </c>
+      <c r="J126" s="15">
+        <v>2025</v>
+      </c>
+      <c r="K126" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="L126" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="M126" s="13" t="s">
+        <v>1140</v>
+      </c>
+      <c r="N126" s="13" t="s">
+        <v>1139</v>
+      </c>
+      <c r="O126" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="P126" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q126" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="R126" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="S126" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="U126" s="28" t="s">
+        <v>864</v>
+      </c>
+      <c r="V126" s="3" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="127" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>605</v>
+      </c>
+      <c r="B127" t="s">
+        <v>742</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D127" t="s">
+        <v>395</v>
+      </c>
+      <c r="E127" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="G126" t="s">
-        <v>10</v>
-      </c>
-      <c r="H126" t="s">
-        <v>0</v>
-      </c>
-      <c r="I126" s="9" t="s">
-        <v>605</v>
-      </c>
-      <c r="J126">
-        <v>2025</v>
-      </c>
-      <c r="K126" t="s">
-        <v>95</v>
-      </c>
-      <c r="L126" s="3" t="s">
-        <v>842</v>
-      </c>
-      <c r="M126" s="3" t="s">
-        <v>1144</v>
-      </c>
-      <c r="N126" s="3" t="s">
-        <v>1143</v>
-      </c>
-      <c r="O126" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P126" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q126" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R126" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="S126" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="U126" s="28" t="s">
-        <v>863</v>
-      </c>
-      <c r="V126" s="3" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="127" spans="1:22" ht="135" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>608</v>
-      </c>
-      <c r="B127" t="s">
-        <v>744</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="D127" t="s">
-        <v>396</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="F127" t="s">
-        <v>38</v>
+        <v>392</v>
       </c>
       <c r="G127" t="s">
         <v>10</v>
       </c>
       <c r="H127" t="s">
-        <v>236</v>
+        <v>0</v>
       </c>
       <c r="I127" s="9" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="J127">
         <v>2025</v>
@@ -12338,13 +12342,13 @@
         <v>95</v>
       </c>
       <c r="L127" s="3" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="M127" s="3" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="N127" s="3" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="O127" s="30" t="s">
         <v>29</v>
@@ -12362,156 +12366,156 @@
         <v>29</v>
       </c>
       <c r="U127" s="28" t="s">
-        <v>885</v>
+        <v>861</v>
       </c>
       <c r="V127" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="128" spans="1:22" s="15" customFormat="1" ht="120" x14ac:dyDescent="0.25">
-      <c r="A128" s="15" t="s">
-        <v>619</v>
-      </c>
-      <c r="B128" s="15" t="s">
-        <v>745</v>
-      </c>
-      <c r="C128" s="17" t="s">
-        <v>756</v>
-      </c>
-      <c r="D128" s="18" t="s">
-        <v>396</v>
-      </c>
-      <c r="E128" s="17" t="s">
-        <v>620</v>
+        <v>980</v>
+      </c>
+    </row>
+    <row r="128" spans="1:22" s="15" customFormat="1" ht="255" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>607</v>
+      </c>
+      <c r="B128" t="s">
+        <v>743</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="D128" t="s">
+        <v>395</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>397</v>
       </c>
       <c r="F128" t="s">
         <v>38</v>
       </c>
-      <c r="G128" s="15" t="s">
+      <c r="G128" t="s">
         <v>10</v>
       </c>
-      <c r="I128" s="19" t="s">
-        <v>605</v>
-      </c>
-      <c r="J128" s="15">
+      <c r="H128" t="s">
+        <v>236</v>
+      </c>
+      <c r="I128" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="J128">
         <v>2025</v>
       </c>
-      <c r="K128" s="15" t="s">
+      <c r="K128" t="s">
         <v>95</v>
       </c>
       <c r="L128" s="3" t="s">
-        <v>843</v>
-      </c>
-      <c r="M128" s="13" t="s">
-        <v>621</v>
-      </c>
-      <c r="N128" s="13" t="s">
-        <v>622</v>
-      </c>
-      <c r="O128" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="P128" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q128" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="R128" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="S128" s="36" t="s">
-        <v>30</v>
+        <v>846</v>
+      </c>
+      <c r="M128" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="N128" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="O128" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="P128" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q128" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R128" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S128" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="T128" s="28"/>
       <c r="U128" s="28" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="V128" s="3" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="129" spans="1:22" s="15" customFormat="1" ht="105" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>607</v>
-      </c>
-      <c r="B129" t="s">
-        <v>746</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="D129" t="s">
-        <v>396</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>399</v>
+        <v>987</v>
+      </c>
+    </row>
+    <row r="129" spans="1:22" s="15" customFormat="1" ht="135" x14ac:dyDescent="0.25">
+      <c r="A129" s="15" t="s">
+        <v>618</v>
+      </c>
+      <c r="B129" s="15" t="s">
+        <v>744</v>
+      </c>
+      <c r="C129" s="17" t="s">
+        <v>755</v>
+      </c>
+      <c r="D129" s="18" t="s">
+        <v>395</v>
+      </c>
+      <c r="E129" s="17" t="s">
+        <v>619</v>
       </c>
       <c r="F129" t="s">
         <v>38</v>
       </c>
-      <c r="G129" t="s">
+      <c r="G129" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H129" t="s">
-        <v>4</v>
-      </c>
-      <c r="I129" s="9" t="s">
-        <v>605</v>
-      </c>
-      <c r="J129">
+      <c r="I129" s="19" t="s">
+        <v>604</v>
+      </c>
+      <c r="J129" s="15">
         <v>2025</v>
       </c>
-      <c r="K129" t="s">
+      <c r="K129" s="15" t="s">
         <v>95</v>
       </c>
       <c r="L129" s="3" t="s">
-        <v>844</v>
-      </c>
-      <c r="M129" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="N129" s="3" t="s">
-        <v>694</v>
-      </c>
-      <c r="O129" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P129" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q129" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R129" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="S129" s="31" t="s">
+        <v>841</v>
+      </c>
+      <c r="M129" s="13" t="s">
+        <v>620</v>
+      </c>
+      <c r="N129" s="13" t="s">
+        <v>621</v>
+      </c>
+      <c r="O129" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="P129" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q129" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="R129" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="S129" s="36" t="s">
         <v>30</v>
       </c>
       <c r="T129" s="28"/>
       <c r="U129" s="28" t="s">
-        <v>863</v>
+        <v>879</v>
       </c>
       <c r="V129" s="3" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
     </row>
     <row r="130" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="B130" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D130" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="F130" t="s">
         <v>38</v>
@@ -12520,10 +12524,10 @@
         <v>10</v>
       </c>
       <c r="H130" t="s">
-        <v>400</v>
+        <v>4</v>
       </c>
       <c r="I130" s="9" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="J130">
         <v>2025</v>
@@ -12532,13 +12536,13 @@
         <v>95</v>
       </c>
       <c r="L130" s="3" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="M130" s="3" t="s">
-        <v>1144</v>
+        <v>394</v>
       </c>
       <c r="N130" s="3" t="s">
-        <v>1146</v>
+        <v>693</v>
       </c>
       <c r="O130" s="30" t="s">
         <v>29</v>
@@ -12556,27 +12560,27 @@
         <v>30</v>
       </c>
       <c r="U130" s="28" t="s">
-        <v>885</v>
+        <v>861</v>
       </c>
       <c r="V130" s="3" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="131" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="131" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>611</v>
       </c>
       <c r="B131" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="D131" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F131" t="s">
         <v>38</v>
@@ -12585,10 +12589,10 @@
         <v>10</v>
       </c>
       <c r="H131" t="s">
-        <v>4</v>
+        <v>399</v>
       </c>
       <c r="I131" s="9" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="J131">
         <v>2025</v>
@@ -12597,181 +12601,181 @@
         <v>95</v>
       </c>
       <c r="L131" s="3" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="M131" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="N131" s="3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="O131" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="P131" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q131" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R131" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S131" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="U131" s="28" t="s">
+        <v>883</v>
+      </c>
+      <c r="V131" s="3" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="132" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>610</v>
+      </c>
+      <c r="B132" t="s">
+        <v>747</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="D132" t="s">
         <v>395</v>
       </c>
-      <c r="N131" s="3" t="s">
-        <v>695</v>
-      </c>
-      <c r="O131" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P131" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q131" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R131" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="S131" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="U131" s="28" t="s">
-        <v>868</v>
-      </c>
-      <c r="V131" s="3" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="132" spans="1:22" ht="60" x14ac:dyDescent="0.25">
-      <c r="A132" s="15" t="s">
+      <c r="E132" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="F132" t="s">
+        <v>38</v>
+      </c>
+      <c r="G132" t="s">
+        <v>10</v>
+      </c>
+      <c r="H132" t="s">
+        <v>4</v>
+      </c>
+      <c r="I132" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="J132">
+        <v>2025</v>
+      </c>
+      <c r="K132" t="s">
+        <v>95</v>
+      </c>
+      <c r="L132" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="M132" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="N132" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="O132" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="P132" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q132" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R132" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S132" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="U132" s="28" t="s">
+        <v>866</v>
+      </c>
+      <c r="V132" s="3" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="133" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+      <c r="A133" s="15" t="s">
+        <v>622</v>
+      </c>
+      <c r="B133" s="15" t="s">
+        <v>748</v>
+      </c>
+      <c r="C133" s="17" t="s">
+        <v>759</v>
+      </c>
+      <c r="D133" s="18" t="s">
+        <v>395</v>
+      </c>
+      <c r="E133" s="17" t="s">
         <v>623</v>
       </c>
-      <c r="B132" s="15" t="s">
+      <c r="F133" t="s">
+        <v>38</v>
+      </c>
+      <c r="G133" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H133" s="15" t="s">
+        <v>592</v>
+      </c>
+      <c r="I133" s="19" t="s">
+        <v>604</v>
+      </c>
+      <c r="J133" s="15">
+        <v>2025</v>
+      </c>
+      <c r="K133" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="L133" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="M133" s="13" t="s">
+        <v>1142</v>
+      </c>
+      <c r="N133" s="13" t="s">
+        <v>519</v>
+      </c>
+      <c r="O133" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="P133" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q133" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="R133" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="S133" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="U133" s="28" t="s">
+        <v>859</v>
+      </c>
+      <c r="V133" s="3" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="134" spans="1:22" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>609</v>
+      </c>
+      <c r="B134" t="s">
         <v>749</v>
       </c>
-      <c r="C132" s="17" t="s">
+      <c r="C134" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="D132" s="18" t="s">
-        <v>396</v>
-      </c>
-      <c r="E132" s="17" t="s">
-        <v>624</v>
-      </c>
-      <c r="F132" t="s">
-        <v>38</v>
-      </c>
-      <c r="G132" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H132" s="15" t="s">
-        <v>593</v>
-      </c>
-      <c r="I132" s="19" t="s">
-        <v>605</v>
-      </c>
-      <c r="J132" s="15">
-        <v>2025</v>
-      </c>
-      <c r="K132" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="L132" s="3" t="s">
-        <v>846</v>
-      </c>
-      <c r="M132" s="13" t="s">
-        <v>1144</v>
-      </c>
-      <c r="N132" s="13" t="s">
-        <v>520</v>
-      </c>
-      <c r="O132" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="P132" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q132" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="R132" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="S132" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="U132" s="28" t="s">
-        <v>861</v>
-      </c>
-      <c r="V132" s="3" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="133" spans="1:22" ht="90" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>610</v>
-      </c>
-      <c r="B133" t="s">
-        <v>750</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="D133" t="s">
-        <v>396</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="F133" t="s">
-        <v>38</v>
-      </c>
-      <c r="G133" t="s">
-        <v>10</v>
-      </c>
-      <c r="H133" t="s">
-        <v>0</v>
-      </c>
-      <c r="I133" s="9" t="s">
-        <v>605</v>
-      </c>
-      <c r="J133">
-        <v>2025</v>
-      </c>
-      <c r="K133" t="s">
-        <v>95</v>
-      </c>
-      <c r="L133" s="3" t="s">
-        <v>850</v>
-      </c>
-      <c r="M133" s="3" t="s">
-        <v>1148</v>
-      </c>
-      <c r="N133" s="3" t="s">
-        <v>1147</v>
-      </c>
-      <c r="O133" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P133" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q133" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R133" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="S133" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="U133" s="28" t="s">
-        <v>892</v>
-      </c>
-      <c r="V133" s="3" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="134" spans="1:22" s="15" customFormat="1" ht="90" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>614</v>
-      </c>
-      <c r="B134" t="s">
-        <v>751</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>762</v>
-      </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="F134" t="s">
         <v>38</v>
@@ -12779,24 +12783,26 @@
       <c r="G134" t="s">
         <v>10</v>
       </c>
-      <c r="H134"/>
+      <c r="H134" t="s">
+        <v>0</v>
+      </c>
       <c r="I134" s="9" t="s">
-        <v>397</v>
+        <v>604</v>
       </c>
       <c r="J134">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="K134" t="s">
         <v>95</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>405</v>
+        <v>848</v>
       </c>
       <c r="M134" s="3" t="s">
-        <v>38</v>
+        <v>1146</v>
       </c>
       <c r="N134" s="3" t="s">
-        <v>696</v>
+        <v>1145</v>
       </c>
       <c r="O134" s="30" t="s">
         <v>29</v>
@@ -12811,31 +12817,31 @@
         <v>29</v>
       </c>
       <c r="S134" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T134" s="28"/>
       <c r="U134" s="28" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="V134" s="3" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="135" spans="1:22" ht="150" x14ac:dyDescent="0.25">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="135" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B135" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>408</v>
+        <v>761</v>
       </c>
       <c r="D135" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="F135" t="s">
         <v>38</v>
@@ -12843,26 +12849,23 @@
       <c r="G135" t="s">
         <v>10</v>
       </c>
-      <c r="H135" t="s">
-        <v>407</v>
-      </c>
       <c r="I135" s="9" t="s">
-        <v>605</v>
+        <v>396</v>
       </c>
       <c r="J135">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="K135" t="s">
         <v>95</v>
       </c>
       <c r="L135" s="3" t="s">
-        <v>851</v>
+        <v>404</v>
       </c>
       <c r="M135" s="3" t="s">
-        <v>1150</v>
+        <v>38</v>
       </c>
       <c r="N135" s="3" t="s">
-        <v>1149</v>
+        <v>695</v>
       </c>
       <c r="O135" s="30" t="s">
         <v>29</v>
@@ -12877,206 +12880,214 @@
         <v>29</v>
       </c>
       <c r="S135" s="31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U135" s="28" t="s">
-        <v>868</v>
+        <v>890</v>
       </c>
       <c r="V135" s="3" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="136" spans="1:22" ht="60" x14ac:dyDescent="0.25">
-      <c r="A136" s="15" t="s">
-        <v>625</v>
-      </c>
-      <c r="B136" s="15" t="s">
-        <v>753</v>
-      </c>
-      <c r="C136" s="17" t="s">
-        <v>763</v>
-      </c>
-      <c r="D136" s="18" t="s">
-        <v>396</v>
-      </c>
-      <c r="E136" s="17" t="s">
-        <v>626</v>
+        <v>990</v>
+      </c>
+    </row>
+    <row r="136" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>608</v>
+      </c>
+      <c r="B136" t="s">
+        <v>751</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D136" t="s">
+        <v>395</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>407</v>
       </c>
       <c r="F136" t="s">
         <v>38</v>
       </c>
-      <c r="G136" s="15" t="s">
+      <c r="G136" t="s">
         <v>10</v>
       </c>
-      <c r="H136" s="15"/>
-      <c r="I136" s="19" t="s">
-        <v>605</v>
-      </c>
-      <c r="J136" s="15">
+      <c r="H136" t="s">
+        <v>406</v>
+      </c>
+      <c r="I136" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="J136">
         <v>2025</v>
       </c>
-      <c r="K136" s="15" t="s">
+      <c r="K136" t="s">
         <v>95</v>
       </c>
       <c r="L136" s="3" t="s">
-        <v>852</v>
-      </c>
-      <c r="M136" s="13" t="s">
-        <v>1152</v>
-      </c>
-      <c r="N136" s="13" t="s">
-        <v>1151</v>
-      </c>
-      <c r="O136" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="P136" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q136" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="R136" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="S136" s="36" t="s">
-        <v>29</v>
+        <v>849</v>
+      </c>
+      <c r="M136" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="N136" s="3" t="s">
+        <v>1147</v>
+      </c>
+      <c r="O136" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="P136" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q136" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R136" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S136" s="31" t="s">
+        <v>30</v>
       </c>
       <c r="U136" s="28" t="s">
         <v>866</v>
       </c>
       <c r="V136" s="3" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="137" spans="1:22" ht="90" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="137" spans="1:22" ht="150" x14ac:dyDescent="0.25">
+      <c r="A137" s="15" t="s">
+        <v>624</v>
+      </c>
+      <c r="B137" s="15" t="s">
+        <v>752</v>
+      </c>
+      <c r="C137" s="17" t="s">
+        <v>762</v>
+      </c>
+      <c r="D137" s="18" t="s">
+        <v>395</v>
+      </c>
+      <c r="E137" s="17" t="s">
+        <v>625</v>
+      </c>
+      <c r="F137" t="s">
+        <v>38</v>
+      </c>
+      <c r="G137" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H137" s="15"/>
+      <c r="I137" s="19" t="s">
+        <v>604</v>
+      </c>
+      <c r="J137" s="15">
+        <v>2025</v>
+      </c>
+      <c r="K137" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="L137" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="M137" s="13" t="s">
+        <v>1150</v>
+      </c>
+      <c r="N137" s="13" t="s">
+        <v>1149</v>
+      </c>
+      <c r="O137" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="P137" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q137" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="R137" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="S137" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="U137" s="28" t="s">
+        <v>864</v>
+      </c>
+      <c r="V137" s="3" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="138" spans="1:22" ht="60" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>422</v>
+      </c>
+      <c r="B138" t="s">
         <v>423</v>
       </c>
-      <c r="B137" t="s">
+      <c r="C138" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="D138" t="s">
+        <v>38</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="F138" t="s">
+        <v>38</v>
+      </c>
+      <c r="G138" t="s">
+        <v>17</v>
+      </c>
+      <c r="H138" t="s">
+        <v>6</v>
+      </c>
+      <c r="I138" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="J138">
+        <v>2020</v>
+      </c>
+      <c r="K138" t="s">
         <v>424</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="D137" t="s">
-        <v>38</v>
-      </c>
-      <c r="E137" s="1" t="s">
+      <c r="L138" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="M138" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="F137" t="s">
-        <v>38</v>
-      </c>
-      <c r="G137" t="s">
-        <v>17</v>
-      </c>
-      <c r="H137" t="s">
-        <v>6</v>
-      </c>
-      <c r="I137" s="9">
-        <v>0.6</v>
-      </c>
-      <c r="J137">
-        <v>2020</v>
-      </c>
-      <c r="K137" t="s">
-        <v>425</v>
-      </c>
-      <c r="L137" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="M137" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="N137" s="3" t="s">
-        <v>699</v>
-      </c>
-      <c r="O137" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P137" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q137" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R137" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="S137" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="U137" s="28" t="s">
-        <v>863</v>
-      </c>
-      <c r="V137" s="3" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="138" spans="1:22" ht="120" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>429</v>
-      </c>
-      <c r="B138" t="s">
-        <v>430</v>
-      </c>
-      <c r="C138" t="s">
-        <v>38</v>
-      </c>
-      <c r="D138" t="s">
-        <v>38</v>
-      </c>
-      <c r="E138" s="7" t="s">
-        <v>432</v>
-      </c>
-      <c r="F138" t="s">
-        <v>38</v>
-      </c>
-      <c r="G138" t="s">
-        <v>0</v>
-      </c>
-      <c r="H138" t="s">
-        <v>1</v>
-      </c>
-      <c r="I138" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J138" t="s">
-        <v>38</v>
-      </c>
-      <c r="K138" t="s">
-        <v>38</v>
-      </c>
-      <c r="L138" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="M138" s="3" t="s">
-        <v>433</v>
-      </c>
       <c r="N138" s="3" t="s">
-        <v>702</v>
+        <v>698</v>
+      </c>
+      <c r="O138" s="30" t="s">
+        <v>29</v>
       </c>
       <c r="P138" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="Q138" s="38"/>
+      <c r="Q138" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R138" s="30" t="s">
+        <v>29</v>
+      </c>
       <c r="S138" s="31" t="s">
         <v>30</v>
       </c>
       <c r="U138" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V138" s="3" t="s">
-        <v>980</v>
+        <v>993</v>
       </c>
     </row>
     <row r="139" spans="1:22" s="15" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="B139" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C139" t="s">
         <v>38</v>
@@ -13084,358 +13095,353 @@
       <c r="D139" t="s">
         <v>38</v>
       </c>
-      <c r="E139" s="1" t="s">
-        <v>436</v>
+      <c r="E139" s="7" t="s">
+        <v>431</v>
       </c>
       <c r="F139" t="s">
         <v>38</v>
       </c>
       <c r="G139" t="s">
-        <v>4</v>
-      </c>
-      <c r="H139"/>
+        <v>0</v>
+      </c>
+      <c r="H139" t="s">
+        <v>1</v>
+      </c>
       <c r="I139" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="J139">
-        <v>2017</v>
+      <c r="J139" t="s">
+        <v>38</v>
       </c>
       <c r="K139" t="s">
         <v>38</v>
       </c>
       <c r="L139" s="3" t="s">
-        <v>836</v>
+        <v>430</v>
       </c>
       <c r="M139" s="3" t="s">
-        <v>38</v>
+        <v>432</v>
       </c>
       <c r="N139" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O139" s="30" t="s">
-        <v>30</v>
-      </c>
+        <v>701</v>
+      </c>
+      <c r="O139" s="30"/>
       <c r="P139" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q139" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R139" s="30" t="s">
-        <v>30</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="Q139" s="38"/>
+      <c r="R139" s="30"/>
       <c r="S139" s="31" t="s">
         <v>30</v>
       </c>
       <c r="T139" s="28"/>
       <c r="U139" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V139" s="3" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="140" spans="1:22" s="15" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="140" spans="1:22" s="15" customFormat="1" ht="120" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="B140" t="s">
-        <v>438</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>440</v>
+        <v>434</v>
+      </c>
+      <c r="C140" t="s">
+        <v>38</v>
       </c>
       <c r="D140" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>26</v>
+        <v>435</v>
       </c>
       <c r="F140" t="s">
         <v>38</v>
       </c>
       <c r="G140" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H140"/>
       <c r="I140" s="9" t="s">
-        <v>285</v>
+        <v>38</v>
       </c>
       <c r="J140">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="K140" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="L140" s="3" t="s">
-        <v>439</v>
+        <v>834</v>
       </c>
       <c r="M140" s="3" t="s">
-        <v>316</v>
+        <v>38</v>
       </c>
       <c r="N140" s="3" t="s">
-        <v>701</v>
+        <v>38</v>
       </c>
       <c r="O140" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P140" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q140" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R140" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S140" s="31" t="s">
         <v>30</v>
       </c>
       <c r="T140" s="28"/>
       <c r="U140" s="28" t="s">
-        <v>881</v>
+        <v>861</v>
       </c>
       <c r="V140" s="3" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="141" spans="1:22" ht="75" x14ac:dyDescent="0.25">
-      <c r="A141" s="15" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="141" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>436</v>
+      </c>
+      <c r="B141" t="s">
+        <v>437</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D141" t="s">
+        <v>32</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F141" t="s">
+        <v>38</v>
+      </c>
+      <c r="G141" t="s">
+        <v>10</v>
+      </c>
+      <c r="I141" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="J141">
+        <v>2020</v>
+      </c>
+      <c r="K141" t="s">
+        <v>23</v>
+      </c>
+      <c r="L141" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="M141" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="N141" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="O141" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="P141" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q141" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R141" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S141" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="U141" s="28" t="s">
+        <v>879</v>
+      </c>
+      <c r="V141" s="3" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="142" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+      <c r="A142" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="B142" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C142" s="17" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D142" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E142" s="17" t="s">
         <v>441</v>
       </c>
-      <c r="B141" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C141" s="17" t="s">
-        <v>1167</v>
-      </c>
-      <c r="D141" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="E141" s="17" t="s">
-        <v>442</v>
-      </c>
-      <c r="F141" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G141" s="15" t="s">
+      <c r="F142" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G142" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="H141" s="15" t="s">
+      <c r="H142" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="I141" s="19" t="s">
+      <c r="I142" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="J141" s="15">
+      <c r="J142" s="15">
         <v>2017</v>
       </c>
-      <c r="K141" s="15" t="s">
+      <c r="K142" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="L141" s="13" t="s">
-        <v>853</v>
-      </c>
-      <c r="M141" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="N141" s="13" t="s">
-        <v>703</v>
-      </c>
-      <c r="O141" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="P141" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q141" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="R141" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="S141" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="T141" s="40"/>
-      <c r="U141" s="40" t="s">
-        <v>892</v>
-      </c>
-      <c r="V141" s="13" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="142" spans="1:22" ht="300" x14ac:dyDescent="0.25">
-      <c r="A142" s="15" t="s">
-        <v>443</v>
-      </c>
-      <c r="B142" s="15" t="s">
-        <v>444</v>
-      </c>
-      <c r="C142" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="D142" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="E142" s="17" t="s">
-        <v>445</v>
-      </c>
-      <c r="F142" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G142" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="H142" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="I142" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="J142" s="15">
-        <v>2024</v>
-      </c>
-      <c r="K142" s="15" t="s">
-        <v>38</v>
-      </c>
       <c r="L142" s="13" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="M142" s="13" t="s">
-        <v>446</v>
+        <v>38</v>
       </c>
       <c r="N142" s="13" t="s">
-        <v>38</v>
+        <v>702</v>
       </c>
       <c r="O142" s="36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P142" s="36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q142" s="36" t="s">
         <v>29</v>
       </c>
       <c r="R142" s="36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S142" s="36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T142" s="40"/>
       <c r="U142" s="40" t="s">
-        <v>866</v>
+        <v>890</v>
       </c>
       <c r="V142" s="13" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="143" spans="1:22" ht="270" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="143" spans="1:22" ht="75" x14ac:dyDescent="0.25">
+      <c r="A143" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="B143" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="C143" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D143" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E143" s="17" t="s">
+        <v>444</v>
+      </c>
+      <c r="F143" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G143" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="H143" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I143" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="J143" s="15">
+        <v>2024</v>
+      </c>
+      <c r="K143" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L143" s="13" t="s">
+        <v>852</v>
+      </c>
+      <c r="M143" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="N143" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O143" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="P143" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q143" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="R143" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="S143" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="T143" s="40"/>
+      <c r="U143" s="40" t="s">
+        <v>864</v>
+      </c>
+      <c r="V143" s="13" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="144" spans="1:22" s="14" customFormat="1" ht="300" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>532</v>
+      </c>
+      <c r="B144" t="s">
+        <v>529</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="D144" t="s">
+        <v>534</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="F144" t="s">
         <v>533</v>
       </c>
-      <c r="B143" t="s">
-        <v>530</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="D143" t="s">
-        <v>535</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="F143" t="s">
-        <v>534</v>
-      </c>
-      <c r="G143" t="s">
+      <c r="G144" t="s">
         <v>19</v>
       </c>
-      <c r="H143" t="s">
+      <c r="H144" t="s">
         <v>9</v>
       </c>
-      <c r="I143" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J143" t="s">
-        <v>38</v>
-      </c>
-      <c r="K143" t="s">
-        <v>38</v>
-      </c>
-      <c r="L143" s="3" t="s">
-        <v>815</v>
-      </c>
-      <c r="M143" s="3" t="s">
-        <v>1154</v>
-      </c>
-      <c r="N143" s="3" t="s">
-        <v>1153</v>
-      </c>
-      <c r="O143" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P143" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q143" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R143" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="S143" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="U143" s="28" t="s">
-        <v>863</v>
-      </c>
-      <c r="V143" s="3" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="144" spans="1:22" s="14" customFormat="1" ht="120" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>447</v>
-      </c>
-      <c r="B144" t="s">
-        <v>239</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="D144" t="s">
-        <v>38</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="F144" t="s">
-        <v>38</v>
-      </c>
-      <c r="G144" t="s">
-        <v>10</v>
-      </c>
-      <c r="H144"/>
       <c r="I144" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="J144">
-        <v>2017</v>
+      <c r="J144" t="s">
+        <v>38</v>
       </c>
       <c r="K144" t="s">
         <v>38</v>
       </c>
       <c r="L144" s="3" t="s">
-        <v>840</v>
+        <v>813</v>
       </c>
       <c r="M144" s="3" t="s">
-        <v>38</v>
+        <v>1152</v>
       </c>
       <c r="N144" s="3" t="s">
-        <v>449</v>
+        <v>1151</v>
       </c>
       <c r="O144" s="30" t="s">
         <v>29</v>
@@ -13454,27 +13460,27 @@
       </c>
       <c r="T144" s="28"/>
       <c r="U144" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V144" s="3" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="145" spans="1:22" ht="60" x14ac:dyDescent="0.25">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="145" spans="1:22" ht="270" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B145" t="s">
-        <v>418</v>
+        <v>239</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="D145" t="s">
         <v>38</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="F145" t="s">
         <v>38</v>
@@ -13492,137 +13498,140 @@
         <v>38</v>
       </c>
       <c r="L145" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="M145" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N145" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="O145" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="P145" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q145" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R145" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S145" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="U145" s="28" t="s">
+        <v>861</v>
+      </c>
+      <c r="V145" s="3" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="146" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>449</v>
+      </c>
+      <c r="B146" t="s">
+        <v>417</v>
+      </c>
+      <c r="C146" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="M145" s="3" t="s">
+      <c r="D146" t="s">
+        <v>38</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="F146" t="s">
+        <v>38</v>
+      </c>
+      <c r="G146" t="s">
+        <v>10</v>
+      </c>
+      <c r="I146" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J146">
+        <v>2017</v>
+      </c>
+      <c r="K146" t="s">
+        <v>38</v>
+      </c>
+      <c r="L146" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="M146" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="N145" s="3" t="s">
+      <c r="N146" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="O146" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="P146" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q146" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R146" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S146" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="U146" s="28" t="s">
+        <v>861</v>
+      </c>
+      <c r="V146" s="3" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="147" spans="1:22" ht="60" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
         <v>454</v>
       </c>
-      <c r="O145" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P145" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q145" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R145" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="S145" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="U145" s="28" t="s">
-        <v>863</v>
-      </c>
-      <c r="V145" s="3" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="146" spans="1:22" ht="90" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
+      <c r="B147" t="s">
         <v>455</v>
       </c>
-      <c r="B146" t="s">
-        <v>456</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="D146" t="s">
-        <v>38</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="F146" t="s">
-        <v>38</v>
-      </c>
-      <c r="G146" t="s">
-        <v>0</v>
-      </c>
-      <c r="H146" t="s">
+      <c r="C147" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="D147" t="s">
+        <v>38</v>
+      </c>
+      <c r="E147" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="I146" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J146">
-        <v>2019</v>
-      </c>
-      <c r="K146" t="s">
-        <v>38</v>
-      </c>
-      <c r="L146" s="3" t="s">
-        <v>839</v>
-      </c>
-      <c r="M146" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="N146" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O146" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P146" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q146" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R146" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="S146" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="U146" s="28" t="s">
-        <v>863</v>
-      </c>
-      <c r="V146" s="3" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="147" spans="1:22" ht="105" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>214</v>
-      </c>
-      <c r="B147" t="s">
-        <v>643</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="D147" t="s">
-        <v>38</v>
-      </c>
       <c r="F147" t="s">
-        <v>215</v>
+        <v>38</v>
       </c>
       <c r="G147" t="s">
         <v>0</v>
       </c>
       <c r="H147" t="s">
-        <v>1</v>
+        <v>456</v>
+      </c>
+      <c r="I147" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="J147">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="K147" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="L147" s="3" t="s">
-        <v>216</v>
+        <v>837</v>
       </c>
       <c r="M147" s="3" t="s">
-        <v>217</v>
+        <v>458</v>
       </c>
       <c r="N147" s="3" t="s">
-        <v>218</v>
+        <v>38</v>
       </c>
       <c r="O147" s="30" t="s">
         <v>29</v>
@@ -13634,104 +13643,101 @@
         <v>29</v>
       </c>
       <c r="R147" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S147" s="31" t="s">
         <v>30</v>
       </c>
       <c r="U147" s="28" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="V147" s="3" t="s">
-        <v>918</v>
+        <v>976</v>
       </c>
     </row>
     <row r="148" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>214</v>
+      </c>
+      <c r="B148" t="s">
+        <v>642</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="D148" t="s">
+        <v>38</v>
+      </c>
+      <c r="F148" t="s">
+        <v>215</v>
+      </c>
+      <c r="G148" t="s">
+        <v>0</v>
+      </c>
+      <c r="H148" t="s">
+        <v>1</v>
+      </c>
+      <c r="J148">
+        <v>2023</v>
+      </c>
+      <c r="K148" t="s">
+        <v>128</v>
+      </c>
+      <c r="L148" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="M148" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="N148" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="O148" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="P148" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q148" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R148" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S148" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="U148" s="28" t="s">
+        <v>861</v>
+      </c>
+      <c r="V148" s="3" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="149" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>459</v>
+      </c>
+      <c r="B149" s="15" t="s">
         <v>460</v>
       </c>
-      <c r="B148" s="15" t="s">
+      <c r="C149" s="17" t="s">
+        <v>801</v>
+      </c>
+      <c r="D149" t="s">
+        <v>38</v>
+      </c>
+      <c r="E149" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="C148" s="17" t="s">
-        <v>803</v>
-      </c>
-      <c r="D148" t="s">
-        <v>38</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="F148" t="s">
-        <v>38</v>
-      </c>
-      <c r="G148" t="s">
+      <c r="F149" t="s">
+        <v>38</v>
+      </c>
+      <c r="G149" t="s">
         <v>3</v>
       </c>
-      <c r="I148" s="9">
+      <c r="I149" s="9">
         <v>1.01</v>
-      </c>
-      <c r="J148">
-        <v>2013</v>
-      </c>
-      <c r="K148" t="s">
-        <v>38</v>
-      </c>
-      <c r="L148" s="3" t="s">
-        <v>858</v>
-      </c>
-      <c r="M148" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N148" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="O148" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P148" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q148" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R148" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="S148" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="U148" s="28" t="s">
-        <v>881</v>
-      </c>
-      <c r="V148" s="3" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="149" spans="1:22" ht="90" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>464</v>
-      </c>
-      <c r="B149" s="15" t="s">
-        <v>465</v>
-      </c>
-      <c r="C149" s="17" t="s">
-        <v>806</v>
-      </c>
-      <c r="D149" t="s">
-        <v>38</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="F149" t="s">
-        <v>38</v>
-      </c>
-      <c r="G149" t="s">
-        <v>0</v>
-      </c>
-      <c r="I149" s="9">
-        <v>1.1200000000000001</v>
       </c>
       <c r="J149">
         <v>2013</v>
@@ -13740,16 +13746,16 @@
         <v>38</v>
       </c>
       <c r="L149" s="3" t="s">
-        <v>1006</v>
+        <v>856</v>
       </c>
       <c r="M149" s="3" t="s">
-        <v>804</v>
+        <v>38</v>
       </c>
       <c r="N149" s="3" t="s">
-        <v>812</v>
+        <v>462</v>
       </c>
       <c r="O149" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P149" s="30" t="s">
         <v>29</v>
@@ -13758,42 +13764,42 @@
         <v>30</v>
       </c>
       <c r="R149" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="S149" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S149" s="31" t="s">
         <v>30</v>
       </c>
       <c r="U149" s="28" t="s">
-        <v>863</v>
+        <v>879</v>
       </c>
       <c r="V149" s="3" t="s">
-        <v>864</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="150" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B150" s="15" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C150" s="17" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D150" t="s">
         <v>38</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="F150" t="s">
         <v>38</v>
       </c>
       <c r="G150" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I150" s="9">
-        <v>1.03</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="J150">
         <v>2013</v>
@@ -13802,16 +13808,16 @@
         <v>38</v>
       </c>
       <c r="L150" s="3" t="s">
-        <v>816</v>
+        <v>1004</v>
       </c>
       <c r="M150" s="3" t="s">
-        <v>38</v>
+        <v>802</v>
       </c>
       <c r="N150" s="3" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="O150" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P150" s="30" t="s">
         <v>29</v>
@@ -13820,36 +13826,33 @@
         <v>30</v>
       </c>
       <c r="R150" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="S150" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="T150" s="28">
-        <v>15</v>
+        <v>30</v>
+      </c>
+      <c r="S150" s="30" t="s">
+        <v>30</v>
       </c>
       <c r="U150" s="28" t="s">
-        <v>892</v>
+        <v>861</v>
       </c>
       <c r="V150" s="3" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="151" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="151" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B151" s="15" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C151" s="17" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="D151" t="s">
         <v>38</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="F151" t="s">
         <v>38</v>
@@ -13858,7 +13861,7 @@
         <v>4</v>
       </c>
       <c r="I151" s="9">
-        <v>1.1399999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="J151">
         <v>2013</v>
@@ -13867,7 +13870,7 @@
         <v>38</v>
       </c>
       <c r="L151" s="3" t="s">
-        <v>855</v>
+        <v>814</v>
       </c>
       <c r="M151" s="3" t="s">
         <v>38</v>
@@ -13876,7 +13879,7 @@
         <v>809</v>
       </c>
       <c r="O151" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P151" s="30" t="s">
         <v>29</v>
@@ -13888,39 +13891,42 @@
         <v>29</v>
       </c>
       <c r="S151" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="T151" s="28">
+        <v>15</v>
       </c>
       <c r="U151" s="28" t="s">
-        <v>881</v>
+        <v>890</v>
       </c>
       <c r="V151" s="3" t="s">
-        <v>1000</v>
+        <v>939</v>
       </c>
     </row>
     <row r="152" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>555</v>
+        <v>469</v>
       </c>
       <c r="B152" s="15" t="s">
-        <v>804</v>
+        <v>470</v>
       </c>
       <c r="C152" s="17" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="D152" t="s">
         <v>38</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="F152" t="s">
         <v>38</v>
       </c>
       <c r="G152" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I152" s="9">
-        <v>1.1200000000000001</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="J152">
         <v>2013</v>
@@ -13929,13 +13935,13 @@
         <v>38</v>
       </c>
       <c r="L152" s="3" t="s">
-        <v>1020</v>
+        <v>853</v>
       </c>
       <c r="M152" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N152" s="3" t="s">
-        <v>38</v>
+        <v>807</v>
       </c>
       <c r="O152" s="30" t="s">
         <v>30</v>
@@ -13947,24 +13953,24 @@
         <v>30</v>
       </c>
       <c r="R152" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S152" s="31" t="s">
         <v>29</v>
       </c>
       <c r="U152" s="28" t="s">
-        <v>863</v>
+        <v>879</v>
       </c>
       <c r="V152" s="3" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="153" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="153" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>473</v>
+        <v>554</v>
       </c>
       <c r="B153" s="15" t="s">
-        <v>474</v>
+        <v>802</v>
       </c>
       <c r="C153" s="17" t="s">
         <v>808</v>
@@ -13973,16 +13979,16 @@
         <v>38</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="F153" t="s">
         <v>38</v>
       </c>
       <c r="G153" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I153" s="9">
-        <v>1.03</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="J153">
         <v>2013</v>
@@ -13991,13 +13997,13 @@
         <v>38</v>
       </c>
       <c r="L153" s="3" t="s">
-        <v>859</v>
+        <v>1018</v>
       </c>
       <c r="M153" s="3" t="s">
-        <v>1059</v>
+        <v>38</v>
       </c>
       <c r="N153" s="3" t="s">
-        <v>463</v>
+        <v>38</v>
       </c>
       <c r="O153" s="30" t="s">
         <v>30</v>
@@ -14012,373 +14018,435 @@
         <v>30</v>
       </c>
       <c r="S153" s="31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U153" s="28" t="s">
-        <v>885</v>
+        <v>861</v>
       </c>
       <c r="V153" s="3" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="154" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="154" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>472</v>
+      </c>
+      <c r="B154" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="C154" s="17" t="s">
+        <v>806</v>
+      </c>
+      <c r="D154" t="s">
+        <v>38</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="F154" t="s">
+        <v>38</v>
+      </c>
+      <c r="G154" t="s">
+        <v>18</v>
+      </c>
+      <c r="I154" s="9">
+        <v>1.03</v>
+      </c>
+      <c r="J154">
+        <v>2013</v>
+      </c>
+      <c r="K154" t="s">
+        <v>38</v>
+      </c>
+      <c r="L154" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="M154" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="N154" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="O154" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="P154" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q154" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="R154" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="S154" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="U154" s="28" t="s">
+        <v>883</v>
+      </c>
+      <c r="V154" s="3" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="155" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>475</v>
+      </c>
+      <c r="B155" t="s">
         <v>476</v>
       </c>
-      <c r="B154" t="s">
+      <c r="C155" t="s">
+        <v>38</v>
+      </c>
+      <c r="D155" t="s">
+        <v>38</v>
+      </c>
+      <c r="E155" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="C154" t="s">
-        <v>38</v>
-      </c>
-      <c r="D154" t="s">
-        <v>38</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="F154" t="s">
-        <v>38</v>
-      </c>
-      <c r="G154" t="s">
+      <c r="F155" t="s">
+        <v>38</v>
+      </c>
+      <c r="G155" t="s">
         <v>12</v>
       </c>
-      <c r="I154" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J154">
+      <c r="I155" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J155">
         <v>2009</v>
       </c>
-      <c r="K154" t="s">
-        <v>38</v>
-      </c>
-      <c r="L154" s="3" t="s">
-        <v>856</v>
-      </c>
-      <c r="M154" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N154" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O154" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P154" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q154" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R154" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="S154" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="U154" s="28" t="s">
-        <v>881</v>
-      </c>
-      <c r="V154" s="3" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="155" spans="1:22" ht="90" x14ac:dyDescent="0.25">
-      <c r="A155" s="4" t="s">
-        <v>515</v>
-      </c>
-      <c r="B155" t="s">
-        <v>516</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="D155" t="s">
-        <v>38</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="F155" t="s">
-        <v>38</v>
-      </c>
-      <c r="G155" t="s">
-        <v>17</v>
-      </c>
-      <c r="I155" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J155">
-        <v>2024</v>
-      </c>
       <c r="K155" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="L155" s="3" t="s">
-        <v>517</v>
+        <v>854</v>
       </c>
       <c r="M155" s="3" t="s">
-        <v>519</v>
+        <v>38</v>
       </c>
       <c r="N155" s="3" t="s">
-        <v>520</v>
+        <v>38</v>
       </c>
       <c r="O155" s="30" t="s">
         <v>29</v>
       </c>
       <c r="P155" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q155" s="30" t="s">
         <v>29</v>
       </c>
       <c r="R155" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S155" s="31" t="s">
         <v>30</v>
       </c>
       <c r="U155" s="28" t="s">
-        <v>861</v>
+        <v>879</v>
       </c>
       <c r="V155" s="3" t="s">
         <v>999</v>
       </c>
     </row>
-    <row r="156" spans="1:22" ht="315" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
+    <row r="156" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="B156" t="s">
+        <v>515</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="D156" t="s">
+        <v>38</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="F156" t="s">
+        <v>38</v>
+      </c>
+      <c r="G156" t="s">
+        <v>17</v>
+      </c>
+      <c r="I156" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J156">
+        <v>2024</v>
+      </c>
+      <c r="K156" t="s">
+        <v>128</v>
+      </c>
+      <c r="L156" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="M156" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="N156" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="O156" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="P156" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q156" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R156" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S156" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="U156" s="28" t="s">
+        <v>859</v>
+      </c>
+      <c r="V156" s="3" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="157" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>478</v>
+      </c>
+      <c r="B157" t="s">
         <v>479</v>
       </c>
-      <c r="B156" t="s">
+      <c r="C157" t="s">
+        <v>38</v>
+      </c>
+      <c r="D157" t="s">
+        <v>38</v>
+      </c>
+      <c r="E157" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="C156" t="s">
-        <v>38</v>
-      </c>
-      <c r="D156" t="s">
-        <v>38</v>
-      </c>
-      <c r="E156" s="1" t="s">
+      <c r="F157" t="s">
+        <v>38</v>
+      </c>
+      <c r="G157" t="s">
+        <v>12</v>
+      </c>
+      <c r="I157" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J157">
+        <v>2009</v>
+      </c>
+      <c r="K157" t="s">
+        <v>38</v>
+      </c>
+      <c r="L157" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="M157" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N157" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O157" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="P157" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q157" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R157" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="S157" s="31"/>
+      <c r="U157" s="28" t="s">
+        <v>879</v>
+      </c>
+      <c r="V157" s="3" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="158" spans="1:22" ht="315" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
         <v>481</v>
       </c>
-      <c r="F156" t="s">
-        <v>38</v>
-      </c>
-      <c r="G156" t="s">
-        <v>12</v>
-      </c>
-      <c r="I156" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J156">
-        <v>2009</v>
-      </c>
-      <c r="K156" t="s">
-        <v>38</v>
-      </c>
-      <c r="L156" s="3" t="s">
-        <v>857</v>
-      </c>
-      <c r="M156" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N156" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O156" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P156" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q156" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R156" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="S156" s="31"/>
-      <c r="U156" s="28" t="s">
-        <v>881</v>
-      </c>
-      <c r="V156" s="3" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="157" spans="1:22" ht="255" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
+      <c r="B158" t="s">
         <v>482</v>
       </c>
-      <c r="B157" t="s">
+      <c r="C158" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="C157" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="D157" t="s">
+      <c r="D158" t="s">
         <v>32</v>
       </c>
-      <c r="E157" s="1" t="s">
+      <c r="E158" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F157" t="s">
-        <v>38</v>
-      </c>
-      <c r="G157" t="s">
+      <c r="F158" t="s">
+        <v>38</v>
+      </c>
+      <c r="G158" t="s">
         <v>18</v>
       </c>
-      <c r="I157" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J157">
+      <c r="I158" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J158">
         <v>2020</v>
       </c>
-      <c r="K157" t="s">
+      <c r="K158" t="s">
         <v>23</v>
       </c>
-      <c r="L157" s="3" t="s">
-        <v>1016</v>
-      </c>
-      <c r="M157" s="3" t="s">
-        <v>1117</v>
-      </c>
-      <c r="N157" s="3" t="s">
-        <v>1116</v>
-      </c>
-      <c r="O157" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P157" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q157" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R157" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="S157" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="U157" s="28" t="s">
-        <v>885</v>
-      </c>
-      <c r="V157" s="3" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="158" spans="1:22" ht="90" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>704</v>
-      </c>
-      <c r="B158" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C158" s="25" t="s">
-        <v>767</v>
-      </c>
-      <c r="D158" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="F158" t="s">
-        <v>38</v>
-      </c>
-      <c r="G158" t="s">
+      <c r="L158" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="M158" s="3" t="s">
+        <v>1115</v>
+      </c>
+      <c r="N158" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="O158" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="P158" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q158" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R158" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S158" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="U158" s="28" t="s">
+        <v>883</v>
+      </c>
+      <c r="V158" s="3" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="159" spans="1:22" ht="255" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>703</v>
+      </c>
+      <c r="B159" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C159" s="25" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="F159" t="s">
+        <v>38</v>
+      </c>
+      <c r="G159" t="s">
         <v>7</v>
       </c>
-      <c r="I158" s="9">
+      <c r="I159" s="9">
         <v>1.21</v>
       </c>
-      <c r="J158">
+      <c r="J159">
         <v>2006</v>
       </c>
-      <c r="L158" s="3" t="s">
+      <c r="L159" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="M159" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N159" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O159" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="P159" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q159" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R159" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S159" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="T159" s="28">
+        <v>30</v>
+      </c>
+      <c r="U159" s="30" t="s">
+        <v>883</v>
+      </c>
+      <c r="V159" s="32" t="s">
         <v>860</v>
       </c>
-      <c r="M158" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N158" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="O158" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="P158" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q158" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R158" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="S158" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="T158" s="28">
-        <v>30</v>
-      </c>
-      <c r="U158" s="30" t="s">
-        <v>885</v>
-      </c>
-      <c r="V158" s="32" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="159" spans="1:22" ht="180" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
+    </row>
+    <row r="160" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B160" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C160" s="25" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E160" s="27" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F160" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="G160" t="s">
+        <v>4</v>
+      </c>
+      <c r="H160" t="s">
+        <v>14</v>
+      </c>
+      <c r="I160" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J160">
+        <v>2026</v>
+      </c>
+      <c r="K160" t="s">
+        <v>23</v>
+      </c>
+      <c r="L160" s="3" t="s">
         <v>1054</v>
       </c>
-      <c r="B159" t="s">
+      <c r="M160" t="s">
         <v>1055</v>
       </c>
-      <c r="C159" s="25" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D159" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E159" s="27" t="s">
-        <v>1065</v>
-      </c>
-      <c r="F159" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="G159" t="s">
-        <v>4</v>
-      </c>
-      <c r="H159" t="s">
-        <v>14</v>
-      </c>
-      <c r="I159" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J159">
-        <v>2026</v>
-      </c>
-      <c r="K159" t="s">
-        <v>23</v>
-      </c>
-      <c r="L159" s="3" t="s">
+      <c r="N160" s="13" t="s">
         <v>1056</v>
       </c>
-      <c r="M159" t="s">
-        <v>1057</v>
-      </c>
-      <c r="N159" s="13" t="s">
-        <v>1058</v>
-      </c>
-      <c r="O159" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="S159" s="31"/>
-      <c r="T159" s="30"/>
-      <c r="U159" s="30"/>
-      <c r="V159" s="32"/>
+      <c r="O160" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S160" s="31"/>
+      <c r="T160" s="30"/>
+      <c r="U160" s="30"/>
+      <c r="V160" s="32"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -14386,17 +14454,17 @@
     <hyperlink ref="C71" r:id="rId1" xr:uid="{09689414-3477-4574-B4C1-145654B8F872}"/>
     <hyperlink ref="C9" r:id="rId2" xr:uid="{093A01EE-86EE-45C4-8EB3-9E2035175000}"/>
     <hyperlink ref="C31" r:id="rId3" xr:uid="{647907ED-3EF1-4900-B2E2-99B4EA674B9D}"/>
-    <hyperlink ref="C111" r:id="rId4" xr:uid="{FAE6907E-C81E-4A5D-817E-230B91B1B725}"/>
+    <hyperlink ref="C112" r:id="rId4" xr:uid="{FAE6907E-C81E-4A5D-817E-230B91B1B725}"/>
     <hyperlink ref="C60" r:id="rId5" xr:uid="{C753E4AB-C43C-4DA7-BCBB-4C6B42AE449C}"/>
-    <hyperlink ref="C146" r:id="rId6" xr:uid="{371EC661-68AD-4E55-A1EB-3AD1B3210212}"/>
-    <hyperlink ref="C145" r:id="rId7" xr:uid="{87EC244C-7916-48F7-AB46-F1434A4E3208}"/>
+    <hyperlink ref="C147" r:id="rId6" xr:uid="{371EC661-68AD-4E55-A1EB-3AD1B3210212}"/>
+    <hyperlink ref="C146" r:id="rId7" xr:uid="{87EC244C-7916-48F7-AB46-F1434A4E3208}"/>
     <hyperlink ref="C64" r:id="rId8" xr:uid="{C7C324AF-CD50-4932-996A-89F85253BFD5}"/>
     <hyperlink ref="C4" r:id="rId9" xr:uid="{EDB880A2-AA3E-4F26-A446-E9157F173772}"/>
     <hyperlink ref="C46" r:id="rId10" xr:uid="{9A17C16E-C332-458A-ADE6-19BE3A083F23}"/>
     <hyperlink ref="C53" r:id="rId11" xr:uid="{B6233385-F901-40C6-AEFB-2742E1A95C52}"/>
     <hyperlink ref="C6" r:id="rId12" xr:uid="{17CBE166-8555-4ADF-8563-DD807A994D87}"/>
     <hyperlink ref="C84" r:id="rId13" xr:uid="{5A5F426A-1EDA-41D8-B9CB-7227502B01CB}"/>
-    <hyperlink ref="C137" r:id="rId14" xr:uid="{82446CC2-3C94-440E-AAD6-8D54906361E8}"/>
+    <hyperlink ref="C138" r:id="rId14" xr:uid="{82446CC2-3C94-440E-AAD6-8D54906361E8}"/>
     <hyperlink ref="C26" r:id="rId15" xr:uid="{7A9FCCD8-8795-4FEF-A34B-74181A73AEB9}"/>
     <hyperlink ref="C42" r:id="rId16" xr:uid="{8EACE7F8-9420-4163-ABD1-0A6C80C10BC0}"/>
     <hyperlink ref="C48" r:id="rId17" xr:uid="{4E230D6B-A2E5-482B-847D-728150A3AAC3}"/>
@@ -14411,11 +14479,11 @@
     <hyperlink ref="C27" r:id="rId26" xr:uid="{D53591D3-EF0A-4301-B038-F4C64E0F14B1}"/>
     <hyperlink ref="C68" r:id="rId27" xr:uid="{6774AFFC-3F72-4FC8-83D4-C6E9745490F7}"/>
     <hyperlink ref="C39" r:id="rId28" xr:uid="{D01E6549-8C0C-4A44-AF08-ED09A47D4252}"/>
-    <hyperlink ref="C122" r:id="rId29" xr:uid="{DE66E60B-BA52-4BF5-91BF-04E031C85DF4}"/>
-    <hyperlink ref="C157" r:id="rId30" xr:uid="{6B7C0C1E-80A1-4C90-B400-939A08EB9E26}"/>
-    <hyperlink ref="C144" r:id="rId31" xr:uid="{39C94BCA-35A0-4C33-8523-A608427AF1AC}"/>
-    <hyperlink ref="C141" r:id="rId32" xr:uid="{0078D0DD-F4F6-49B0-885D-B066223BAE60}"/>
-    <hyperlink ref="C140" r:id="rId33" xr:uid="{C5712289-6DD8-4698-B94D-78A55B1677AB}"/>
+    <hyperlink ref="C123" r:id="rId29" xr:uid="{DE66E60B-BA52-4BF5-91BF-04E031C85DF4}"/>
+    <hyperlink ref="C158" r:id="rId30" xr:uid="{6B7C0C1E-80A1-4C90-B400-939A08EB9E26}"/>
+    <hyperlink ref="C145" r:id="rId31" xr:uid="{39C94BCA-35A0-4C33-8523-A608427AF1AC}"/>
+    <hyperlink ref="C142" r:id="rId32" xr:uid="{0078D0DD-F4F6-49B0-885D-B066223BAE60}"/>
+    <hyperlink ref="C141" r:id="rId33" xr:uid="{C5712289-6DD8-4698-B94D-78A55B1677AB}"/>
     <hyperlink ref="C56" r:id="rId34" xr:uid="{009176AE-ADE1-49A3-B8B5-187A70213738}"/>
     <hyperlink ref="C51" r:id="rId35" xr:uid="{53B27E08-A450-4488-BA16-0EBEE4AF4455}"/>
     <hyperlink ref="C55" r:id="rId36" xr:uid="{A5096D46-1AA5-4208-813B-8023926F7367}"/>
@@ -14439,225 +14507,227 @@
     <hyperlink ref="C96" r:id="rId54" xr:uid="{42BCD2DF-E790-4589-A30F-037C5CC98618}"/>
     <hyperlink ref="C97" r:id="rId55" xr:uid="{D04172B2-FA86-479A-B554-457A76AC12EB}"/>
     <hyperlink ref="C98" r:id="rId56" xr:uid="{4D285DE5-B50D-4CAB-A92F-4534B3369428}"/>
-    <hyperlink ref="C103" r:id="rId57" xr:uid="{4788DE4E-DD21-4F17-A0F5-F0127C036B93}"/>
-    <hyperlink ref="C105" r:id="rId58" xr:uid="{F8DE4A00-90C4-4883-8925-84D02A72603D}"/>
-    <hyperlink ref="C106" r:id="rId59" xr:uid="{537D1EAA-FB2D-4A1A-A7EF-263F86E9B731}"/>
-    <hyperlink ref="C110" r:id="rId60" xr:uid="{ACD371A2-0E1B-4667-A917-FB870D976F44}"/>
-    <hyperlink ref="C113" r:id="rId61" xr:uid="{280984BC-9AF6-43D6-B7C6-0B942360A963}"/>
-    <hyperlink ref="C114" r:id="rId62" xr:uid="{076877CE-8ABA-4EB5-BBFC-50357A612F35}"/>
-    <hyperlink ref="C119" r:id="rId63" xr:uid="{5628464F-D8DE-4F76-9B77-04A7AFF90F62}"/>
-    <hyperlink ref="C120" r:id="rId64" xr:uid="{03CB87A5-498E-4649-8556-4CBF15C6B9FD}"/>
-    <hyperlink ref="C126" r:id="rId65" xr:uid="{CF37847B-1569-47B2-9A5A-E969CE56BF8B}"/>
-    <hyperlink ref="C127" r:id="rId66" xr:uid="{434996DF-4908-4245-B541-2571CDFEF5CA}"/>
-    <hyperlink ref="C129" r:id="rId67" xr:uid="{7F8DD870-012B-4FA5-B272-8F9C10BE0F67}"/>
-    <hyperlink ref="C130" r:id="rId68" xr:uid="{811E91E6-D722-4048-979A-0A1B3944C89F}"/>
-    <hyperlink ref="C131" r:id="rId69" xr:uid="{D712678C-0ED2-435A-B50F-8727B237AA85}"/>
-    <hyperlink ref="C133" r:id="rId70" xr:uid="{23570306-858B-4CEB-A34A-C76767C43F2C}"/>
-    <hyperlink ref="C134" r:id="rId71" xr:uid="{8A4373FA-901A-4FE5-A250-36C1CBE1C863}"/>
-    <hyperlink ref="C135" r:id="rId72" xr:uid="{04465534-930B-4B39-A965-677749107D82}"/>
-    <hyperlink ref="C121" r:id="rId73" xr:uid="{54C7F5BF-5DB5-4C4D-AED8-A9EF695BADE3}"/>
-    <hyperlink ref="C123" r:id="rId74" xr:uid="{722E83D6-EBD5-4CA8-87EC-CF744B148F5E}"/>
-    <hyperlink ref="C7" r:id="rId75" xr:uid="{B9D7E0EF-7657-47FA-A60E-18C7906C6F64}"/>
-    <hyperlink ref="C24" r:id="rId76" xr:uid="{DF815018-1A91-4EEA-97A8-53FCF3C51484}"/>
-    <hyperlink ref="C32" r:id="rId77" xr:uid="{741DF32C-57B4-4296-8D2B-447F78C164E4}"/>
-    <hyperlink ref="C2" r:id="rId78" xr:uid="{9C1B3465-ED4E-4642-BA4D-5C7E5510B7B6}"/>
-    <hyperlink ref="C77" r:id="rId79" xr:uid="{AB3EAE1F-65EA-44FC-AB99-16D2D5ED71B3}"/>
-    <hyperlink ref="C155" r:id="rId80" xr:uid="{CF6EACC9-E6EB-45BD-B707-52712C2A62C9}"/>
-    <hyperlink ref="C104" r:id="rId81" xr:uid="{02D0ECDA-FD32-4CF7-8440-EC4C7DCD63E5}"/>
-    <hyperlink ref="C143" r:id="rId82" location=" " xr:uid="{2FFDF6BA-7A97-4D5C-9D4F-2CCB9C0E6DED}"/>
-    <hyperlink ref="C102" r:id="rId83" xr:uid="{7F7A3FF6-CCE9-4E2E-982B-1B4E31731333}"/>
-    <hyperlink ref="C34" r:id="rId84" xr:uid="{17D56B7A-25AE-48DC-87D5-86A3E9DAEC57}"/>
-    <hyperlink ref="C93" r:id="rId85" xr:uid="{D8CE449C-151D-4D39-B26F-B961900B9F5D}"/>
-    <hyperlink ref="C43" r:id="rId86" xr:uid="{8083253A-88C3-43D3-9D68-6E726A4F9587}"/>
-    <hyperlink ref="C80" r:id="rId87" xr:uid="{9E0E87F8-6FE5-4DF7-B96C-922AD4830E08}"/>
-    <hyperlink ref="C41" r:id="rId88" xr:uid="{4972827C-BEE0-44B4-A458-FDE24FCE89C0}"/>
-    <hyperlink ref="C40" r:id="rId89" xr:uid="{AA048B82-F6AA-4179-9DA8-92CB88AA34CD}"/>
-    <hyperlink ref="C37" r:id="rId90" xr:uid="{1218E00E-EF0C-494E-BECE-099FB05742E5}"/>
-    <hyperlink ref="C117" r:id="rId91" xr:uid="{860357C4-6C5E-4883-814C-F21FA9C924DE}"/>
-    <hyperlink ref="C124" r:id="rId92" xr:uid="{16AB466E-682E-47B8-A4E2-382FD289A028}"/>
-    <hyperlink ref="C125" r:id="rId93" xr:uid="{6DCCCDA1-E5B8-4573-BC96-2C385646B65F}"/>
-    <hyperlink ref="C128" r:id="rId94" xr:uid="{5ED2B850-5619-4803-9E96-99424F17CB82}"/>
-    <hyperlink ref="C132" r:id="rId95" xr:uid="{F046FA23-A48D-4FEC-B2CE-9AD00AACEB66}"/>
-    <hyperlink ref="C136" r:id="rId96" xr:uid="{1F850D9E-5286-41BA-90F6-0FD05DFBBBE5}"/>
-    <hyperlink ref="E4" r:id="rId97" xr:uid="{811C4818-C847-4731-BB38-2D52F1834045}"/>
-    <hyperlink ref="E18" r:id="rId98" xr:uid="{94100DD3-02BF-4E61-A172-C4A9D09569F8}"/>
-    <hyperlink ref="E22" r:id="rId99" location="s0035" xr:uid="{13AE09A2-4522-46D1-AC75-5B95A8D15C9C}"/>
-    <hyperlink ref="E58" r:id="rId100" xr:uid="{5C414BC3-1364-419D-9DDD-1A6F60C0D845}"/>
-    <hyperlink ref="E71" r:id="rId101" xr:uid="{C5A0DFB4-1FB7-49B8-8FD3-9AC01312958D}"/>
-    <hyperlink ref="E108" r:id="rId102" xr:uid="{51CBF759-50E7-428F-81D5-CB1BF0D6F9DE}"/>
-    <hyperlink ref="E139" r:id="rId103" xr:uid="{DD230CEE-1804-40FB-BD78-0C67303DB967}"/>
-    <hyperlink ref="E146" r:id="rId104" location="f0020" xr:uid="{3778DDB7-E612-4F6A-A3B0-B453CF8B64A9}"/>
-    <hyperlink ref="E101" r:id="rId105" xr:uid="{88E00939-FB4B-46C7-8C26-9BF914C2DEFC}"/>
-    <hyperlink ref="E122" r:id="rId106" xr:uid="{1BF75D9D-D348-4E2D-9C84-905D4A8F3B25}"/>
-    <hyperlink ref="E53" r:id="rId107" xr:uid="{731847B6-AFA8-4FD0-B2B9-DA4073CF6576}"/>
-    <hyperlink ref="E153" r:id="rId108" xr:uid="{A734FA6A-1E5E-4197-893E-26AEB8863486}"/>
-    <hyperlink ref="E149" r:id="rId109" xr:uid="{2DAAFB64-43EF-4609-9512-3EECAF83A0D8}"/>
-    <hyperlink ref="E21" r:id="rId110" location="s0035" xr:uid="{B0E30218-34ED-4F0F-8578-9A603C364391}"/>
-    <hyperlink ref="E154" r:id="rId111" xr:uid="{33D09351-6D20-4F3E-B2E7-73DE845CAB80}"/>
-    <hyperlink ref="E156" r:id="rId112" xr:uid="{BA5C5148-161B-4925-9347-1EBB2828D7A5}"/>
-    <hyperlink ref="E137" r:id="rId113" xr:uid="{686C1381-B3D9-4F4F-B355-F6C8BDA10898}"/>
-    <hyperlink ref="E81" r:id="rId114" xr:uid="{8A34E89F-B55C-44D1-9032-56436D05CE5D}"/>
-    <hyperlink ref="E35" r:id="rId115" xr:uid="{F267D5CF-D0FE-473C-A3F7-FECCC233A441}"/>
-    <hyperlink ref="E42" r:id="rId116" xr:uid="{442EB302-E477-4F77-B393-3E4D99A564E5}"/>
-    <hyperlink ref="E57" r:id="rId117" xr:uid="{D135E4D3-2F2E-469B-85FF-8BEC89A2618B}"/>
-    <hyperlink ref="E5" r:id="rId118" xr:uid="{12D8EB59-83CA-4597-928E-5FE6B23E156B}"/>
-    <hyperlink ref="E144" r:id="rId119" xr:uid="{81632F3A-005C-4176-BECE-2F3B9EEB6891}"/>
-    <hyperlink ref="E107" r:id="rId120" xr:uid="{37A04716-A03F-4D57-96D9-A5BFAD7D2359}"/>
-    <hyperlink ref="E142" r:id="rId121" xr:uid="{0E7FBF6C-CAA7-4FF2-A8EE-7F2D8A88BF96}"/>
-    <hyperlink ref="E150" r:id="rId122" xr:uid="{D55E6DD1-6984-4A50-A0AD-BA6FF596E41C}"/>
-    <hyperlink ref="E118" r:id="rId123" xr:uid="{2B877B96-8FD1-4F41-B88E-AD70830BE725}"/>
-    <hyperlink ref="E148" r:id="rId124" xr:uid="{7CB9413F-F297-47A4-B2F8-2E8BEC8F96E8}"/>
-    <hyperlink ref="E36" r:id="rId125" xr:uid="{FA27BDCB-DB0A-480B-876B-7B017E0E677B}"/>
-    <hyperlink ref="E31" r:id="rId126" xr:uid="{48520E64-60FA-43C7-9523-3F8A2187E6CC}"/>
-    <hyperlink ref="E33" r:id="rId127" xr:uid="{05E3211D-230E-48F4-BB1E-822C21AAAFED}"/>
-    <hyperlink ref="E70" r:id="rId128" xr:uid="{FD6A6FF4-BD3D-4A75-A3F7-C6081FFB6C91}"/>
-    <hyperlink ref="E91" r:id="rId129" xr:uid="{A79F7F03-9B5B-4489-B080-107B98530A6B}"/>
-    <hyperlink ref="E113" r:id="rId130" xr:uid="{F431B0F7-5D38-4E60-AD18-2B301C1F824A}"/>
-    <hyperlink ref="E114" r:id="rId131" xr:uid="{8D237475-1999-48E3-B25D-339AE9C8EDD4}"/>
-    <hyperlink ref="E120" r:id="rId132" xr:uid="{6CFEE99F-77B8-453F-B0EB-481B5544EB7E}"/>
-    <hyperlink ref="E121" r:id="rId133" xr:uid="{0095BCC3-FA71-4827-B8E0-87D678153928}"/>
-    <hyperlink ref="E39" r:id="rId134" xr:uid="{620BDACF-75EA-4500-BA77-23B953049278}"/>
-    <hyperlink ref="E116" r:id="rId135" xr:uid="{E4CE47AF-12EB-4DBE-9E99-0FABFC9402A8}"/>
-    <hyperlink ref="E138" r:id="rId136" xr:uid="{A59ECC74-526B-4136-A3D5-05BA9BB6787C}"/>
-    <hyperlink ref="E141" r:id="rId137" xr:uid="{D6FF6640-82FF-4A0D-A828-72ED67D3AD4F}"/>
-    <hyperlink ref="E157" r:id="rId138" xr:uid="{9B13D64B-97F0-4098-BAE2-F0343CD81A80}"/>
-    <hyperlink ref="E151" r:id="rId139" xr:uid="{BADE4669-D317-4460-B448-C8D94D35753B}"/>
-    <hyperlink ref="E145" r:id="rId140" xr:uid="{850A2301-83A8-46A6-86BC-61587D12CD21}"/>
-    <hyperlink ref="E140" r:id="rId141" xr:uid="{7E135D94-3307-4285-876D-E50B63D987DF}"/>
-    <hyperlink ref="E69" r:id="rId142" xr:uid="{1AED701A-018D-49C9-969C-0C378A17C522}"/>
-    <hyperlink ref="E74" r:id="rId143" xr:uid="{184F465E-B6F3-4207-8050-030FFF3C7183}"/>
-    <hyperlink ref="E44" r:id="rId144" xr:uid="{6543D113-650C-4476-8130-C0483837619C}"/>
-    <hyperlink ref="E45" r:id="rId145" xr:uid="{FF0B3ADF-CBF0-42B9-8D3E-864E6D620CF1}"/>
-    <hyperlink ref="E52" r:id="rId146" xr:uid="{3E97C6A8-683F-4E0F-B475-3D5C212C5AFB}"/>
-    <hyperlink ref="E46" r:id="rId147" xr:uid="{CCEC51F1-262A-4CCF-80C1-A2B666658C93}"/>
-    <hyperlink ref="E47" r:id="rId148" xr:uid="{C206D26F-C731-4AF1-BD04-B213908CD9B9}"/>
-    <hyperlink ref="E48" r:id="rId149" xr:uid="{14EDB458-A34B-4779-9965-F5FE1CCB50B4}"/>
-    <hyperlink ref="E49" r:id="rId150" xr:uid="{3E1D03BB-6005-4825-A023-802A774824DD}"/>
-    <hyperlink ref="E50" r:id="rId151" xr:uid="{D171B4DD-4752-4A1C-B749-476C3263BFA2}"/>
-    <hyperlink ref="E61" r:id="rId152" xr:uid="{C6824C04-CEDB-4179-8131-356484F7C66A}"/>
-    <hyperlink ref="E60" r:id="rId153" xr:uid="{F0A47980-178B-4307-BC06-208B0A0787C0}"/>
-    <hyperlink ref="E6" r:id="rId154" xr:uid="{006F9965-F9A0-4D18-8A5E-055D979E592B}"/>
-    <hyperlink ref="E7" r:id="rId155" xr:uid="{42036A72-05E5-4B54-A1E5-2DE4DEC53013}"/>
-    <hyperlink ref="E8" r:id="rId156" xr:uid="{30D4BCEA-77E7-4F67-9879-7D974DDCB30D}"/>
-    <hyperlink ref="E9" r:id="rId157" xr:uid="{27745033-13CE-45AE-B517-ECF515AB30D0}"/>
-    <hyperlink ref="E19" r:id="rId158" xr:uid="{652AB408-8BA1-4CFB-95EC-99AE53E42B68}"/>
-    <hyperlink ref="E24" r:id="rId159" xr:uid="{60B241F5-B00E-49A2-B401-FAD99BF0E300}"/>
-    <hyperlink ref="E26" r:id="rId160" xr:uid="{652270A6-F3A5-4CCF-ABA7-C14BC5C42423}"/>
-    <hyperlink ref="E27" r:id="rId161" xr:uid="{63180BA9-A5BF-48B3-9FB4-C4B440D39A56}"/>
-    <hyperlink ref="E28" r:id="rId162" xr:uid="{6F6B612D-7ED2-4FC1-8D0B-A4BB4951744D}"/>
-    <hyperlink ref="E30" r:id="rId163" xr:uid="{E69650D7-F915-46E1-8F1F-02B7FFB12F2E}"/>
-    <hyperlink ref="E32" r:id="rId164" xr:uid="{CA514BF8-8B41-4BFC-AC79-0B520CB3F2AC}"/>
-    <hyperlink ref="E54" r:id="rId165" xr:uid="{54FE9C2C-B8A0-4854-A022-1A7169CD0C72}"/>
-    <hyperlink ref="E62" r:id="rId166" xr:uid="{0C047F6E-8077-4EDF-9184-56251B4A40EC}"/>
-    <hyperlink ref="E63" r:id="rId167" xr:uid="{A883FFE8-5423-44FE-B5C8-56C449AB6627}"/>
-    <hyperlink ref="E66" r:id="rId168" xr:uid="{A14809D5-65CA-4A10-8330-439AF1AB07EB}"/>
-    <hyperlink ref="E67" r:id="rId169" xr:uid="{16F6BA4E-D132-404A-B8A5-6A4055D3B1DE}"/>
-    <hyperlink ref="E73" r:id="rId170" xr:uid="{ED6CF27F-6387-4DE6-BE4C-E850E5881B88}"/>
-    <hyperlink ref="E76" r:id="rId171" xr:uid="{E9B998E1-EC82-42B0-AACA-73FB4DD88CE9}"/>
-    <hyperlink ref="E84" r:id="rId172" xr:uid="{47645E3C-39E5-4CAC-8820-A7C6FD8B5579}"/>
-    <hyperlink ref="E85" r:id="rId173" xr:uid="{0625CF4F-DA2B-4EE7-A702-0219AD1C68CB}"/>
-    <hyperlink ref="E86" r:id="rId174" xr:uid="{0282C361-4DE5-48B1-9823-FCE619290498}"/>
-    <hyperlink ref="E88" r:id="rId175" xr:uid="{67DEF3F7-0CAA-4CD6-8D88-5F8DB78DE540}"/>
-    <hyperlink ref="E89" r:id="rId176" xr:uid="{D969C0A9-F9DD-4566-8223-41D811B4D5C6}"/>
-    <hyperlink ref="E90" r:id="rId177" xr:uid="{CA72B61B-2AF9-4500-84C6-0F0C62189095}"/>
-    <hyperlink ref="E94" r:id="rId178" xr:uid="{EC57EFF2-9F41-45C7-A332-FFA2687C3F75}"/>
-    <hyperlink ref="E95" r:id="rId179" xr:uid="{149A410F-01E9-4C9E-A3BF-8106E7830F57}"/>
-    <hyperlink ref="E96" r:id="rId180" xr:uid="{1AA34E58-053E-4462-B269-60B1C19E26FF}"/>
-    <hyperlink ref="E97" r:id="rId181" xr:uid="{BEF77FE6-2F82-47F6-B96C-ADAF84945125}"/>
-    <hyperlink ref="E98" r:id="rId182" xr:uid="{F2874A98-0A0B-45C2-8CD6-EA4A785A2370}"/>
-    <hyperlink ref="E103" r:id="rId183" xr:uid="{CA4C0D7C-9C19-4E48-A158-F4413BD6178C}"/>
-    <hyperlink ref="E105" r:id="rId184" xr:uid="{EEFF914F-ABA0-4E3C-9FD5-12FBECFDBB91}"/>
-    <hyperlink ref="E106" r:id="rId185" xr:uid="{88EE7216-4A06-465B-8FC6-606F50CBCFBC}"/>
-    <hyperlink ref="E109" r:id="rId186" xr:uid="{7BDEE9B8-5D7C-4202-B74C-6BE982C328AB}"/>
-    <hyperlink ref="E110" r:id="rId187" xr:uid="{77709C72-C9F9-499D-B133-6DF9E7E61890}"/>
-    <hyperlink ref="E111" r:id="rId188" xr:uid="{4F359565-B34E-4BD5-803D-7DC3D9732BAD}"/>
-    <hyperlink ref="E119" r:id="rId189" xr:uid="{A5574257-EDF9-4DC4-9A80-018F938B8B76}"/>
-    <hyperlink ref="E126" r:id="rId190" xr:uid="{E6837BC7-5BFC-4721-BAEC-5150ACC2E92A}"/>
-    <hyperlink ref="E127" r:id="rId191" xr:uid="{5AE70EB7-4DA2-4D5D-B00B-AE08DC919335}"/>
-    <hyperlink ref="E129" r:id="rId192" xr:uid="{C7A06CCF-1682-41F2-925C-4CCAC157C4E2}"/>
-    <hyperlink ref="E130" r:id="rId193" xr:uid="{2C04A538-B780-4A40-A836-B3954133A859}"/>
-    <hyperlink ref="E131" r:id="rId194" xr:uid="{533F3B58-531B-4E96-AF2B-08DB72D544CF}"/>
-    <hyperlink ref="E133" r:id="rId195" xr:uid="{62821B07-9EEB-41DA-A82A-CCDC6B6E1FB3}"/>
-    <hyperlink ref="E134" r:id="rId196" xr:uid="{B0802ADB-CF30-44C5-89E2-BCFA655BA70A}"/>
-    <hyperlink ref="E135" r:id="rId197" xr:uid="{9471BEB4-CC62-4A65-95D9-0E8F08554CFE}"/>
-    <hyperlink ref="E123" r:id="rId198" xr:uid="{349E9ACC-59EC-49C5-8729-16D1175BEF4F}"/>
-    <hyperlink ref="E68" r:id="rId199" xr:uid="{BB6956D7-23ED-4A46-A37D-A8372BE7A10E}"/>
-    <hyperlink ref="E2" r:id="rId200" xr:uid="{FA6C54D1-21A6-4366-A61A-B63E45510502}"/>
-    <hyperlink ref="E20" r:id="rId201" xr:uid="{1811DDC7-B1CB-48D6-97CC-8589C8A392B3}"/>
-    <hyperlink ref="E77" r:id="rId202" xr:uid="{C5DA3CF3-7B30-4A03-82DD-7F2E14081684}"/>
-    <hyperlink ref="E155" r:id="rId203" xr:uid="{7115DB7A-AE90-495D-9676-EA1BA0F179A0}"/>
-    <hyperlink ref="E104" r:id="rId204" xr:uid="{E875AA82-E9BD-43BA-B96A-443BE71A661D}"/>
-    <hyperlink ref="E143" r:id="rId205" display="https://standards.cencenelec.eu/dyn/www/f?p=CEN:110:0::::FSP_PROJECT,FSP_ORG_ID:67839,1991542&amp;cs=1BCE2DE4154949B53FB406C2D4EE5011D " xr:uid="{1198A376-FAFB-4B63-8F31-3CC40DDC0188}"/>
-    <hyperlink ref="E102" r:id="rId206" xr:uid="{CDB629AC-7318-4A45-902E-8C95EF4661CF}"/>
-    <hyperlink ref="E38" r:id="rId207" xr:uid="{F20CB13F-7541-474A-BB7F-D8B745D301C0}"/>
-    <hyperlink ref="E152" r:id="rId208" xr:uid="{62676230-6266-4D08-B848-64E61BE4B592}"/>
-    <hyperlink ref="E93" r:id="rId209" display="https://lov.linkeddata.es/dataset/lov/vocabs/jup/versions/2016-07-14.n3" xr:uid="{AE487E94-18DC-4254-BE84-4C41E95CF5BD}"/>
-    <hyperlink ref="E43" r:id="rId210" xr:uid="{3B2D46D8-B3FB-420A-B722-C4AE65399511}"/>
-    <hyperlink ref="E80" r:id="rId211" xr:uid="{CEDD056B-0AF1-476A-BD5E-3BDADF64D853}"/>
-    <hyperlink ref="E41" r:id="rId212" xr:uid="{5E225EF5-93E6-41EE-89D9-FFE8A5198461}"/>
-    <hyperlink ref="E40" r:id="rId213" xr:uid="{074596C3-DC36-46D9-B1FA-6177FB0CE294}"/>
-    <hyperlink ref="E37" r:id="rId214" xr:uid="{8839DCA9-B1C9-4B05-BAA3-2A9B25F26A93}"/>
-    <hyperlink ref="E117" r:id="rId215" xr:uid="{16B53E58-79E0-4B7C-AC2E-C71F2322D92F}"/>
-    <hyperlink ref="E79" r:id="rId216" xr:uid="{7E895DE5-2CE7-45C1-A136-57B4BCE29015}"/>
-    <hyperlink ref="E78" r:id="rId217" xr:uid="{47784ED5-2C28-44C3-81EB-31DA2532A95A}"/>
-    <hyperlink ref="E59" r:id="rId218" xr:uid="{D997BB59-BF3F-477F-A29B-A26EC0C6DB4C}"/>
-    <hyperlink ref="E124" r:id="rId219" xr:uid="{8B03E269-70CC-43E2-802D-196D1A76D2C6}"/>
-    <hyperlink ref="E125" r:id="rId220" xr:uid="{4CB1390B-88E8-414B-819B-3EBA1096C650}"/>
-    <hyperlink ref="E128" r:id="rId221" xr:uid="{7E0BEE99-7810-43FE-8B6E-F313CACD1280}"/>
-    <hyperlink ref="E132" r:id="rId222" xr:uid="{A941CDD9-0B08-4ACA-8885-324C2A700E2F}"/>
-    <hyperlink ref="E136" r:id="rId223" xr:uid="{4183CDB1-AB57-415B-91B7-AABB33124063}"/>
-    <hyperlink ref="E72" r:id="rId224" xr:uid="{BE8311D4-A8A6-4008-870A-9CEF9052ED5C}"/>
-    <hyperlink ref="C147" r:id="rId225" xr:uid="{8A2C5288-ADB4-463A-85BA-B1183BAF8DDF}"/>
-    <hyperlink ref="C66" r:id="rId226" xr:uid="{07F92C0D-DB82-4582-A72B-52659867C160}"/>
-    <hyperlink ref="C8" r:id="rId227" xr:uid="{A84DDA47-6ACC-464D-952D-0387101E0611}"/>
-    <hyperlink ref="C158" r:id="rId228" xr:uid="{AE033172-A711-4880-AB36-40FB9AE60B05}"/>
-    <hyperlink ref="C3" r:id="rId229" xr:uid="{87BD7AD7-F7D3-4FFD-A9E2-12853E86A7FE}"/>
-    <hyperlink ref="E3" r:id="rId230" xr:uid="{512DDB69-1C56-4690-B2D9-AC64B48E7A6E}"/>
-    <hyperlink ref="C65" r:id="rId231" xr:uid="{0F674644-7FE0-46D4-B1A3-3075C11E0658}"/>
-    <hyperlink ref="C75" r:id="rId232" xr:uid="{1EFCCF69-133B-446A-B214-3B92B837A2A4}"/>
-    <hyperlink ref="E75" r:id="rId233" xr:uid="{D09DEDB3-49E2-4C48-B494-81711DA43BF0}"/>
-    <hyperlink ref="C83" r:id="rId234" display="https://w3id.org/hmo" xr:uid="{E4AF1C6F-DF28-43F7-ACA9-70BE220B042B}"/>
-    <hyperlink ref="E83" r:id="rId235" xr:uid="{49B2000D-4C70-49FD-A5F3-84C8A5029347}"/>
-    <hyperlink ref="C148" r:id="rId236" xr:uid="{0D2D8DED-68FD-46CA-AE92-1461FF576E92}"/>
-    <hyperlink ref="C150" r:id="rId237" xr:uid="{290C515B-CDF1-463F-85EB-BCFC5378D1E4}"/>
-    <hyperlink ref="C149" r:id="rId238" xr:uid="{DFE53865-6A47-46EC-BB35-4A0B7009EA86}"/>
-    <hyperlink ref="C151" r:id="rId239" xr:uid="{54FC6350-1D41-40D1-85C1-5FEB82150346}"/>
-    <hyperlink ref="C152" r:id="rId240" xr:uid="{218ED3BE-F2B1-4A98-ADC4-F128684E3B28}"/>
-    <hyperlink ref="C153" r:id="rId241" xr:uid="{31E930C8-EAAF-4B34-8443-75427984FA75}"/>
-    <hyperlink ref="C115" r:id="rId242" xr:uid="{379FD10B-9650-463A-84C0-55B4727D7D47}"/>
-    <hyperlink ref="E115" r:id="rId243" xr:uid="{F803CDF1-49F8-4F15-83C4-1374EEB2B30A}"/>
-    <hyperlink ref="C100" r:id="rId244" xr:uid="{C5C87514-E810-480B-A94B-83BB9DAD7389}"/>
-    <hyperlink ref="C159" r:id="rId245" xr:uid="{6EEE95DA-9BE0-4E1F-8E9A-8A354ABF1F8F}"/>
-    <hyperlink ref="C23" r:id="rId246" xr:uid="{0379DD25-CEE8-4F75-8C9B-E81D3B61747B}"/>
-    <hyperlink ref="E23" r:id="rId247" xr:uid="{E2A3119B-37AA-43A8-A582-4ED028637960}"/>
-    <hyperlink ref="C10" r:id="rId248" xr:uid="{A32D057F-0E64-4CBF-9B62-C57706447D34}"/>
-    <hyperlink ref="E10" r:id="rId249" xr:uid="{A65F3CDA-CD7D-4433-A029-81CC9238D823}"/>
-    <hyperlink ref="C14" r:id="rId250" xr:uid="{CBACED67-B915-430A-ABFB-6E922C06F5DB}"/>
-    <hyperlink ref="E14" r:id="rId251" xr:uid="{D19A3F16-CA81-4C85-B42A-FE0EB7D29FD6}"/>
-    <hyperlink ref="E15" r:id="rId252" xr:uid="{892CE20C-2CEA-4A57-8CB2-DE1FFDF67484}"/>
-    <hyperlink ref="E12" r:id="rId253" xr:uid="{73DE6366-9616-419D-A431-4F1008663A9E}"/>
-    <hyperlink ref="E13" r:id="rId254" xr:uid="{FC638811-A0C3-41F5-B132-5E9AC65F5A04}"/>
-    <hyperlink ref="E11" r:id="rId255" xr:uid="{64C26841-E8E4-4556-A67D-888111E8C883}"/>
-    <hyperlink ref="C15" r:id="rId256" xr:uid="{EEE203C4-C0DB-4A31-9B51-43E0DFF8BE38}"/>
-    <hyperlink ref="C12" r:id="rId257" xr:uid="{9E4FAC27-1581-492F-A27D-78631630D968}"/>
-    <hyperlink ref="C13" r:id="rId258" xr:uid="{3E4C2CEC-A992-4071-8AE1-06983D54F46F}"/>
-    <hyperlink ref="C11" r:id="rId259" xr:uid="{39874698-1D5A-41F0-90EF-FA837F5C1B23}"/>
-    <hyperlink ref="C17" r:id="rId260" xr:uid="{CBF98465-F451-41BC-8811-E98E321BE048}"/>
-    <hyperlink ref="C16" r:id="rId261" xr:uid="{1C6A0EA2-A8D6-4C7E-8833-72CD216F91B6}"/>
-    <hyperlink ref="C87" r:id="rId262" xr:uid="{3EAB1B23-E180-46E2-9E59-CF59E174BE8D}"/>
-    <hyperlink ref="E87" r:id="rId263" xr:uid="{9C03D4EC-81F8-4A0E-AE28-7FCE9FEC76F3}"/>
-    <hyperlink ref="C25" r:id="rId264" xr:uid="{F18D5489-B8E3-498D-8754-A7EFD69CA755}"/>
-    <hyperlink ref="E25" r:id="rId265" xr:uid="{67F2FA68-03F0-4457-B9F2-784DD703595B}"/>
-    <hyperlink ref="E29" r:id="rId266" xr:uid="{04870334-A1AD-48DB-ADAC-FB5BD11031A6}"/>
-    <hyperlink ref="C29" r:id="rId267" xr:uid="{366A4D26-021B-4981-B78E-49DB8CD72564}"/>
-    <hyperlink ref="E92" r:id="rId268" xr:uid="{3662ADB9-2338-4A94-B9E0-12D4855B5699}"/>
-    <hyperlink ref="C92" r:id="rId269" xr:uid="{974B5868-BD71-41E2-A9C9-2CFC11BFCE7F}"/>
+    <hyperlink ref="C105" r:id="rId57" xr:uid="{F8DE4A00-90C4-4883-8925-84D02A72603D}"/>
+    <hyperlink ref="C106" r:id="rId58" xr:uid="{537D1EAA-FB2D-4A1A-A7EF-263F86E9B731}"/>
+    <hyperlink ref="C111" r:id="rId59" xr:uid="{ACD371A2-0E1B-4667-A917-FB870D976F44}"/>
+    <hyperlink ref="C114" r:id="rId60" xr:uid="{280984BC-9AF6-43D6-B7C6-0B942360A963}"/>
+    <hyperlink ref="C115" r:id="rId61" xr:uid="{076877CE-8ABA-4EB5-BBFC-50357A612F35}"/>
+    <hyperlink ref="C120" r:id="rId62" xr:uid="{5628464F-D8DE-4F76-9B77-04A7AFF90F62}"/>
+    <hyperlink ref="C121" r:id="rId63" xr:uid="{03CB87A5-498E-4649-8556-4CBF15C6B9FD}"/>
+    <hyperlink ref="C127" r:id="rId64" xr:uid="{CF37847B-1569-47B2-9A5A-E969CE56BF8B}"/>
+    <hyperlink ref="C128" r:id="rId65" xr:uid="{434996DF-4908-4245-B541-2571CDFEF5CA}"/>
+    <hyperlink ref="C130" r:id="rId66" xr:uid="{7F8DD870-012B-4FA5-B272-8F9C10BE0F67}"/>
+    <hyperlink ref="C131" r:id="rId67" xr:uid="{811E91E6-D722-4048-979A-0A1B3944C89F}"/>
+    <hyperlink ref="C132" r:id="rId68" xr:uid="{D712678C-0ED2-435A-B50F-8727B237AA85}"/>
+    <hyperlink ref="C134" r:id="rId69" xr:uid="{23570306-858B-4CEB-A34A-C76767C43F2C}"/>
+    <hyperlink ref="C135" r:id="rId70" xr:uid="{8A4373FA-901A-4FE5-A250-36C1CBE1C863}"/>
+    <hyperlink ref="C136" r:id="rId71" xr:uid="{04465534-930B-4B39-A965-677749107D82}"/>
+    <hyperlink ref="C122" r:id="rId72" xr:uid="{54C7F5BF-5DB5-4C4D-AED8-A9EF695BADE3}"/>
+    <hyperlink ref="C124" r:id="rId73" xr:uid="{722E83D6-EBD5-4CA8-87EC-CF744B148F5E}"/>
+    <hyperlink ref="C7" r:id="rId74" xr:uid="{B9D7E0EF-7657-47FA-A60E-18C7906C6F64}"/>
+    <hyperlink ref="C24" r:id="rId75" xr:uid="{DF815018-1A91-4EEA-97A8-53FCF3C51484}"/>
+    <hyperlink ref="C32" r:id="rId76" xr:uid="{741DF32C-57B4-4296-8D2B-447F78C164E4}"/>
+    <hyperlink ref="C2" r:id="rId77" xr:uid="{9C1B3465-ED4E-4642-BA4D-5C7E5510B7B6}"/>
+    <hyperlink ref="C77" r:id="rId78" xr:uid="{AB3EAE1F-65EA-44FC-AB99-16D2D5ED71B3}"/>
+    <hyperlink ref="C156" r:id="rId79" xr:uid="{CF6EACC9-E6EB-45BD-B707-52712C2A62C9}"/>
+    <hyperlink ref="C104" r:id="rId80" xr:uid="{02D0ECDA-FD32-4CF7-8440-EC4C7DCD63E5}"/>
+    <hyperlink ref="C144" r:id="rId81" location=" " xr:uid="{2FFDF6BA-7A97-4D5C-9D4F-2CCB9C0E6DED}"/>
+    <hyperlink ref="C102" r:id="rId82" xr:uid="{7F7A3FF6-CCE9-4E2E-982B-1B4E31731333}"/>
+    <hyperlink ref="C34" r:id="rId83" xr:uid="{17D56B7A-25AE-48DC-87D5-86A3E9DAEC57}"/>
+    <hyperlink ref="C93" r:id="rId84" xr:uid="{D8CE449C-151D-4D39-B26F-B961900B9F5D}"/>
+    <hyperlink ref="C43" r:id="rId85" xr:uid="{8083253A-88C3-43D3-9D68-6E726A4F9587}"/>
+    <hyperlink ref="C80" r:id="rId86" xr:uid="{9E0E87F8-6FE5-4DF7-B96C-922AD4830E08}"/>
+    <hyperlink ref="C41" r:id="rId87" xr:uid="{4972827C-BEE0-44B4-A458-FDE24FCE89C0}"/>
+    <hyperlink ref="C40" r:id="rId88" xr:uid="{AA048B82-F6AA-4179-9DA8-92CB88AA34CD}"/>
+    <hyperlink ref="C37" r:id="rId89" xr:uid="{1218E00E-EF0C-494E-BECE-099FB05742E5}"/>
+    <hyperlink ref="C118" r:id="rId90" xr:uid="{860357C4-6C5E-4883-814C-F21FA9C924DE}"/>
+    <hyperlink ref="C125" r:id="rId91" xr:uid="{16AB466E-682E-47B8-A4E2-382FD289A028}"/>
+    <hyperlink ref="C126" r:id="rId92" xr:uid="{6DCCCDA1-E5B8-4573-BC96-2C385646B65F}"/>
+    <hyperlink ref="C129" r:id="rId93" xr:uid="{5ED2B850-5619-4803-9E96-99424F17CB82}"/>
+    <hyperlink ref="C133" r:id="rId94" xr:uid="{F046FA23-A48D-4FEC-B2CE-9AD00AACEB66}"/>
+    <hyperlink ref="C137" r:id="rId95" xr:uid="{1F850D9E-5286-41BA-90F6-0FD05DFBBBE5}"/>
+    <hyperlink ref="E4" r:id="rId96" xr:uid="{811C4818-C847-4731-BB38-2D52F1834045}"/>
+    <hyperlink ref="E18" r:id="rId97" xr:uid="{94100DD3-02BF-4E61-A172-C4A9D09569F8}"/>
+    <hyperlink ref="E22" r:id="rId98" location="s0035" xr:uid="{13AE09A2-4522-46D1-AC75-5B95A8D15C9C}"/>
+    <hyperlink ref="E58" r:id="rId99" xr:uid="{5C414BC3-1364-419D-9DDD-1A6F60C0D845}"/>
+    <hyperlink ref="E71" r:id="rId100" xr:uid="{C5A0DFB4-1FB7-49B8-8FD3-9AC01312958D}"/>
+    <hyperlink ref="E109" r:id="rId101" xr:uid="{51CBF759-50E7-428F-81D5-CB1BF0D6F9DE}"/>
+    <hyperlink ref="E140" r:id="rId102" xr:uid="{DD230CEE-1804-40FB-BD78-0C67303DB967}"/>
+    <hyperlink ref="E147" r:id="rId103" location="f0020" xr:uid="{3778DDB7-E612-4F6A-A3B0-B453CF8B64A9}"/>
+    <hyperlink ref="E101" r:id="rId104" xr:uid="{88E00939-FB4B-46C7-8C26-9BF914C2DEFC}"/>
+    <hyperlink ref="E123" r:id="rId105" xr:uid="{1BF75D9D-D348-4E2D-9C84-905D4A8F3B25}"/>
+    <hyperlink ref="E53" r:id="rId106" xr:uid="{731847B6-AFA8-4FD0-B2B9-DA4073CF6576}"/>
+    <hyperlink ref="E154" r:id="rId107" xr:uid="{A734FA6A-1E5E-4197-893E-26AEB8863486}"/>
+    <hyperlink ref="E150" r:id="rId108" xr:uid="{2DAAFB64-43EF-4609-9512-3EECAF83A0D8}"/>
+    <hyperlink ref="E21" r:id="rId109" location="s0035" xr:uid="{B0E30218-34ED-4F0F-8578-9A603C364391}"/>
+    <hyperlink ref="E155" r:id="rId110" xr:uid="{33D09351-6D20-4F3E-B2E7-73DE845CAB80}"/>
+    <hyperlink ref="E157" r:id="rId111" xr:uid="{BA5C5148-161B-4925-9347-1EBB2828D7A5}"/>
+    <hyperlink ref="E138" r:id="rId112" xr:uid="{686C1381-B3D9-4F4F-B355-F6C8BDA10898}"/>
+    <hyperlink ref="E81" r:id="rId113" xr:uid="{8A34E89F-B55C-44D1-9032-56436D05CE5D}"/>
+    <hyperlink ref="E35" r:id="rId114" xr:uid="{F267D5CF-D0FE-473C-A3F7-FECCC233A441}"/>
+    <hyperlink ref="E42" r:id="rId115" xr:uid="{442EB302-E477-4F77-B393-3E4D99A564E5}"/>
+    <hyperlink ref="E57" r:id="rId116" xr:uid="{D135E4D3-2F2E-469B-85FF-8BEC89A2618B}"/>
+    <hyperlink ref="E5" r:id="rId117" xr:uid="{12D8EB59-83CA-4597-928E-5FE6B23E156B}"/>
+    <hyperlink ref="E145" r:id="rId118" xr:uid="{81632F3A-005C-4176-BECE-2F3B9EEB6891}"/>
+    <hyperlink ref="E107" r:id="rId119" xr:uid="{37A04716-A03F-4D57-96D9-A5BFAD7D2359}"/>
+    <hyperlink ref="E143" r:id="rId120" xr:uid="{0E7FBF6C-CAA7-4FF2-A8EE-7F2D8A88BF96}"/>
+    <hyperlink ref="E151" r:id="rId121" xr:uid="{D55E6DD1-6984-4A50-A0AD-BA6FF596E41C}"/>
+    <hyperlink ref="E119" r:id="rId122" xr:uid="{2B877B96-8FD1-4F41-B88E-AD70830BE725}"/>
+    <hyperlink ref="E149" r:id="rId123" xr:uid="{7CB9413F-F297-47A4-B2F8-2E8BEC8F96E8}"/>
+    <hyperlink ref="E36" r:id="rId124" xr:uid="{FA27BDCB-DB0A-480B-876B-7B017E0E677B}"/>
+    <hyperlink ref="E31" r:id="rId125" xr:uid="{48520E64-60FA-43C7-9523-3F8A2187E6CC}"/>
+    <hyperlink ref="E33" r:id="rId126" xr:uid="{05E3211D-230E-48F4-BB1E-822C21AAAFED}"/>
+    <hyperlink ref="E70" r:id="rId127" xr:uid="{FD6A6FF4-BD3D-4A75-A3F7-C6081FFB6C91}"/>
+    <hyperlink ref="E91" r:id="rId128" xr:uid="{A79F7F03-9B5B-4489-B080-107B98530A6B}"/>
+    <hyperlink ref="E114" r:id="rId129" xr:uid="{F431B0F7-5D38-4E60-AD18-2B301C1F824A}"/>
+    <hyperlink ref="E115" r:id="rId130" xr:uid="{8D237475-1999-48E3-B25D-339AE9C8EDD4}"/>
+    <hyperlink ref="E121" r:id="rId131" xr:uid="{6CFEE99F-77B8-453F-B0EB-481B5544EB7E}"/>
+    <hyperlink ref="E122" r:id="rId132" xr:uid="{0095BCC3-FA71-4827-B8E0-87D678153928}"/>
+    <hyperlink ref="E39" r:id="rId133" xr:uid="{620BDACF-75EA-4500-BA77-23B953049278}"/>
+    <hyperlink ref="E117" r:id="rId134" xr:uid="{E4CE47AF-12EB-4DBE-9E99-0FABFC9402A8}"/>
+    <hyperlink ref="E139" r:id="rId135" xr:uid="{A59ECC74-526B-4136-A3D5-05BA9BB6787C}"/>
+    <hyperlink ref="E142" r:id="rId136" xr:uid="{D6FF6640-82FF-4A0D-A828-72ED67D3AD4F}"/>
+    <hyperlink ref="E158" r:id="rId137" xr:uid="{9B13D64B-97F0-4098-BAE2-F0343CD81A80}"/>
+    <hyperlink ref="E152" r:id="rId138" xr:uid="{BADE4669-D317-4460-B448-C8D94D35753B}"/>
+    <hyperlink ref="E146" r:id="rId139" xr:uid="{850A2301-83A8-46A6-86BC-61587D12CD21}"/>
+    <hyperlink ref="E141" r:id="rId140" xr:uid="{7E135D94-3307-4285-876D-E50B63D987DF}"/>
+    <hyperlink ref="E69" r:id="rId141" xr:uid="{1AED701A-018D-49C9-969C-0C378A17C522}"/>
+    <hyperlink ref="E74" r:id="rId142" xr:uid="{184F465E-B6F3-4207-8050-030FFF3C7183}"/>
+    <hyperlink ref="E44" r:id="rId143" xr:uid="{6543D113-650C-4476-8130-C0483837619C}"/>
+    <hyperlink ref="E45" r:id="rId144" xr:uid="{FF0B3ADF-CBF0-42B9-8D3E-864E6D620CF1}"/>
+    <hyperlink ref="E52" r:id="rId145" xr:uid="{3E97C6A8-683F-4E0F-B475-3D5C212C5AFB}"/>
+    <hyperlink ref="E46" r:id="rId146" xr:uid="{CCEC51F1-262A-4CCF-80C1-A2B666658C93}"/>
+    <hyperlink ref="E47" r:id="rId147" xr:uid="{C206D26F-C731-4AF1-BD04-B213908CD9B9}"/>
+    <hyperlink ref="E48" r:id="rId148" xr:uid="{14EDB458-A34B-4779-9965-F5FE1CCB50B4}"/>
+    <hyperlink ref="E49" r:id="rId149" xr:uid="{3E1D03BB-6005-4825-A023-802A774824DD}"/>
+    <hyperlink ref="E50" r:id="rId150" xr:uid="{D171B4DD-4752-4A1C-B749-476C3263BFA2}"/>
+    <hyperlink ref="E61" r:id="rId151" xr:uid="{C6824C04-CEDB-4179-8131-356484F7C66A}"/>
+    <hyperlink ref="E60" r:id="rId152" xr:uid="{F0A47980-178B-4307-BC06-208B0A0787C0}"/>
+    <hyperlink ref="E6" r:id="rId153" xr:uid="{006F9965-F9A0-4D18-8A5E-055D979E592B}"/>
+    <hyperlink ref="E7" r:id="rId154" xr:uid="{42036A72-05E5-4B54-A1E5-2DE4DEC53013}"/>
+    <hyperlink ref="E8" r:id="rId155" xr:uid="{30D4BCEA-77E7-4F67-9879-7D974DDCB30D}"/>
+    <hyperlink ref="E9" r:id="rId156" xr:uid="{27745033-13CE-45AE-B517-ECF515AB30D0}"/>
+    <hyperlink ref="E19" r:id="rId157" xr:uid="{652AB408-8BA1-4CFB-95EC-99AE53E42B68}"/>
+    <hyperlink ref="E24" r:id="rId158" xr:uid="{60B241F5-B00E-49A2-B401-FAD99BF0E300}"/>
+    <hyperlink ref="E26" r:id="rId159" xr:uid="{652270A6-F3A5-4CCF-ABA7-C14BC5C42423}"/>
+    <hyperlink ref="E27" r:id="rId160" xr:uid="{63180BA9-A5BF-48B3-9FB4-C4B440D39A56}"/>
+    <hyperlink ref="E28" r:id="rId161" xr:uid="{6F6B612D-7ED2-4FC1-8D0B-A4BB4951744D}"/>
+    <hyperlink ref="E30" r:id="rId162" xr:uid="{E69650D7-F915-46E1-8F1F-02B7FFB12F2E}"/>
+    <hyperlink ref="E32" r:id="rId163" xr:uid="{CA514BF8-8B41-4BFC-AC79-0B520CB3F2AC}"/>
+    <hyperlink ref="E54" r:id="rId164" xr:uid="{54FE9C2C-B8A0-4854-A022-1A7169CD0C72}"/>
+    <hyperlink ref="E62" r:id="rId165" xr:uid="{0C047F6E-8077-4EDF-9184-56251B4A40EC}"/>
+    <hyperlink ref="E63" r:id="rId166" xr:uid="{A883FFE8-5423-44FE-B5C8-56C449AB6627}"/>
+    <hyperlink ref="E66" r:id="rId167" xr:uid="{A14809D5-65CA-4A10-8330-439AF1AB07EB}"/>
+    <hyperlink ref="E67" r:id="rId168" xr:uid="{16F6BA4E-D132-404A-B8A5-6A4055D3B1DE}"/>
+    <hyperlink ref="E73" r:id="rId169" xr:uid="{ED6CF27F-6387-4DE6-BE4C-E850E5881B88}"/>
+    <hyperlink ref="E76" r:id="rId170" xr:uid="{E9B998E1-EC82-42B0-AACA-73FB4DD88CE9}"/>
+    <hyperlink ref="E84" r:id="rId171" xr:uid="{47645E3C-39E5-4CAC-8820-A7C6FD8B5579}"/>
+    <hyperlink ref="E85" r:id="rId172" xr:uid="{0625CF4F-DA2B-4EE7-A702-0219AD1C68CB}"/>
+    <hyperlink ref="E86" r:id="rId173" xr:uid="{0282C361-4DE5-48B1-9823-FCE619290498}"/>
+    <hyperlink ref="E88" r:id="rId174" xr:uid="{67DEF3F7-0CAA-4CD6-8D88-5F8DB78DE540}"/>
+    <hyperlink ref="E89" r:id="rId175" xr:uid="{D969C0A9-F9DD-4566-8223-41D811B4D5C6}"/>
+    <hyperlink ref="E90" r:id="rId176" xr:uid="{CA72B61B-2AF9-4500-84C6-0F0C62189095}"/>
+    <hyperlink ref="E94" r:id="rId177" xr:uid="{EC57EFF2-9F41-45C7-A332-FFA2687C3F75}"/>
+    <hyperlink ref="E95" r:id="rId178" xr:uid="{149A410F-01E9-4C9E-A3BF-8106E7830F57}"/>
+    <hyperlink ref="E96" r:id="rId179" xr:uid="{1AA34E58-053E-4462-B269-60B1C19E26FF}"/>
+    <hyperlink ref="E97" r:id="rId180" xr:uid="{BEF77FE6-2F82-47F6-B96C-ADAF84945125}"/>
+    <hyperlink ref="E98" r:id="rId181" xr:uid="{F2874A98-0A0B-45C2-8CD6-EA4A785A2370}"/>
+    <hyperlink ref="E103" r:id="rId182" xr:uid="{CA4C0D7C-9C19-4E48-A158-F4413BD6178C}"/>
+    <hyperlink ref="E105" r:id="rId183" xr:uid="{EEFF914F-ABA0-4E3C-9FD5-12FBECFDBB91}"/>
+    <hyperlink ref="E106" r:id="rId184" xr:uid="{88EE7216-4A06-465B-8FC6-606F50CBCFBC}"/>
+    <hyperlink ref="E110" r:id="rId185" xr:uid="{7BDEE9B8-5D7C-4202-B74C-6BE982C328AB}"/>
+    <hyperlink ref="E111" r:id="rId186" xr:uid="{77709C72-C9F9-499D-B133-6DF9E7E61890}"/>
+    <hyperlink ref="E112" r:id="rId187" xr:uid="{4F359565-B34E-4BD5-803D-7DC3D9732BAD}"/>
+    <hyperlink ref="E120" r:id="rId188" xr:uid="{A5574257-EDF9-4DC4-9A80-018F938B8B76}"/>
+    <hyperlink ref="E127" r:id="rId189" xr:uid="{E6837BC7-5BFC-4721-BAEC-5150ACC2E92A}"/>
+    <hyperlink ref="E128" r:id="rId190" xr:uid="{5AE70EB7-4DA2-4D5D-B00B-AE08DC919335}"/>
+    <hyperlink ref="E130" r:id="rId191" xr:uid="{C7A06CCF-1682-41F2-925C-4CCAC157C4E2}"/>
+    <hyperlink ref="E131" r:id="rId192" xr:uid="{2C04A538-B780-4A40-A836-B3954133A859}"/>
+    <hyperlink ref="E132" r:id="rId193" xr:uid="{533F3B58-531B-4E96-AF2B-08DB72D544CF}"/>
+    <hyperlink ref="E134" r:id="rId194" xr:uid="{62821B07-9EEB-41DA-A82A-CCDC6B6E1FB3}"/>
+    <hyperlink ref="E135" r:id="rId195" xr:uid="{B0802ADB-CF30-44C5-89E2-BCFA655BA70A}"/>
+    <hyperlink ref="E136" r:id="rId196" xr:uid="{9471BEB4-CC62-4A65-95D9-0E8F08554CFE}"/>
+    <hyperlink ref="E124" r:id="rId197" xr:uid="{349E9ACC-59EC-49C5-8729-16D1175BEF4F}"/>
+    <hyperlink ref="E68" r:id="rId198" xr:uid="{BB6956D7-23ED-4A46-A37D-A8372BE7A10E}"/>
+    <hyperlink ref="E2" r:id="rId199" xr:uid="{FA6C54D1-21A6-4366-A61A-B63E45510502}"/>
+    <hyperlink ref="E20" r:id="rId200" xr:uid="{1811DDC7-B1CB-48D6-97CC-8589C8A392B3}"/>
+    <hyperlink ref="E77" r:id="rId201" xr:uid="{C5DA3CF3-7B30-4A03-82DD-7F2E14081684}"/>
+    <hyperlink ref="E156" r:id="rId202" xr:uid="{7115DB7A-AE90-495D-9676-EA1BA0F179A0}"/>
+    <hyperlink ref="E104" r:id="rId203" xr:uid="{E875AA82-E9BD-43BA-B96A-443BE71A661D}"/>
+    <hyperlink ref="E144" r:id="rId204" display="https://standards.cencenelec.eu/dyn/www/f?p=CEN:110:0::::FSP_PROJECT,FSP_ORG_ID:67839,1991542&amp;cs=1BCE2DE4154949B53FB406C2D4EE5011D " xr:uid="{1198A376-FAFB-4B63-8F31-3CC40DDC0188}"/>
+    <hyperlink ref="E102" r:id="rId205" xr:uid="{CDB629AC-7318-4A45-902E-8C95EF4661CF}"/>
+    <hyperlink ref="E38" r:id="rId206" xr:uid="{F20CB13F-7541-474A-BB7F-D8B745D301C0}"/>
+    <hyperlink ref="E153" r:id="rId207" xr:uid="{62676230-6266-4D08-B848-64E61BE4B592}"/>
+    <hyperlink ref="E93" r:id="rId208" display="https://lov.linkeddata.es/dataset/lov/vocabs/jup/versions/2016-07-14.n3" xr:uid="{AE487E94-18DC-4254-BE84-4C41E95CF5BD}"/>
+    <hyperlink ref="E43" r:id="rId209" xr:uid="{3B2D46D8-B3FB-420A-B722-C4AE65399511}"/>
+    <hyperlink ref="E80" r:id="rId210" xr:uid="{CEDD056B-0AF1-476A-BD5E-3BDADF64D853}"/>
+    <hyperlink ref="E41" r:id="rId211" xr:uid="{5E225EF5-93E6-41EE-89D9-FFE8A5198461}"/>
+    <hyperlink ref="E40" r:id="rId212" xr:uid="{074596C3-DC36-46D9-B1FA-6177FB0CE294}"/>
+    <hyperlink ref="E37" r:id="rId213" xr:uid="{8839DCA9-B1C9-4B05-BAA3-2A9B25F26A93}"/>
+    <hyperlink ref="E118" r:id="rId214" xr:uid="{16B53E58-79E0-4B7C-AC2E-C71F2322D92F}"/>
+    <hyperlink ref="E79" r:id="rId215" xr:uid="{7E895DE5-2CE7-45C1-A136-57B4BCE29015}"/>
+    <hyperlink ref="E78" r:id="rId216" xr:uid="{47784ED5-2C28-44C3-81EB-31DA2532A95A}"/>
+    <hyperlink ref="E59" r:id="rId217" xr:uid="{D997BB59-BF3F-477F-A29B-A26EC0C6DB4C}"/>
+    <hyperlink ref="E125" r:id="rId218" xr:uid="{8B03E269-70CC-43E2-802D-196D1A76D2C6}"/>
+    <hyperlink ref="E126" r:id="rId219" xr:uid="{4CB1390B-88E8-414B-819B-3EBA1096C650}"/>
+    <hyperlink ref="E129" r:id="rId220" xr:uid="{7E0BEE99-7810-43FE-8B6E-F313CACD1280}"/>
+    <hyperlink ref="E133" r:id="rId221" xr:uid="{A941CDD9-0B08-4ACA-8885-324C2A700E2F}"/>
+    <hyperlink ref="E137" r:id="rId222" xr:uid="{4183CDB1-AB57-415B-91B7-AABB33124063}"/>
+    <hyperlink ref="E72" r:id="rId223" xr:uid="{BE8311D4-A8A6-4008-870A-9CEF9052ED5C}"/>
+    <hyperlink ref="C148" r:id="rId224" xr:uid="{8A2C5288-ADB4-463A-85BA-B1183BAF8DDF}"/>
+    <hyperlink ref="C66" r:id="rId225" xr:uid="{07F92C0D-DB82-4582-A72B-52659867C160}"/>
+    <hyperlink ref="C8" r:id="rId226" xr:uid="{A84DDA47-6ACC-464D-952D-0387101E0611}"/>
+    <hyperlink ref="C159" r:id="rId227" xr:uid="{AE033172-A711-4880-AB36-40FB9AE60B05}"/>
+    <hyperlink ref="C3" r:id="rId228" xr:uid="{87BD7AD7-F7D3-4FFD-A9E2-12853E86A7FE}"/>
+    <hyperlink ref="E3" r:id="rId229" xr:uid="{512DDB69-1C56-4690-B2D9-AC64B48E7A6E}"/>
+    <hyperlink ref="C65" r:id="rId230" xr:uid="{0F674644-7FE0-46D4-B1A3-3075C11E0658}"/>
+    <hyperlink ref="C75" r:id="rId231" xr:uid="{1EFCCF69-133B-446A-B214-3B92B837A2A4}"/>
+    <hyperlink ref="E75" r:id="rId232" xr:uid="{D09DEDB3-49E2-4C48-B494-81711DA43BF0}"/>
+    <hyperlink ref="C83" r:id="rId233" display="https://w3id.org/hmo" xr:uid="{E4AF1C6F-DF28-43F7-ACA9-70BE220B042B}"/>
+    <hyperlink ref="E83" r:id="rId234" xr:uid="{49B2000D-4C70-49FD-A5F3-84C8A5029347}"/>
+    <hyperlink ref="C149" r:id="rId235" xr:uid="{0D2D8DED-68FD-46CA-AE92-1461FF576E92}"/>
+    <hyperlink ref="C151" r:id="rId236" xr:uid="{290C515B-CDF1-463F-85EB-BCFC5378D1E4}"/>
+    <hyperlink ref="C150" r:id="rId237" xr:uid="{DFE53865-6A47-46EC-BB35-4A0B7009EA86}"/>
+    <hyperlink ref="C152" r:id="rId238" xr:uid="{54FC6350-1D41-40D1-85C1-5FEB82150346}"/>
+    <hyperlink ref="C153" r:id="rId239" xr:uid="{218ED3BE-F2B1-4A98-ADC4-F128684E3B28}"/>
+    <hyperlink ref="C154" r:id="rId240" xr:uid="{31E930C8-EAAF-4B34-8443-75427984FA75}"/>
+    <hyperlink ref="C116" r:id="rId241" xr:uid="{379FD10B-9650-463A-84C0-55B4727D7D47}"/>
+    <hyperlink ref="E116" r:id="rId242" xr:uid="{F803CDF1-49F8-4F15-83C4-1374EEB2B30A}"/>
+    <hyperlink ref="C100" r:id="rId243" xr:uid="{C5C87514-E810-480B-A94B-83BB9DAD7389}"/>
+    <hyperlink ref="C160" r:id="rId244" xr:uid="{6EEE95DA-9BE0-4E1F-8E9A-8A354ABF1F8F}"/>
+    <hyperlink ref="C23" r:id="rId245" xr:uid="{0379DD25-CEE8-4F75-8C9B-E81D3B61747B}"/>
+    <hyperlink ref="E23" r:id="rId246" xr:uid="{E2A3119B-37AA-43A8-A582-4ED028637960}"/>
+    <hyperlink ref="C10" r:id="rId247" xr:uid="{A32D057F-0E64-4CBF-9B62-C57706447D34}"/>
+    <hyperlink ref="E10" r:id="rId248" xr:uid="{A65F3CDA-CD7D-4433-A029-81CC9238D823}"/>
+    <hyperlink ref="C14" r:id="rId249" xr:uid="{CBACED67-B915-430A-ABFB-6E922C06F5DB}"/>
+    <hyperlink ref="E14" r:id="rId250" xr:uid="{D19A3F16-CA81-4C85-B42A-FE0EB7D29FD6}"/>
+    <hyperlink ref="E15" r:id="rId251" xr:uid="{892CE20C-2CEA-4A57-8CB2-DE1FFDF67484}"/>
+    <hyperlink ref="E12" r:id="rId252" xr:uid="{73DE6366-9616-419D-A431-4F1008663A9E}"/>
+    <hyperlink ref="E13" r:id="rId253" xr:uid="{FC638811-A0C3-41F5-B132-5E9AC65F5A04}"/>
+    <hyperlink ref="E11" r:id="rId254" xr:uid="{64C26841-E8E4-4556-A67D-888111E8C883}"/>
+    <hyperlink ref="C15" r:id="rId255" xr:uid="{EEE203C4-C0DB-4A31-9B51-43E0DFF8BE38}"/>
+    <hyperlink ref="C12" r:id="rId256" xr:uid="{9E4FAC27-1581-492F-A27D-78631630D968}"/>
+    <hyperlink ref="C13" r:id="rId257" xr:uid="{3E4C2CEC-A992-4071-8AE1-06983D54F46F}"/>
+    <hyperlink ref="C11" r:id="rId258" xr:uid="{39874698-1D5A-41F0-90EF-FA837F5C1B23}"/>
+    <hyperlink ref="C17" r:id="rId259" xr:uid="{CBF98465-F451-41BC-8811-E98E321BE048}"/>
+    <hyperlink ref="C16" r:id="rId260" xr:uid="{1C6A0EA2-A8D6-4C7E-8833-72CD216F91B6}"/>
+    <hyperlink ref="C87" r:id="rId261" xr:uid="{3EAB1B23-E180-46E2-9E59-CF59E174BE8D}"/>
+    <hyperlink ref="E87" r:id="rId262" xr:uid="{9C03D4EC-81F8-4A0E-AE28-7FCE9FEC76F3}"/>
+    <hyperlink ref="C25" r:id="rId263" xr:uid="{F18D5489-B8E3-498D-8754-A7EFD69CA755}"/>
+    <hyperlink ref="E25" r:id="rId264" xr:uid="{67F2FA68-03F0-4457-B9F2-784DD703595B}"/>
+    <hyperlink ref="E29" r:id="rId265" xr:uid="{04870334-A1AD-48DB-ADAC-FB5BD11031A6}"/>
+    <hyperlink ref="C29" r:id="rId266" xr:uid="{366A4D26-021B-4981-B78E-49DB8CD72564}"/>
+    <hyperlink ref="E92" r:id="rId267" xr:uid="{3662ADB9-2338-4A94-B9E0-12D4855B5699}"/>
+    <hyperlink ref="C92" r:id="rId268" xr:uid="{974B5868-BD71-41E2-A9C9-2CFC11BFCE7F}"/>
+    <hyperlink ref="C108" r:id="rId269" xr:uid="{8FBB5FBA-13BC-43C3-B062-F0D13FB9E1AF}"/>
+    <hyperlink ref="E108" r:id="rId270" display="https://github.com/RUB-Informatik-im-Bauwesen/ontobpr" xr:uid="{C4A389CC-BE51-4488-8EDC-9866A1041CA5}"/>
+    <hyperlink ref="C103" r:id="rId271" xr:uid="{4788DE4E-DD21-4F17-A0F5-F0127C036B93}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId270"/>
-  <legacyDrawing r:id="rId271"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId272"/>
+  <legacyDrawing r:id="rId273"/>
   <tableParts count="1">
-    <tablePart r:id="rId272"/>
+    <tablePart r:id="rId274"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -14666,7 +14736,7 @@
           <x14:formula1>
             <xm:f>Domains!$A$2:$A$28</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:H2 G4:H53 G55:H62 G64:H69 G71:H158 G159</xm:sqref>
+          <xm:sqref>G2:H2 G4:H53 G55:H62 G64:H69 G71:H158 G159:G160</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -14684,12 +14754,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -14719,7 +14789,7 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -14754,17 +14824,17 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -14774,7 +14844,7 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
@@ -14794,7 +14864,7 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -14809,12 +14879,12 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
@@ -14836,13 +14906,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e06419a-bc24-4bca-aaf1-3b90bf7d837a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15050,20 +15119,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e06419a-bc24-4bca-aaf1-3b90bf7d837a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CBC734A-37E0-4A55-B328-89CFAE297459}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1E73802-DE0F-482B-8B75-044CD712CFB1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7e06419a-bc24-4bca-aaf1-3b90bf7d837a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -15087,9 +15155,11 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1E73802-DE0F-482B-8B75-044CD712CFB1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CBC734A-37E0-4A55-B328-89CFAE297459}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7e06419a-bc24-4bca-aaf1-3b90bf7d837a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/source/ontologies_source.xlsx
+++ b/data/source/ontologies_source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fbosche\Documents\GitHub\BE-OLS\data\source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E6E8BD-D2A1-4833-BF86-BE9CFE30934C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67785F31-6A42-4BEC-8A91-B67743FCC614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="2655" windowWidth="21600" windowHeight="12360" xr2:uid="{C460B36E-D875-4E13-ACEB-9CF2004FB6B5}"/>
+    <workbookView xWindow="8730" yWindow="2850" windowWidth="28800" windowHeight="11295" xr2:uid="{C460B36E-D875-4E13-ACEB-9CF2004FB6B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="14" r:id="rId1"/>
@@ -351,7 +351,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E150" authorId="14" shapeId="0" xr:uid="{CAD6BC40-6B67-4E9E-AB3E-DA05BF8F7896}">
+    <comment ref="E151" authorId="14" shapeId="0" xr:uid="{CAD6BC40-6B67-4E9E-AB3E-DA05BF8F7896}">
       <text>
         <r>
           <rPr>
@@ -368,7 +368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E153" authorId="15" shapeId="0" xr:uid="{3EE948F8-4E0F-4FD4-8BC9-EA54C6408FF1}">
+    <comment ref="E154" authorId="15" shapeId="0" xr:uid="{3EE948F8-4E0F-4FD4-8BC9-EA54C6408FF1}">
       <text>
         <r>
           <rPr>
@@ -390,7 +390,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2933" uniqueCount="1179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2946" uniqueCount="1185">
   <si>
     <t>BE Product (Building)</t>
   </si>
@@ -3947,6 +3947,24 @@
   </si>
   <si>
     <t>https://w3id.org/obpa#</t>
+  </si>
+  <si>
+    <t>Structural Simulation Ontology (SSO)</t>
+  </si>
+  <si>
+    <t>sso</t>
+  </si>
+  <si>
+    <t>https://w3id.org/sso#</t>
+  </si>
+  <si>
+    <t>SSO (Structural Simulation Ontology) is an OWL ontology for representing structural analysis models as an RDF graph. It captures the finite element mesh (objects, nodes, elements), its assembled instances and node/element sets, the materials and sections — including parametric cross-section profiles — assigned to elements, and the load cases, loads, and boundary conditions applied to the model. SSO also provides open-domain properties (referenced_in_sam, idealized_by) for linking a structural analysis model, and the finite elements that idealize a physical component, to descriptions of that same building or bridge in external building/topology ontologies (BOT, BEO, BROT), and a PROV-based Calibration class for recording how a model parameter was calibrated against measured data. SSO is developed to support integrating structural simulation data into knowledge-graph-based digital twins. It is based on the O-SAM (Open Structural Analysis Models) data model available at: https://github.com/LabModelsDigitalsUPC/O-SAM</t>
+  </si>
+  <si>
+    <t>bot, brot, beo</t>
+  </si>
+  <si>
+    <t>dcterms, prov, rdfs</t>
   </si>
 </sst>
 </file>
@@ -4067,7 +4085,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
@@ -4143,6 +4161,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -4235,10 +4256,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}" name="Table2" displayName="Table2" ref="A1:V160" totalsRowShown="0" headerRowDxfId="14">
-  <autoFilter ref="A1:V160" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V160">
-    <sortCondition ref="B1:B160"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}" name="Table2" displayName="Table2" ref="A1:V161" totalsRowShown="0" headerRowDxfId="14">
+  <autoFilter ref="A1:V161" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V161">
+    <sortCondition ref="B1:B161"/>
   </sortState>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{9A74C9B8-D669-464E-AF30-98194DC54E48}" name="title"/>
@@ -4653,7 +4674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6484B993-682B-477D-B31E-A58D58B7BF22}">
-  <dimension ref="A1:Z160"/>
+  <dimension ref="A1:Z161"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.5703125" customWidth="1"/>
@@ -11093,7 +11114,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="107" spans="1:26" ht="105" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:26" ht="165" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>343</v>
       </c>
@@ -11155,7 +11176,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="108" spans="1:26" ht="90" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>1171</v>
       </c>
@@ -11204,7 +11225,7 @@
       <c r="U108" s="30"/>
       <c r="V108" s="32"/>
     </row>
-    <row r="109" spans="1:26" ht="60" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:26" ht="75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>348</v>
       </c>
@@ -11266,7 +11287,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="110" spans="1:26" ht="90" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:26" ht="105" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>352</v>
       </c>
@@ -11391,7 +11412,7 @@
       </c>
       <c r="Z111" s="3"/>
     </row>
-    <row r="112" spans="1:26" ht="90" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>360</v>
       </c>
@@ -11453,7 +11474,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="113" spans="1:22" ht="150" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:22" ht="135" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>792</v>
       </c>
@@ -11517,7 +11538,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="114" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>364</v>
       </c>
@@ -11579,7 +11600,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="115" spans="1:22" ht="150" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>369</v>
       </c>
@@ -11641,7 +11662,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="116" spans="1:22" ht="195" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:22" ht="150" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>1040</v>
       </c>
@@ -11746,7 +11767,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="118" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:22" ht="285" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>582</v>
       </c>
@@ -11805,7 +11826,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="119" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:22" ht="195" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>380</v>
       </c>
@@ -11867,7 +11888,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="120" spans="1:22" ht="165" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>382</v>
       </c>
@@ -11929,7 +11950,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="121" spans="1:22" ht="75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>388</v>
       </c>
@@ -12055,7 +12076,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="123" spans="1:22" ht="150" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:22" ht="165" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>413</v>
       </c>
@@ -12117,7 +12138,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="124" spans="1:22" ht="285" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>419</v>
       </c>
@@ -12242,7 +12263,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="126" spans="1:22" ht="285" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:22" ht="150" x14ac:dyDescent="0.25">
       <c r="A126" s="15" t="s">
         <v>616</v>
       </c>
@@ -12307,7 +12328,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="127" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:22" ht="285" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>605</v>
       </c>
@@ -12372,7 +12393,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="128" spans="1:22" s="15" customFormat="1" ht="255" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:22" s="15" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>607</v>
       </c>
@@ -12438,7 +12459,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="129" spans="1:22" s="15" customFormat="1" ht="135" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:22" s="15" customFormat="1" ht="255" x14ac:dyDescent="0.25">
       <c r="A129" s="15" t="s">
         <v>618</v>
       </c>
@@ -12501,7 +12522,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="130" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:22" ht="135" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>606</v>
       </c>
@@ -12566,7 +12587,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="131" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>611</v>
       </c>
@@ -12631,7 +12652,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="132" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>610</v>
       </c>
@@ -12696,7 +12717,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="133" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A133" s="15" t="s">
         <v>622</v>
       </c>
@@ -12761,7 +12782,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="134" spans="1:22" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:22" s="15" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>609</v>
       </c>
@@ -12827,7 +12848,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="135" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:22" ht="60" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>613</v>
       </c>
@@ -12954,7 +12975,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="137" spans="1:22" ht="150" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A137" s="15" t="s">
         <v>624</v>
       </c>
@@ -13017,7 +13038,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="138" spans="1:22" ht="60" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:22" ht="150" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>422</v>
       </c>
@@ -13082,7 +13103,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="139" spans="1:22" s="15" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:22" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>428</v>
       </c>
@@ -13142,7 +13163,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="140" spans="1:22" s="15" customFormat="1" ht="120" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:22" s="15" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>433</v>
       </c>
@@ -13206,7 +13227,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="141" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>436</v>
       </c>
@@ -13334,7 +13355,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="143" spans="1:22" ht="75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A143" s="15" t="s">
         <v>442</v>
       </c>
@@ -13400,7 +13421,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="144" spans="1:22" s="14" customFormat="1" ht="300" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:22" s="14" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>532</v>
       </c>
@@ -13466,7 +13487,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="145" spans="1:22" ht="270" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:22" ht="300" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>446</v>
       </c>
@@ -13528,7 +13549,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="146" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:22" ht="270" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>449</v>
       </c>
@@ -13590,107 +13611,96 @@
         <v>977</v>
       </c>
     </row>
-    <row r="147" spans="1:22" ht="60" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B147" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C147" s="25" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E147" s="25" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F147" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="G147" s="27" t="s">
+        <v>591</v>
+      </c>
+      <c r="I147" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="J147">
+        <v>2026</v>
+      </c>
+      <c r="K147" t="s">
+        <v>242</v>
+      </c>
+      <c r="L147" s="41" t="s">
+        <v>1182</v>
+      </c>
+      <c r="M147" s="3" t="s">
+        <v>1183</v>
+      </c>
+      <c r="N147" s="13" t="s">
+        <v>1184</v>
+      </c>
+      <c r="O147" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S147" s="31"/>
+      <c r="T147" s="30"/>
+      <c r="U147" s="30"/>
+      <c r="V147" s="32"/>
+    </row>
+    <row r="148" spans="1:22" ht="60" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
         <v>454</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B148" t="s">
         <v>455</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="C148" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="D147" t="s">
-        <v>38</v>
-      </c>
-      <c r="E147" s="1" t="s">
+      <c r="D148" t="s">
+        <v>38</v>
+      </c>
+      <c r="E148" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="F147" t="s">
-        <v>38</v>
-      </c>
-      <c r="G147" t="s">
-        <v>0</v>
-      </c>
-      <c r="H147" t="s">
-        <v>456</v>
-      </c>
-      <c r="I147" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J147">
-        <v>2019</v>
-      </c>
-      <c r="K147" t="s">
-        <v>38</v>
-      </c>
-      <c r="L147" s="3" t="s">
-        <v>837</v>
-      </c>
-      <c r="M147" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="N147" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O147" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P147" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q147" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R147" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="S147" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="U147" s="28" t="s">
-        <v>861</v>
-      </c>
-      <c r="V147" s="3" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="148" spans="1:22" ht="90" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>214</v>
-      </c>
-      <c r="B148" t="s">
-        <v>642</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="D148" t="s">
-        <v>38</v>
-      </c>
       <c r="F148" t="s">
-        <v>215</v>
+        <v>38</v>
       </c>
       <c r="G148" t="s">
         <v>0</v>
       </c>
       <c r="H148" t="s">
-        <v>1</v>
+        <v>456</v>
+      </c>
+      <c r="I148" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="J148">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="K148" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="L148" s="3" t="s">
-        <v>216</v>
+        <v>837</v>
       </c>
       <c r="M148" s="3" t="s">
-        <v>217</v>
+        <v>458</v>
       </c>
       <c r="N148" s="3" t="s">
-        <v>218</v>
+        <v>38</v>
       </c>
       <c r="O148" s="30" t="s">
         <v>29</v>
@@ -13702,7 +13712,7 @@
         <v>29</v>
       </c>
       <c r="R148" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S148" s="31" t="s">
         <v>30</v>
@@ -13711,95 +13721,92 @@
         <v>861</v>
       </c>
       <c r="V148" s="3" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="149" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>214</v>
+      </c>
+      <c r="B149" t="s">
+        <v>642</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="D149" t="s">
+        <v>38</v>
+      </c>
+      <c r="F149" t="s">
+        <v>215</v>
+      </c>
+      <c r="G149" t="s">
+        <v>0</v>
+      </c>
+      <c r="H149" t="s">
+        <v>1</v>
+      </c>
+      <c r="J149">
+        <v>2023</v>
+      </c>
+      <c r="K149" t="s">
+        <v>128</v>
+      </c>
+      <c r="L149" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="M149" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="N149" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="O149" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="P149" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q149" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R149" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S149" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="U149" s="28" t="s">
+        <v>861</v>
+      </c>
+      <c r="V149" s="3" t="s">
         <v>916</v>
       </c>
     </row>
-    <row r="149" spans="1:22" ht="105" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
+    <row r="150" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
         <v>459</v>
       </c>
-      <c r="B149" s="15" t="s">
+      <c r="B150" s="15" t="s">
         <v>460</v>
       </c>
-      <c r="C149" s="17" t="s">
+      <c r="C150" s="17" t="s">
         <v>801</v>
       </c>
-      <c r="D149" t="s">
-        <v>38</v>
-      </c>
-      <c r="E149" s="1" t="s">
+      <c r="D150" t="s">
+        <v>38</v>
+      </c>
+      <c r="E150" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="F149" t="s">
-        <v>38</v>
-      </c>
-      <c r="G149" t="s">
+      <c r="F150" t="s">
+        <v>38</v>
+      </c>
+      <c r="G150" t="s">
         <v>3</v>
       </c>
-      <c r="I149" s="9">
+      <c r="I150" s="9">
         <v>1.01</v>
-      </c>
-      <c r="J149">
-        <v>2013</v>
-      </c>
-      <c r="K149" t="s">
-        <v>38</v>
-      </c>
-      <c r="L149" s="3" t="s">
-        <v>856</v>
-      </c>
-      <c r="M149" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N149" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="O149" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P149" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q149" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R149" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="S149" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="U149" s="28" t="s">
-        <v>879</v>
-      </c>
-      <c r="V149" s="3" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="150" spans="1:22" ht="90" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>463</v>
-      </c>
-      <c r="B150" s="15" t="s">
-        <v>464</v>
-      </c>
-      <c r="C150" s="17" t="s">
-        <v>804</v>
-      </c>
-      <c r="D150" t="s">
-        <v>38</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="F150" t="s">
-        <v>38</v>
-      </c>
-      <c r="G150" t="s">
-        <v>0</v>
-      </c>
-      <c r="I150" s="9">
-        <v>1.1200000000000001</v>
       </c>
       <c r="J150">
         <v>2013</v>
@@ -13808,16 +13815,16 @@
         <v>38</v>
       </c>
       <c r="L150" s="3" t="s">
-        <v>1004</v>
+        <v>856</v>
       </c>
       <c r="M150" s="3" t="s">
-        <v>802</v>
+        <v>38</v>
       </c>
       <c r="N150" s="3" t="s">
-        <v>810</v>
+        <v>462</v>
       </c>
       <c r="O150" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P150" s="30" t="s">
         <v>29</v>
@@ -13826,42 +13833,42 @@
         <v>30</v>
       </c>
       <c r="R150" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="S150" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S150" s="31" t="s">
         <v>30</v>
       </c>
       <c r="U150" s="28" t="s">
-        <v>861</v>
+        <v>879</v>
       </c>
       <c r="V150" s="3" t="s">
-        <v>862</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="151" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B151" s="15" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C151" s="17" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D151" t="s">
         <v>38</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F151" t="s">
         <v>38</v>
       </c>
       <c r="G151" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I151" s="9">
-        <v>1.03</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="J151">
         <v>2013</v>
@@ -13870,16 +13877,16 @@
         <v>38</v>
       </c>
       <c r="L151" s="3" t="s">
-        <v>814</v>
+        <v>1004</v>
       </c>
       <c r="M151" s="3" t="s">
-        <v>38</v>
+        <v>802</v>
       </c>
       <c r="N151" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="O151" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P151" s="30" t="s">
         <v>29</v>
@@ -13888,36 +13895,33 @@
         <v>30</v>
       </c>
       <c r="R151" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="S151" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="T151" s="28">
-        <v>15</v>
+        <v>30</v>
+      </c>
+      <c r="S151" s="30" t="s">
+        <v>30</v>
       </c>
       <c r="U151" s="28" t="s">
-        <v>890</v>
+        <v>861</v>
       </c>
       <c r="V151" s="3" t="s">
-        <v>939</v>
+        <v>862</v>
       </c>
     </row>
     <row r="152" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B152" s="15" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C152" s="17" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D152" t="s">
         <v>38</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="F152" t="s">
         <v>38</v>
@@ -13926,7 +13930,7 @@
         <v>4</v>
       </c>
       <c r="I152" s="9">
-        <v>1.1399999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="J152">
         <v>2013</v>
@@ -13935,16 +13939,16 @@
         <v>38</v>
       </c>
       <c r="L152" s="3" t="s">
-        <v>853</v>
+        <v>814</v>
       </c>
       <c r="M152" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N152" s="3" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="O152" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P152" s="30" t="s">
         <v>29</v>
@@ -13956,39 +13960,42 @@
         <v>29</v>
       </c>
       <c r="S152" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="T152" s="28">
+        <v>15</v>
       </c>
       <c r="U152" s="28" t="s">
-        <v>879</v>
+        <v>890</v>
       </c>
       <c r="V152" s="3" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="153" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="153" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>554</v>
+        <v>469</v>
       </c>
       <c r="B153" s="15" t="s">
-        <v>802</v>
+        <v>470</v>
       </c>
       <c r="C153" s="17" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D153" t="s">
         <v>38</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="F153" t="s">
         <v>38</v>
       </c>
       <c r="G153" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I153" s="9">
-        <v>1.1200000000000001</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="J153">
         <v>2013</v>
@@ -13997,13 +14004,13 @@
         <v>38</v>
       </c>
       <c r="L153" s="3" t="s">
-        <v>1018</v>
+        <v>853</v>
       </c>
       <c r="M153" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N153" s="3" t="s">
-        <v>38</v>
+        <v>807</v>
       </c>
       <c r="O153" s="30" t="s">
         <v>30</v>
@@ -14015,42 +14022,42 @@
         <v>30</v>
       </c>
       <c r="R153" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S153" s="31" t="s">
         <v>29</v>
       </c>
       <c r="U153" s="28" t="s">
-        <v>861</v>
+        <v>879</v>
       </c>
       <c r="V153" s="3" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="154" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="154" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>472</v>
+        <v>554</v>
       </c>
       <c r="B154" s="15" t="s">
-        <v>473</v>
+        <v>802</v>
       </c>
       <c r="C154" s="17" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="D154" t="s">
         <v>38</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="F154" t="s">
         <v>38</v>
       </c>
       <c r="G154" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I154" s="9">
-        <v>1.03</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="J154">
         <v>2013</v>
@@ -14059,394 +14066,456 @@
         <v>38</v>
       </c>
       <c r="L154" s="3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="M154" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N154" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O154" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="P154" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q154" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="R154" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="S154" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="U154" s="28" t="s">
+        <v>861</v>
+      </c>
+      <c r="V154" s="3" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="155" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>472</v>
+      </c>
+      <c r="B155" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="C155" s="17" t="s">
+        <v>806</v>
+      </c>
+      <c r="D155" t="s">
+        <v>38</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="F155" t="s">
+        <v>38</v>
+      </c>
+      <c r="G155" t="s">
+        <v>18</v>
+      </c>
+      <c r="I155" s="9">
+        <v>1.03</v>
+      </c>
+      <c r="J155">
+        <v>2013</v>
+      </c>
+      <c r="K155" t="s">
+        <v>38</v>
+      </c>
+      <c r="L155" s="3" t="s">
         <v>857</v>
       </c>
-      <c r="M154" s="3" t="s">
+      <c r="M155" s="3" t="s">
         <v>1057</v>
       </c>
-      <c r="N154" s="3" t="s">
+      <c r="N155" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="O154" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="P154" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q154" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R154" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="S154" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="U154" s="28" t="s">
+      <c r="O155" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="P155" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q155" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="R155" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="S155" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="U155" s="28" t="s">
         <v>883</v>
       </c>
-      <c r="V154" s="3" t="s">
+      <c r="V155" s="3" t="s">
         <v>1002</v>
       </c>
     </row>
-    <row r="155" spans="1:22" ht="120" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
+    <row r="156" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
         <v>475</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B156" t="s">
         <v>476</v>
       </c>
-      <c r="C155" t="s">
-        <v>38</v>
-      </c>
-      <c r="D155" t="s">
-        <v>38</v>
-      </c>
-      <c r="E155" s="1" t="s">
+      <c r="C156" t="s">
+        <v>38</v>
+      </c>
+      <c r="D156" t="s">
+        <v>38</v>
+      </c>
+      <c r="E156" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="F155" t="s">
-        <v>38</v>
-      </c>
-      <c r="G155" t="s">
+      <c r="F156" t="s">
+        <v>38</v>
+      </c>
+      <c r="G156" t="s">
         <v>12</v>
       </c>
-      <c r="I155" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J155">
+      <c r="I156" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J156">
         <v>2009</v>
       </c>
-      <c r="K155" t="s">
-        <v>38</v>
-      </c>
-      <c r="L155" s="3" t="s">
+      <c r="K156" t="s">
+        <v>38</v>
+      </c>
+      <c r="L156" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M155" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N155" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O155" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P155" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q155" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R155" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="S155" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="U155" s="28" t="s">
+      <c r="M156" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N156" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O156" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="P156" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q156" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R156" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="S156" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="U156" s="28" t="s">
         <v>879</v>
       </c>
-      <c r="V155" s="3" t="s">
+      <c r="V156" s="3" t="s">
         <v>999</v>
       </c>
     </row>
-    <row r="156" spans="1:22" ht="120" x14ac:dyDescent="0.25">
-      <c r="A156" s="4" t="s">
+    <row r="157" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B157" t="s">
         <v>515</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="C157" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="D156" t="s">
-        <v>38</v>
-      </c>
-      <c r="E156" s="1" t="s">
+      <c r="D157" t="s">
+        <v>38</v>
+      </c>
+      <c r="E157" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="F156" t="s">
-        <v>38</v>
-      </c>
-      <c r="G156" t="s">
+      <c r="F157" t="s">
+        <v>38</v>
+      </c>
+      <c r="G157" t="s">
         <v>17</v>
       </c>
-      <c r="I156" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J156">
+      <c r="I157" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J157">
         <v>2024</v>
       </c>
-      <c r="K156" t="s">
+      <c r="K157" t="s">
         <v>128</v>
       </c>
-      <c r="L156" s="3" t="s">
+      <c r="L157" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="M156" s="3" t="s">
+      <c r="M157" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="N156" s="3" t="s">
+      <c r="N157" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="O156" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P156" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q156" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R156" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="S156" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="U156" s="28" t="s">
+      <c r="O157" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="P157" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q157" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R157" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S157" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="U157" s="28" t="s">
         <v>859</v>
       </c>
-      <c r="V156" s="3" t="s">
+      <c r="V157" s="3" t="s">
         <v>997</v>
       </c>
     </row>
-    <row r="157" spans="1:22" ht="90" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
+    <row r="158" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
         <v>478</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B158" t="s">
         <v>479</v>
       </c>
-      <c r="C157" t="s">
-        <v>38</v>
-      </c>
-      <c r="D157" t="s">
-        <v>38</v>
-      </c>
-      <c r="E157" s="1" t="s">
+      <c r="C158" t="s">
+        <v>38</v>
+      </c>
+      <c r="D158" t="s">
+        <v>38</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="F157" t="s">
-        <v>38</v>
-      </c>
-      <c r="G157" t="s">
+      <c r="F158" t="s">
+        <v>38</v>
+      </c>
+      <c r="G158" t="s">
         <v>12</v>
       </c>
-      <c r="I157" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J157">
+      <c r="I158" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J158">
         <v>2009</v>
       </c>
-      <c r="K157" t="s">
-        <v>38</v>
-      </c>
-      <c r="L157" s="3" t="s">
+      <c r="K158" t="s">
+        <v>38</v>
+      </c>
+      <c r="L158" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M157" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N157" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O157" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P157" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q157" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R157" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="S157" s="31"/>
-      <c r="U157" s="28" t="s">
+      <c r="M158" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N158" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O158" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="P158" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q158" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R158" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="S158" s="31"/>
+      <c r="U158" s="28" t="s">
         <v>879</v>
       </c>
-      <c r="V157" s="3" t="s">
+      <c r="V158" s="3" t="s">
         <v>1000</v>
       </c>
     </row>
-    <row r="158" spans="1:22" ht="315" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
+    <row r="159" spans="1:22" ht="315" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
         <v>481</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B159" t="s">
         <v>482</v>
       </c>
-      <c r="C158" s="2" t="s">
+      <c r="C159" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="D158" t="s">
+      <c r="D159" t="s">
         <v>32</v>
       </c>
-      <c r="E158" s="1" t="s">
+      <c r="E159" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F158" t="s">
-        <v>38</v>
-      </c>
-      <c r="G158" t="s">
+      <c r="F159" t="s">
+        <v>38</v>
+      </c>
+      <c r="G159" t="s">
         <v>18</v>
       </c>
-      <c r="I158" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J158">
+      <c r="I159" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J159">
         <v>2020</v>
       </c>
-      <c r="K158" t="s">
+      <c r="K159" t="s">
         <v>23</v>
       </c>
-      <c r="L158" s="3" t="s">
+      <c r="L159" s="3" t="s">
         <v>1014</v>
       </c>
-      <c r="M158" s="3" t="s">
+      <c r="M159" s="3" t="s">
         <v>1115</v>
       </c>
-      <c r="N158" s="3" t="s">
+      <c r="N159" s="3" t="s">
         <v>1114</v>
       </c>
-      <c r="O158" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="P158" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q158" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R158" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="S158" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="U158" s="28" t="s">
+      <c r="O159" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="P159" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q159" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R159" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S159" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="U159" s="28" t="s">
         <v>883</v>
       </c>
-      <c r="V158" s="3" t="s">
+      <c r="V159" s="3" t="s">
         <v>884</v>
       </c>
     </row>
-    <row r="159" spans="1:22" ht="255" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
+    <row r="160" spans="1:22" ht="255" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
         <v>703</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B160" t="s">
         <v>1057</v>
       </c>
-      <c r="C159" s="25" t="s">
+      <c r="C160" s="25" t="s">
         <v>1170</v>
       </c>
-      <c r="D159" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E159" s="1" t="s">
+      <c r="D160" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E160" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="F159" t="s">
-        <v>38</v>
-      </c>
-      <c r="G159" t="s">
+      <c r="F160" t="s">
+        <v>38</v>
+      </c>
+      <c r="G160" t="s">
         <v>7</v>
       </c>
-      <c r="I159" s="9">
+      <c r="I160" s="9">
         <v>1.21</v>
       </c>
-      <c r="J159">
+      <c r="J160">
         <v>2006</v>
       </c>
-      <c r="L159" s="3" t="s">
+      <c r="L160" s="3" t="s">
         <v>858</v>
       </c>
-      <c r="M159" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N159" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="O159" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="P159" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q159" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R159" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="S159" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="T159" s="28">
-        <v>30</v>
-      </c>
-      <c r="U159" s="30" t="s">
+      <c r="M160" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N160" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O160" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="P160" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q160" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R160" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S160" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="T160" s="28">
+        <v>30</v>
+      </c>
+      <c r="U160" s="30" t="s">
         <v>883</v>
       </c>
-      <c r="V159" s="32" t="s">
+      <c r="V160" s="32" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="160" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
+    <row r="161" spans="1:22" ht="360" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
         <v>1052</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B161" t="s">
         <v>1053</v>
       </c>
-      <c r="C160" s="25" t="s">
+      <c r="C161" s="25" t="s">
         <v>1062</v>
       </c>
-      <c r="D160" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E160" s="27" t="s">
+      <c r="D161" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E161" s="27" t="s">
         <v>1063</v>
       </c>
-      <c r="F160" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="G160" t="s">
+      <c r="F161" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="G161" t="s">
         <v>4</v>
       </c>
-      <c r="H160" t="s">
+      <c r="H161" t="s">
         <v>14</v>
       </c>
-      <c r="I160" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J160">
+      <c r="I161" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J161">
         <v>2026</v>
       </c>
-      <c r="K160" t="s">
+      <c r="K161" t="s">
         <v>23</v>
       </c>
-      <c r="L160" s="3" t="s">
+      <c r="L161" s="3" t="s">
         <v>1054</v>
       </c>
-      <c r="M160" t="s">
+      <c r="M161" t="s">
         <v>1055</v>
       </c>
-      <c r="N160" s="13" t="s">
+      <c r="N161" s="13" t="s">
         <v>1056</v>
       </c>
-      <c r="O160" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="S160" s="31"/>
-      <c r="T160" s="30"/>
-      <c r="U160" s="30"/>
-      <c r="V160" s="32"/>
+      <c r="O161" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S161" s="31"/>
+      <c r="T161" s="30"/>
+      <c r="U161" s="30"/>
+      <c r="V161" s="32"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -14456,7 +14525,7 @@
     <hyperlink ref="C31" r:id="rId3" xr:uid="{647907ED-3EF1-4900-B2E2-99B4EA674B9D}"/>
     <hyperlink ref="C112" r:id="rId4" xr:uid="{FAE6907E-C81E-4A5D-817E-230B91B1B725}"/>
     <hyperlink ref="C60" r:id="rId5" xr:uid="{C753E4AB-C43C-4DA7-BCBB-4C6B42AE449C}"/>
-    <hyperlink ref="C147" r:id="rId6" xr:uid="{371EC661-68AD-4E55-A1EB-3AD1B3210212}"/>
+    <hyperlink ref="C148" r:id="rId6" xr:uid="{371EC661-68AD-4E55-A1EB-3AD1B3210212}"/>
     <hyperlink ref="C146" r:id="rId7" xr:uid="{87EC244C-7916-48F7-AB46-F1434A4E3208}"/>
     <hyperlink ref="C64" r:id="rId8" xr:uid="{C7C324AF-CD50-4932-996A-89F85253BFD5}"/>
     <hyperlink ref="C4" r:id="rId9" xr:uid="{EDB880A2-AA3E-4F26-A446-E9157F173772}"/>
@@ -14480,7 +14549,7 @@
     <hyperlink ref="C68" r:id="rId27" xr:uid="{6774AFFC-3F72-4FC8-83D4-C6E9745490F7}"/>
     <hyperlink ref="C39" r:id="rId28" xr:uid="{D01E6549-8C0C-4A44-AF08-ED09A47D4252}"/>
     <hyperlink ref="C123" r:id="rId29" xr:uid="{DE66E60B-BA52-4BF5-91BF-04E031C85DF4}"/>
-    <hyperlink ref="C158" r:id="rId30" xr:uid="{6B7C0C1E-80A1-4C90-B400-939A08EB9E26}"/>
+    <hyperlink ref="C159" r:id="rId30" xr:uid="{6B7C0C1E-80A1-4C90-B400-939A08EB9E26}"/>
     <hyperlink ref="C145" r:id="rId31" xr:uid="{39C94BCA-35A0-4C33-8523-A608427AF1AC}"/>
     <hyperlink ref="C142" r:id="rId32" xr:uid="{0078D0DD-F4F6-49B0-885D-B066223BAE60}"/>
     <hyperlink ref="C141" r:id="rId33" xr:uid="{C5712289-6DD8-4698-B94D-78A55B1677AB}"/>
@@ -14529,7 +14598,7 @@
     <hyperlink ref="C32" r:id="rId76" xr:uid="{741DF32C-57B4-4296-8D2B-447F78C164E4}"/>
     <hyperlink ref="C2" r:id="rId77" xr:uid="{9C1B3465-ED4E-4642-BA4D-5C7E5510B7B6}"/>
     <hyperlink ref="C77" r:id="rId78" xr:uid="{AB3EAE1F-65EA-44FC-AB99-16D2D5ED71B3}"/>
-    <hyperlink ref="C156" r:id="rId79" xr:uid="{CF6EACC9-E6EB-45BD-B707-52712C2A62C9}"/>
+    <hyperlink ref="C157" r:id="rId79" xr:uid="{CF6EACC9-E6EB-45BD-B707-52712C2A62C9}"/>
     <hyperlink ref="C104" r:id="rId80" xr:uid="{02D0ECDA-FD32-4CF7-8440-EC4C7DCD63E5}"/>
     <hyperlink ref="C144" r:id="rId81" location=" " xr:uid="{2FFDF6BA-7A97-4D5C-9D4F-2CCB9C0E6DED}"/>
     <hyperlink ref="C102" r:id="rId82" xr:uid="{7F7A3FF6-CCE9-4E2E-982B-1B4E31731333}"/>
@@ -14553,15 +14622,15 @@
     <hyperlink ref="E71" r:id="rId100" xr:uid="{C5A0DFB4-1FB7-49B8-8FD3-9AC01312958D}"/>
     <hyperlink ref="E109" r:id="rId101" xr:uid="{51CBF759-50E7-428F-81D5-CB1BF0D6F9DE}"/>
     <hyperlink ref="E140" r:id="rId102" xr:uid="{DD230CEE-1804-40FB-BD78-0C67303DB967}"/>
-    <hyperlink ref="E147" r:id="rId103" location="f0020" xr:uid="{3778DDB7-E612-4F6A-A3B0-B453CF8B64A9}"/>
+    <hyperlink ref="E148" r:id="rId103" location="f0020" xr:uid="{3778DDB7-E612-4F6A-A3B0-B453CF8B64A9}"/>
     <hyperlink ref="E101" r:id="rId104" xr:uid="{88E00939-FB4B-46C7-8C26-9BF914C2DEFC}"/>
     <hyperlink ref="E123" r:id="rId105" xr:uid="{1BF75D9D-D348-4E2D-9C84-905D4A8F3B25}"/>
     <hyperlink ref="E53" r:id="rId106" xr:uid="{731847B6-AFA8-4FD0-B2B9-DA4073CF6576}"/>
-    <hyperlink ref="E154" r:id="rId107" xr:uid="{A734FA6A-1E5E-4197-893E-26AEB8863486}"/>
-    <hyperlink ref="E150" r:id="rId108" xr:uid="{2DAAFB64-43EF-4609-9512-3EECAF83A0D8}"/>
+    <hyperlink ref="E155" r:id="rId107" xr:uid="{A734FA6A-1E5E-4197-893E-26AEB8863486}"/>
+    <hyperlink ref="E151" r:id="rId108" xr:uid="{2DAAFB64-43EF-4609-9512-3EECAF83A0D8}"/>
     <hyperlink ref="E21" r:id="rId109" location="s0035" xr:uid="{B0E30218-34ED-4F0F-8578-9A603C364391}"/>
-    <hyperlink ref="E155" r:id="rId110" xr:uid="{33D09351-6D20-4F3E-B2E7-73DE845CAB80}"/>
-    <hyperlink ref="E157" r:id="rId111" xr:uid="{BA5C5148-161B-4925-9347-1EBB2828D7A5}"/>
+    <hyperlink ref="E156" r:id="rId110" xr:uid="{33D09351-6D20-4F3E-B2E7-73DE845CAB80}"/>
+    <hyperlink ref="E158" r:id="rId111" xr:uid="{BA5C5148-161B-4925-9347-1EBB2828D7A5}"/>
     <hyperlink ref="E138" r:id="rId112" xr:uid="{686C1381-B3D9-4F4F-B355-F6C8BDA10898}"/>
     <hyperlink ref="E81" r:id="rId113" xr:uid="{8A34E89F-B55C-44D1-9032-56436D05CE5D}"/>
     <hyperlink ref="E35" r:id="rId114" xr:uid="{F267D5CF-D0FE-473C-A3F7-FECCC233A441}"/>
@@ -14571,9 +14640,9 @@
     <hyperlink ref="E145" r:id="rId118" xr:uid="{81632F3A-005C-4176-BECE-2F3B9EEB6891}"/>
     <hyperlink ref="E107" r:id="rId119" xr:uid="{37A04716-A03F-4D57-96D9-A5BFAD7D2359}"/>
     <hyperlink ref="E143" r:id="rId120" xr:uid="{0E7FBF6C-CAA7-4FF2-A8EE-7F2D8A88BF96}"/>
-    <hyperlink ref="E151" r:id="rId121" xr:uid="{D55E6DD1-6984-4A50-A0AD-BA6FF596E41C}"/>
+    <hyperlink ref="E152" r:id="rId121" xr:uid="{D55E6DD1-6984-4A50-A0AD-BA6FF596E41C}"/>
     <hyperlink ref="E119" r:id="rId122" xr:uid="{2B877B96-8FD1-4F41-B88E-AD70830BE725}"/>
-    <hyperlink ref="E149" r:id="rId123" xr:uid="{7CB9413F-F297-47A4-B2F8-2E8BEC8F96E8}"/>
+    <hyperlink ref="E150" r:id="rId123" xr:uid="{7CB9413F-F297-47A4-B2F8-2E8BEC8F96E8}"/>
     <hyperlink ref="E36" r:id="rId124" xr:uid="{FA27BDCB-DB0A-480B-876B-7B017E0E677B}"/>
     <hyperlink ref="E31" r:id="rId125" xr:uid="{48520E64-60FA-43C7-9523-3F8A2187E6CC}"/>
     <hyperlink ref="E33" r:id="rId126" xr:uid="{05E3211D-230E-48F4-BB1E-822C21AAAFED}"/>
@@ -14587,8 +14656,8 @@
     <hyperlink ref="E117" r:id="rId134" xr:uid="{E4CE47AF-12EB-4DBE-9E99-0FABFC9402A8}"/>
     <hyperlink ref="E139" r:id="rId135" xr:uid="{A59ECC74-526B-4136-A3D5-05BA9BB6787C}"/>
     <hyperlink ref="E142" r:id="rId136" xr:uid="{D6FF6640-82FF-4A0D-A828-72ED67D3AD4F}"/>
-    <hyperlink ref="E158" r:id="rId137" xr:uid="{9B13D64B-97F0-4098-BAE2-F0343CD81A80}"/>
-    <hyperlink ref="E152" r:id="rId138" xr:uid="{BADE4669-D317-4460-B448-C8D94D35753B}"/>
+    <hyperlink ref="E159" r:id="rId137" xr:uid="{9B13D64B-97F0-4098-BAE2-F0343CD81A80}"/>
+    <hyperlink ref="E153" r:id="rId138" xr:uid="{BADE4669-D317-4460-B448-C8D94D35753B}"/>
     <hyperlink ref="E146" r:id="rId139" xr:uid="{850A2301-83A8-46A6-86BC-61587D12CD21}"/>
     <hyperlink ref="E141" r:id="rId140" xr:uid="{7E135D94-3307-4285-876D-E50B63D987DF}"/>
     <hyperlink ref="E69" r:id="rId141" xr:uid="{1AED701A-018D-49C9-969C-0C378A17C522}"/>
@@ -14652,12 +14721,12 @@
     <hyperlink ref="E2" r:id="rId199" xr:uid="{FA6C54D1-21A6-4366-A61A-B63E45510502}"/>
     <hyperlink ref="E20" r:id="rId200" xr:uid="{1811DDC7-B1CB-48D6-97CC-8589C8A392B3}"/>
     <hyperlink ref="E77" r:id="rId201" xr:uid="{C5DA3CF3-7B30-4A03-82DD-7F2E14081684}"/>
-    <hyperlink ref="E156" r:id="rId202" xr:uid="{7115DB7A-AE90-495D-9676-EA1BA0F179A0}"/>
+    <hyperlink ref="E157" r:id="rId202" xr:uid="{7115DB7A-AE90-495D-9676-EA1BA0F179A0}"/>
     <hyperlink ref="E104" r:id="rId203" xr:uid="{E875AA82-E9BD-43BA-B96A-443BE71A661D}"/>
     <hyperlink ref="E144" r:id="rId204" display="https://standards.cencenelec.eu/dyn/www/f?p=CEN:110:0::::FSP_PROJECT,FSP_ORG_ID:67839,1991542&amp;cs=1BCE2DE4154949B53FB406C2D4EE5011D " xr:uid="{1198A376-FAFB-4B63-8F31-3CC40DDC0188}"/>
     <hyperlink ref="E102" r:id="rId205" xr:uid="{CDB629AC-7318-4A45-902E-8C95EF4661CF}"/>
     <hyperlink ref="E38" r:id="rId206" xr:uid="{F20CB13F-7541-474A-BB7F-D8B745D301C0}"/>
-    <hyperlink ref="E153" r:id="rId207" xr:uid="{62676230-6266-4D08-B848-64E61BE4B592}"/>
+    <hyperlink ref="E154" r:id="rId207" xr:uid="{62676230-6266-4D08-B848-64E61BE4B592}"/>
     <hyperlink ref="E93" r:id="rId208" display="https://lov.linkeddata.es/dataset/lov/vocabs/jup/versions/2016-07-14.n3" xr:uid="{AE487E94-18DC-4254-BE84-4C41E95CF5BD}"/>
     <hyperlink ref="E43" r:id="rId209" xr:uid="{3B2D46D8-B3FB-420A-B722-C4AE65399511}"/>
     <hyperlink ref="E80" r:id="rId210" xr:uid="{CEDD056B-0AF1-476A-BD5E-3BDADF64D853}"/>
@@ -14674,10 +14743,10 @@
     <hyperlink ref="E133" r:id="rId221" xr:uid="{A941CDD9-0B08-4ACA-8885-324C2A700E2F}"/>
     <hyperlink ref="E137" r:id="rId222" xr:uid="{4183CDB1-AB57-415B-91B7-AABB33124063}"/>
     <hyperlink ref="E72" r:id="rId223" xr:uid="{BE8311D4-A8A6-4008-870A-9CEF9052ED5C}"/>
-    <hyperlink ref="C148" r:id="rId224" xr:uid="{8A2C5288-ADB4-463A-85BA-B1183BAF8DDF}"/>
+    <hyperlink ref="C149" r:id="rId224" xr:uid="{8A2C5288-ADB4-463A-85BA-B1183BAF8DDF}"/>
     <hyperlink ref="C66" r:id="rId225" xr:uid="{07F92C0D-DB82-4582-A72B-52659867C160}"/>
     <hyperlink ref="C8" r:id="rId226" xr:uid="{A84DDA47-6ACC-464D-952D-0387101E0611}"/>
-    <hyperlink ref="C159" r:id="rId227" xr:uid="{AE033172-A711-4880-AB36-40FB9AE60B05}"/>
+    <hyperlink ref="C160" r:id="rId227" xr:uid="{AE033172-A711-4880-AB36-40FB9AE60B05}"/>
     <hyperlink ref="C3" r:id="rId228" xr:uid="{87BD7AD7-F7D3-4FFD-A9E2-12853E86A7FE}"/>
     <hyperlink ref="E3" r:id="rId229" xr:uid="{512DDB69-1C56-4690-B2D9-AC64B48E7A6E}"/>
     <hyperlink ref="C65" r:id="rId230" xr:uid="{0F674644-7FE0-46D4-B1A3-3075C11E0658}"/>
@@ -14685,16 +14754,16 @@
     <hyperlink ref="E75" r:id="rId232" xr:uid="{D09DEDB3-49E2-4C48-B494-81711DA43BF0}"/>
     <hyperlink ref="C83" r:id="rId233" display="https://w3id.org/hmo" xr:uid="{E4AF1C6F-DF28-43F7-ACA9-70BE220B042B}"/>
     <hyperlink ref="E83" r:id="rId234" xr:uid="{49B2000D-4C70-49FD-A5F3-84C8A5029347}"/>
-    <hyperlink ref="C149" r:id="rId235" xr:uid="{0D2D8DED-68FD-46CA-AE92-1461FF576E92}"/>
-    <hyperlink ref="C151" r:id="rId236" xr:uid="{290C515B-CDF1-463F-85EB-BCFC5378D1E4}"/>
-    <hyperlink ref="C150" r:id="rId237" xr:uid="{DFE53865-6A47-46EC-BB35-4A0B7009EA86}"/>
-    <hyperlink ref="C152" r:id="rId238" xr:uid="{54FC6350-1D41-40D1-85C1-5FEB82150346}"/>
-    <hyperlink ref="C153" r:id="rId239" xr:uid="{218ED3BE-F2B1-4A98-ADC4-F128684E3B28}"/>
-    <hyperlink ref="C154" r:id="rId240" xr:uid="{31E930C8-EAAF-4B34-8443-75427984FA75}"/>
+    <hyperlink ref="C150" r:id="rId235" xr:uid="{0D2D8DED-68FD-46CA-AE92-1461FF576E92}"/>
+    <hyperlink ref="C152" r:id="rId236" xr:uid="{290C515B-CDF1-463F-85EB-BCFC5378D1E4}"/>
+    <hyperlink ref="C151" r:id="rId237" xr:uid="{DFE53865-6A47-46EC-BB35-4A0B7009EA86}"/>
+    <hyperlink ref="C153" r:id="rId238" xr:uid="{54FC6350-1D41-40D1-85C1-5FEB82150346}"/>
+    <hyperlink ref="C154" r:id="rId239" xr:uid="{218ED3BE-F2B1-4A98-ADC4-F128684E3B28}"/>
+    <hyperlink ref="C155" r:id="rId240" xr:uid="{31E930C8-EAAF-4B34-8443-75427984FA75}"/>
     <hyperlink ref="C116" r:id="rId241" xr:uid="{379FD10B-9650-463A-84C0-55B4727D7D47}"/>
     <hyperlink ref="E116" r:id="rId242" xr:uid="{F803CDF1-49F8-4F15-83C4-1374EEB2B30A}"/>
     <hyperlink ref="C100" r:id="rId243" xr:uid="{C5C87514-E810-480B-A94B-83BB9DAD7389}"/>
-    <hyperlink ref="C160" r:id="rId244" xr:uid="{6EEE95DA-9BE0-4E1F-8E9A-8A354ABF1F8F}"/>
+    <hyperlink ref="C161" r:id="rId244" xr:uid="{6EEE95DA-9BE0-4E1F-8E9A-8A354ABF1F8F}"/>
     <hyperlink ref="C23" r:id="rId245" xr:uid="{0379DD25-CEE8-4F75-8C9B-E81D3B61747B}"/>
     <hyperlink ref="E23" r:id="rId246" xr:uid="{E2A3119B-37AA-43A8-A582-4ED028637960}"/>
     <hyperlink ref="C10" r:id="rId247" xr:uid="{A32D057F-0E64-4CBF-9B62-C57706447D34}"/>
@@ -14722,12 +14791,15 @@
     <hyperlink ref="C108" r:id="rId269" xr:uid="{8FBB5FBA-13BC-43C3-B062-F0D13FB9E1AF}"/>
     <hyperlink ref="E108" r:id="rId270" display="https://github.com/RUB-Informatik-im-Bauwesen/ontobpr" xr:uid="{C4A389CC-BE51-4488-8EDC-9866A1041CA5}"/>
     <hyperlink ref="C103" r:id="rId271" xr:uid="{4788DE4E-DD21-4F17-A0F5-F0127C036B93}"/>
+    <hyperlink ref="C147" r:id="rId272" xr:uid="{974442D1-A6FC-4CBA-B667-CA2C80F3B18E}"/>
+    <hyperlink ref="E147" r:id="rId273" xr:uid="{0A024D95-D6C9-4056-8AF8-FFA69686DFC8}"/>
+    <hyperlink ref="L147" r:id="rId274" display="https://github.com/LabModelsDigitalsUPC/O-SAM" xr:uid="{9E54F971-A463-433E-916E-4AB8AA14E048}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId272"/>
-  <legacyDrawing r:id="rId273"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId275"/>
+  <legacyDrawing r:id="rId276"/>
   <tableParts count="1">
-    <tablePart r:id="rId274"/>
+    <tablePart r:id="rId277"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -14736,7 +14808,7 @@
           <x14:formula1>
             <xm:f>Domains!$A$2:$A$28</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:H2 G4:H53 G55:H62 G64:H69 G71:H158 G159:G160</xm:sqref>
+          <xm:sqref>G2:H2 G4:H53 G55:H62 G64:H69 G71:H160 H161</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
